--- a/source_to_target__dbt_mapping_template.xlsx
+++ b/source_to_target__dbt_mapping_template.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STM_MAPPING'!$A$1:$K$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'STM_MAPPING'!$A$1:$T$501</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'STM_MAPPING'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -341,6 +341,69 @@
 Example: emp.updated_at &gt; (select max(updated_at) from {{ this }})</t>
       </text>
     </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Row-level)
+dbt source (system) the table belongs to, e.g. epic_clarity. Blank = --source-name (default raw). Drives the default staging folder and stg_&lt;source&gt;__&lt;table&gt; names.
+Example: hr</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Model-level)
+Custom schema for the model -&gt; config(schema=...).
+Example: hr</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Model-level)
+Comma-separated dbt tags (for selection: dbt build -s tag:daily).
+Example: hr,daily</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Recommended (Model-level)
+Model description written to the YAML docs.
+Example: One row per employee with department.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Recommended (Row-level)
+Column description written to the YAML docs.
+Example: Employee name, upper-cased</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Row-level)
+Comma-separated tests: not_null, unique, accepted_values(A|B|C), relationships(model.column), or any package test (dbt_utils.not_empty_string). Key columns get not_null/unique automatically.
+Example: not_null, relationships(dept_target.deptno)</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Model-level)
+Y = read sources through a stg_&lt;source&gt;__&lt;table&gt; view (ref); N = select from source() directly. Blank = generator default (--staging / --no-staging, off unless set).
+Example: Y</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Row-level)
+Folder under models/ for the staging model of THIS row's source table (and its sources.yml). Blank = staging/&lt;SOURCE_NAME&gt;. Nested allowed. Used only when the table is staged.
+Example: staging/hr/reference</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional (Model-level)
+Folder under models/ for the target model (.sql + docs yml). Blank = marts. Nested allowed, e.g. marts/finance/reporting.
+Example: marts/hr</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -634,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F37"/>
+  <dimension ref="B2:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -677,7 +740,7 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2. Model-level fields (MATERIALIZATION, UNIQUE_KEY, JOIN_*, INCREMENTAL_FILTER) only need filling on the model's first row.</t>
+          <t>2. Model-level fields (Scope = Model below) only need filling on the model's first row.</t>
         </is>
       </c>
     </row>
@@ -705,129 +768,69 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6. Check dbt_output/generation_report.md after each run. Models with errors are skipped (exit code 1).</t>
+          <t>6. Staging layer is optional: USE_STAGING = Y builds stg_ views for that model's sources; blank follows the --staging flag (off by default).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>7. In expressions, join conditions and filters, reference other source columns as table.column (e.g. emp.lname) so they reach the staging model.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>8. Folders: TARGET_MODEL_FOLDER places the model under models/&lt;folder&gt; (blank = marts). STAGING_MODEL_FOLDER places a source table's stg_ model (blank = staging/&lt;SOURCE_NAME&gt;). Paths are relative to models/, e.g. marts/finance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>9. Check dbt_output/generation_report.md after each run. Models with errors are skipped (exit code 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Column guide</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>SOURCE_TABLE</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Source table name. Its lower-cased name becomes the table alias in SQL and join conditions.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>EMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>SOURCE_COLUMN</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Source column name.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>ENAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>TARGET_TABLE</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Row</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Target table. Should be the same on every row of a model; becomes the dbt alias if it differs from MODEL_NAME.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>EMP_TARGET</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>TARGET_COLUMN</t>
+          <t>SOURCE_TABLE</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -842,24 +845,24 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Target column name, OR a SQL expression on the source column (e.g. upper(ename)). An expression is aliased with the source column name.</t>
+          <t>Source table name. Its lower-cased name becomes the table alias in SQL and join conditions.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>upper(ename)</t>
+          <t>EMP</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>TARGET_DATATYPE</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>SOURCE_COLUMN</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -869,24 +872,24 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Type to cast to. Blank = direct mapping, no cast.</t>
+          <t>Source column name.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>ENAME</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>MODEL_NAME</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Required</t>
+          <t>TARGET_TABLE</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -896,19 +899,19 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>dbt model file. One .sql is generated per distinct value. '.sql' suffix optional.</t>
+          <t>Target table. Should be the same on every row of a model; becomes the dbt alias if it differs from MODEL_NAME.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>emp_target.sql</t>
+          <t>EMP_TARGET</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>MATERIALIZATION</t>
+          <t>TARGET_COLUMN</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -918,83 +921,83 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>table | view | incremental | ephemeral. Fill on the model's first row (other rows blank or identical).</t>
+          <t>Target column name, OR a SQL expression on the source column (e.g. upper(ename)). An expression is aliased with the source column name.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>upper(ename)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>UNIQUE_KEY</t>
+          <t>TARGET_DATATYPE</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Key column(s), comma-separated for composite keys. Must match TARGET column names. Drives not_null/unique tests.</t>
+          <t>Type to cast to. Blank = direct mapping, no cast.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>empno,deptno</t>
+          <t>varchar(100)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>JOIN_CONDITION</t>
+          <t>MODEL_NAME</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Conditional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Required when a model has 2+ source tables. Use lower-case table names as aliases. Separate multiple predicates with ';'.</t>
+          <t>dbt model file. One .sql is generated per distinct value. '.sql' suffix optional.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>emp.deptno=dept.deptno</t>
+          <t>emp_target.sql</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>JOIN_TYPE</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>MATERIALIZATION</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1004,143 +1007,502 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>inner (default) | left | right | full. Applied to all joins in the model.</t>
+          <t>table | view | incremental | ephemeral. Fill on the model's first row (other rows blank or identical).</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>table</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>UNIQUE_KEY</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Key column(s), comma-separated for composite keys. Must match TARGET column names. Drives not_null/unique tests.</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>empno,deptno</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>JOIN_CONDITION</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Required when a model has 2+ source tables. Use lower-case table names as aliases. Separate multiple predicates with ';'.</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>emp.deptno=dept.deptno</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>JOIN_TYPE</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>inner (default) | left | right | full. Applied to all joins in the model.</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
           <t>INCREMENTAL_FILTER</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Only for incremental models: predicate placed inside {% if is_incremental() %}.</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>emp.updated_at &gt; (select max(updated_at) from {{ this }})</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SOURCE_NAME</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>dbt source (system) the table belongs to, e.g. epic_clarity. Blank = --source-name (default raw). Drives the default staging folder and stg_&lt;source&gt;__&lt;table&gt; names.</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>SCHEMA</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Custom schema for the model -&gt; config(schema=...).</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>TAGS</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Comma-separated dbt tags (for selection: dbt build -s tag:daily).</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>hr,daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>MODEL_DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Model description written to the YAML docs.</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>One row per employee with department.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>COLUMN_DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Column description written to the YAML docs.</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Employee name, upper-cased</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>COLUMN_TESTS</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Comma-separated tests: not_null, unique, accepted_values(A|B|C), relationships(model.column), or any package test (dbt_utils.not_empty_string). Key columns get not_null/unique automatically.</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>not_null, relationships(dept_target.deptno)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>USE_STAGING</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Y = read sources through a stg_&lt;source&gt;__&lt;table&gt; view (ref); N = select from source() directly. Blank = generator default (--staging / --no-staging, off unless set).</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>STAGING_MODEL_FOLDER</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Folder under models/ for the staging model of THIS row's source table (and its sources.yml). Blank = staging/&lt;SOURCE_NAME&gt;. Nested allowed. Used only when the table is staged.</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>staging/hr/reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>TARGET_MODEL_FOLDER</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Folder under models/ for the target model (.sql + docs yml). Blank = marts. Nested allowed, e.g. marts/finance/reporting.</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>marts/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="10" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Red header</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Required (or required when the condition applies, e.g. JOIN_CONDITION for multi-source models)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Blue header</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Recommended / optional</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="12" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Grey rows</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Example rows - replace with your own</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Validation checks run by the generator</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="13" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>ERROR  - model has 2+ source tables but no JOIN_CONDITION, or a source not referenced by any join</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="13" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>ERROR  - duplicate target column within a model; UNIQUE_KEY not among the model's target columns</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="13" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>ERROR  - conflicting or unsupported MATERIALIZATION values within one model</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="13" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>WARN   - rows in one model point to different TARGET_TABLEs (usually a wrong MODEL_NAME)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>WARN   - incremental model without UNIQUE_KEY or INCREMENTAL_FILTER</t>
+    <row r="49">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>WARN   - incremental model without UNIQUE_KEY or INCREMENTAL_FILTER; non-snake_case names</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>ERROR  - USE_STAGING not Y/N, or conflicting values within one model</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>ERROR  - folder is absolute, contains '..' or invalid characters; conflicting TARGET_MODEL_FOLDER in one model</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>WARN   - one source table given different STAGING_MODEL_FOLDER values (first one is used)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>WARN   - --enforce-contracts but a column has no TARGET_DATATYPE (contract skipped for that model)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="21">
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B50:F50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1153,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:T501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1167,6 +1529,15 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1225,6 +1596,51 @@
           <t>INCREMENTAL_FILTER</t>
         </is>
       </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>SOURCE_NAME</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>SCHEMA</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>TAGS</t>
+        </is>
+      </c>
+      <c r="O1" s="15" t="inlineStr">
+        <is>
+          <t>MODEL_DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="P1" s="15" t="inlineStr">
+        <is>
+          <t>COLUMN_DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="Q1" s="15" t="inlineStr">
+        <is>
+          <t>COLUMN_TESTS</t>
+        </is>
+      </c>
+      <c r="R1" s="15" t="inlineStr">
+        <is>
+          <t>USE_STAGING</t>
+        </is>
+      </c>
+      <c r="S1" s="15" t="inlineStr">
+        <is>
+          <t>STAGING_MODEL_FOLDER</t>
+        </is>
+      </c>
+      <c r="T1" s="15" t="inlineStr">
+        <is>
+          <t>TARGET_MODEL_FOLDER</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -1270,6 +1686,35 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
+      <c r="L2" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M2" s="16" t="n"/>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>One row per employee.</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="inlineStr">
+        <is>
+          <t>Employee number</t>
+        </is>
+      </c>
+      <c r="Q2" s="16" t="n"/>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="16" t="n"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>marts/hr</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -1307,6 +1752,27 @@
       <c r="I3" s="16" t="n"/>
       <c r="J3" s="16" t="n"/>
       <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>Employee name, upper-cased</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>not_null</t>
+        </is>
+      </c>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -1352,6 +1818,35 @@
       <c r="I4" s="16" t="n"/>
       <c r="J4" s="16" t="n"/>
       <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>One row per department.</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>Department number</t>
+        </is>
+      </c>
+      <c r="Q4" s="16" t="n"/>
+      <c r="R4" s="16" t="n"/>
+      <c r="S4" s="16" t="n"/>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <t>marts/hr</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -1389,6 +1884,27 @@
       <c r="I5" s="16" t="n"/>
       <c r="J5" s="16" t="n"/>
       <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>Department name</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>accepted_values(ACCOUNTING|SALES|RESEARCH|OPERATIONS)</t>
+        </is>
+      </c>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -1442,6 +1958,39 @@
         </is>
       </c>
       <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>hr,daily</t>
+        </is>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>Employees joined to their department.</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>Employee number</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="inlineStr">
+        <is>
+          <t>marts/hr/reporting</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -1479,6 +2028,31 @@
       <c r="I7" s="16" t="n"/>
       <c r="J7" s="16" t="n"/>
       <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>Department number</t>
+        </is>
+      </c>
+      <c r="Q7" s="16" t="inlineStr">
+        <is>
+          <t>relationships(dept_target.deptno)</t>
+        </is>
+      </c>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="inlineStr">
+        <is>
+          <t>staging/hr/reference</t>
+        </is>
+      </c>
+      <c r="T7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -1516,6 +2090,23 @@
       <c r="I8" s="16" t="n"/>
       <c r="J8" s="16" t="n"/>
       <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t>Employee name</t>
+        </is>
+      </c>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -1538,7 +2129,11 @@
           <t>DNAME</t>
         </is>
       </c>
-      <c r="E9" s="16" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
           <t>emp_dept_target.sql</t>
@@ -1549,6 +2144,27 @@
       <c r="I9" s="16" t="n"/>
       <c r="J9" s="16" t="n"/>
       <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>Department name</t>
+        </is>
+      </c>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="inlineStr">
+        <is>
+          <t>staging/hr/reference</t>
+        </is>
+      </c>
+      <c r="T9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -1598,6 +2214,31 @@
           <t>emp.updated_at &gt; (select max(updated_at) from {{ this }})</t>
         </is>
       </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>hr,hourly</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>Incrementally loaded employee changes.</t>
+        </is>
+      </c>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t>Employee number</t>
+        </is>
+      </c>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="16" t="n"/>
+      <c r="T10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -1635,6 +2276,23 @@
       <c r="I11" s="16" t="n"/>
       <c r="J11" s="16" t="n"/>
       <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>Employee name</t>
+        </is>
+      </c>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="16" t="n"/>
+      <c r="T11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -1672,6 +2330,27 @@
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>Last change timestamp in source</t>
+        </is>
+      </c>
+      <c r="Q12" s="16" t="inlineStr">
+        <is>
+          <t>not_null</t>
+        </is>
+      </c>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
@@ -1685,6 +2364,15 @@
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
@@ -1698,6 +2386,15 @@
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -1711,6 +2408,15 @@
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -1724,6 +2430,15 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -1737,6 +2452,15 @@
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -1750,6 +2474,15 @@
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -1763,6 +2496,15 @@
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -1776,6 +2518,15 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -1789,6 +2540,15 @@
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -1802,6 +2562,15 @@
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="n"/>
+      <c r="S22" s="4" t="n"/>
+      <c r="T22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -1815,6 +2584,15 @@
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="n"/>
+      <c r="S23" s="4" t="n"/>
+      <c r="T23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -1828,6 +2606,15 @@
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -1841,6 +2628,15 @@
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="4" t="n"/>
+      <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -1854,6 +2650,15 @@
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -1867,6 +2672,15 @@
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="4" t="n"/>
+      <c r="S27" s="4" t="n"/>
+      <c r="T27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -1880,6 +2694,15 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -1893,6 +2716,15 @@
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="4" t="n"/>
+      <c r="R29" s="4" t="n"/>
+      <c r="S29" s="4" t="n"/>
+      <c r="T29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -1906,6 +2738,15 @@
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="4" t="n"/>
+      <c r="S30" s="4" t="n"/>
+      <c r="T30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -1919,6 +2760,15 @@
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="n"/>
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -1932,6 +2782,15 @@
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n"/>
+      <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -1945,6 +2804,15 @@
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+      <c r="R33" s="4" t="n"/>
+      <c r="S33" s="4" t="n"/>
+      <c r="T33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -1958,6 +2826,15 @@
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="n"/>
+      <c r="S34" s="4" t="n"/>
+      <c r="T34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -1971,6 +2848,15 @@
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="n"/>
+      <c r="T35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -1984,6 +2870,15 @@
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n"/>
+      <c r="S36" s="4" t="n"/>
+      <c r="T36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -1997,6 +2892,15 @@
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="n"/>
+      <c r="S37" s="4" t="n"/>
+      <c r="T37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -2010,6 +2914,15 @@
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n"/>
+      <c r="S38" s="4" t="n"/>
+      <c r="T38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -2023,6 +2936,15 @@
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n"/>
+      <c r="R39" s="4" t="n"/>
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -2036,6 +2958,15 @@
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n"/>
+      <c r="R40" s="4" t="n"/>
+      <c r="S40" s="4" t="n"/>
+      <c r="T40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -2049,6 +2980,15 @@
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
+      <c r="Q41" s="4" t="n"/>
+      <c r="R41" s="4" t="n"/>
+      <c r="S41" s="4" t="n"/>
+      <c r="T41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -2062,6 +3002,15 @@
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -2075,6 +3024,15 @@
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n"/>
+      <c r="R43" s="4" t="n"/>
+      <c r="S43" s="4" t="n"/>
+      <c r="T43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -2088,6 +3046,15 @@
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n"/>
+      <c r="R44" s="4" t="n"/>
+      <c r="S44" s="4" t="n"/>
+      <c r="T44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -2101,6 +3068,15 @@
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="4" t="n"/>
+      <c r="R45" s="4" t="n"/>
+      <c r="S45" s="4" t="n"/>
+      <c r="T45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -2114,6 +3090,15 @@
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="4" t="n"/>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -2127,6 +3112,15 @@
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n"/>
+      <c r="R47" s="4" t="n"/>
+      <c r="S47" s="4" t="n"/>
+      <c r="T47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -2140,6 +3134,15 @@
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -2153,6 +3156,15 @@
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="4" t="n"/>
+      <c r="R49" s="4" t="n"/>
+      <c r="S49" s="4" t="n"/>
+      <c r="T49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -2166,6 +3178,15 @@
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -2179,6 +3200,15 @@
       <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n"/>
+      <c r="R51" s="4" t="n"/>
+      <c r="S51" s="4" t="n"/>
+      <c r="T51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -2192,6 +3222,15 @@
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -2205,6 +3244,15 @@
       <c r="I53" s="4" t="n"/>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="4" t="n"/>
+      <c r="R53" s="4" t="n"/>
+      <c r="S53" s="4" t="n"/>
+      <c r="T53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -2218,6 +3266,15 @@
       <c r="I54" s="4" t="n"/>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="4" t="n"/>
+      <c r="R54" s="4" t="n"/>
+      <c r="S54" s="4" t="n"/>
+      <c r="T54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -2231,6 +3288,15 @@
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="4" t="n"/>
+      <c r="S55" s="4" t="n"/>
+      <c r="T55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -2244,6 +3310,15 @@
       <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -2257,6 +3332,15 @@
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="n"/>
+      <c r="S57" s="4" t="n"/>
+      <c r="T57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -2270,6 +3354,15 @@
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n"/>
+      <c r="S58" s="4" t="n"/>
+      <c r="T58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -2283,6 +3376,15 @@
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="4" t="n"/>
+      <c r="R59" s="4" t="n"/>
+      <c r="S59" s="4" t="n"/>
+      <c r="T59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
@@ -2296,6 +3398,15 @@
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="4" t="n"/>
+      <c r="S60" s="4" t="n"/>
+      <c r="T60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -2309,6 +3420,15 @@
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n"/>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n"/>
+      <c r="R61" s="4" t="n"/>
+      <c r="S61" s="4" t="n"/>
+      <c r="T61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
@@ -2322,6 +3442,15 @@
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="n"/>
+      <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="n"/>
+      <c r="T62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -2335,6 +3464,15 @@
       <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="4" t="n"/>
+      <c r="R63" s="4" t="n"/>
+      <c r="S63" s="4" t="n"/>
+      <c r="T63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
@@ -2348,6 +3486,15 @@
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="n"/>
+      <c r="P64" s="4" t="n"/>
+      <c r="Q64" s="4" t="n"/>
+      <c r="R64" s="4" t="n"/>
+      <c r="S64" s="4" t="n"/>
+      <c r="T64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -2361,6 +3508,15 @@
       <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="4" t="n"/>
+      <c r="R65" s="4" t="n"/>
+      <c r="S65" s="4" t="n"/>
+      <c r="T65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n"/>
@@ -2374,6 +3530,15 @@
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="4" t="n"/>
+      <c r="R66" s="4" t="n"/>
+      <c r="S66" s="4" t="n"/>
+      <c r="T66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -2387,6 +3552,15 @@
       <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="4" t="n"/>
+      <c r="S67" s="4" t="n"/>
+      <c r="T67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n"/>
@@ -2400,6 +3574,15 @@
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="4" t="n"/>
+      <c r="R68" s="4" t="n"/>
+      <c r="S68" s="4" t="n"/>
+      <c r="T68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -2413,6 +3596,15 @@
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="4" t="n"/>
+      <c r="R69" s="4" t="n"/>
+      <c r="S69" s="4" t="n"/>
+      <c r="T69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n"/>
@@ -2426,6 +3618,15 @@
       <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n"/>
+      <c r="S70" s="4" t="n"/>
+      <c r="T70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -2439,6 +3640,15 @@
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="4" t="n"/>
+      <c r="R71" s="4" t="n"/>
+      <c r="S71" s="4" t="n"/>
+      <c r="T71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n"/>
@@ -2452,6 +3662,15 @@
       <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
+      <c r="Q72" s="4" t="n"/>
+      <c r="R72" s="4" t="n"/>
+      <c r="S72" s="4" t="n"/>
+      <c r="T72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -2465,6 +3684,15 @@
       <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n"/>
+      <c r="R73" s="4" t="n"/>
+      <c r="S73" s="4" t="n"/>
+      <c r="T73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n"/>
@@ -2478,6 +3706,15 @@
       <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
+      <c r="Q74" s="4" t="n"/>
+      <c r="R74" s="4" t="n"/>
+      <c r="S74" s="4" t="n"/>
+      <c r="T74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -2491,6 +3728,15 @@
       <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="4" t="n"/>
+      <c r="R75" s="4" t="n"/>
+      <c r="S75" s="4" t="n"/>
+      <c r="T75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n"/>
@@ -2504,6 +3750,15 @@
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="4" t="n"/>
+      <c r="R76" s="4" t="n"/>
+      <c r="S76" s="4" t="n"/>
+      <c r="T76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -2517,6 +3772,15 @@
       <c r="I77" s="4" t="n"/>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
+      <c r="P77" s="4" t="n"/>
+      <c r="Q77" s="4" t="n"/>
+      <c r="R77" s="4" t="n"/>
+      <c r="S77" s="4" t="n"/>
+      <c r="T77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n"/>
@@ -2530,6 +3794,15 @@
       <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
+      <c r="Q78" s="4" t="n"/>
+      <c r="R78" s="4" t="n"/>
+      <c r="S78" s="4" t="n"/>
+      <c r="T78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -2543,6 +3816,15 @@
       <c r="I79" s="4" t="n"/>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n"/>
+      <c r="R79" s="4" t="n"/>
+      <c r="S79" s="4" t="n"/>
+      <c r="T79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n"/>
@@ -2556,6 +3838,15 @@
       <c r="I80" s="4" t="n"/>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="4" t="n"/>
+      <c r="R80" s="4" t="n"/>
+      <c r="S80" s="4" t="n"/>
+      <c r="T80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -2569,6 +3860,15 @@
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="4" t="n"/>
+      <c r="R81" s="4" t="n"/>
+      <c r="S81" s="4" t="n"/>
+      <c r="T81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n"/>
@@ -2582,6 +3882,15 @@
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
+      <c r="Q82" s="4" t="n"/>
+      <c r="R82" s="4" t="n"/>
+      <c r="S82" s="4" t="n"/>
+      <c r="T82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -2595,6 +3904,15 @@
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
+      <c r="Q83" s="4" t="n"/>
+      <c r="R83" s="4" t="n"/>
+      <c r="S83" s="4" t="n"/>
+      <c r="T83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
@@ -2608,6 +3926,15 @@
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n"/>
+      <c r="P84" s="4" t="n"/>
+      <c r="Q84" s="4" t="n"/>
+      <c r="R84" s="4" t="n"/>
+      <c r="S84" s="4" t="n"/>
+      <c r="T84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -2621,6 +3948,15 @@
       <c r="I85" s="4" t="n"/>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
+      <c r="Q85" s="4" t="n"/>
+      <c r="R85" s="4" t="n"/>
+      <c r="S85" s="4" t="n"/>
+      <c r="T85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>
@@ -2634,6 +3970,15 @@
       <c r="I86" s="4" t="n"/>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="n"/>
+      <c r="P86" s="4" t="n"/>
+      <c r="Q86" s="4" t="n"/>
+      <c r="R86" s="4" t="n"/>
+      <c r="S86" s="4" t="n"/>
+      <c r="T86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -2647,6 +3992,15 @@
       <c r="I87" s="4" t="n"/>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
+      <c r="L87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="n"/>
+      <c r="P87" s="4" t="n"/>
+      <c r="Q87" s="4" t="n"/>
+      <c r="R87" s="4" t="n"/>
+      <c r="S87" s="4" t="n"/>
+      <c r="T87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n"/>
@@ -2660,6 +4014,15 @@
       <c r="I88" s="4" t="n"/>
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="n"/>
+      <c r="P88" s="4" t="n"/>
+      <c r="Q88" s="4" t="n"/>
+      <c r="R88" s="4" t="n"/>
+      <c r="S88" s="4" t="n"/>
+      <c r="T88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -2673,6 +4036,15 @@
       <c r="I89" s="4" t="n"/>
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
+      <c r="Q89" s="4" t="n"/>
+      <c r="R89" s="4" t="n"/>
+      <c r="S89" s="4" t="n"/>
+      <c r="T89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
@@ -2686,6 +4058,15 @@
       <c r="I90" s="4" t="n"/>
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="n"/>
+      <c r="P90" s="4" t="n"/>
+      <c r="Q90" s="4" t="n"/>
+      <c r="R90" s="4" t="n"/>
+      <c r="S90" s="4" t="n"/>
+      <c r="T90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -2699,6 +4080,15 @@
       <c r="I91" s="4" t="n"/>
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
+      <c r="L91" s="4" t="n"/>
+      <c r="M91" s="4" t="n"/>
+      <c r="N91" s="4" t="n"/>
+      <c r="O91" s="4" t="n"/>
+      <c r="P91" s="4" t="n"/>
+      <c r="Q91" s="4" t="n"/>
+      <c r="R91" s="4" t="n"/>
+      <c r="S91" s="4" t="n"/>
+      <c r="T91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
@@ -2712,6 +4102,15 @@
       <c r="I92" s="4" t="n"/>
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="n"/>
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="4" t="n"/>
+      <c r="N92" s="4" t="n"/>
+      <c r="O92" s="4" t="n"/>
+      <c r="P92" s="4" t="n"/>
+      <c r="Q92" s="4" t="n"/>
+      <c r="R92" s="4" t="n"/>
+      <c r="S92" s="4" t="n"/>
+      <c r="T92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -2725,6 +4124,15 @@
       <c r="I93" s="4" t="n"/>
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
+      <c r="Q93" s="4" t="n"/>
+      <c r="R93" s="4" t="n"/>
+      <c r="S93" s="4" t="n"/>
+      <c r="T93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n"/>
@@ -2738,6 +4146,15 @@
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="n"/>
+      <c r="P94" s="4" t="n"/>
+      <c r="Q94" s="4" t="n"/>
+      <c r="R94" s="4" t="n"/>
+      <c r="S94" s="4" t="n"/>
+      <c r="T94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -2751,6 +4168,15 @@
       <c r="I95" s="4" t="n"/>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="n"/>
+      <c r="P95" s="4" t="n"/>
+      <c r="Q95" s="4" t="n"/>
+      <c r="R95" s="4" t="n"/>
+      <c r="S95" s="4" t="n"/>
+      <c r="T95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
@@ -2764,6 +4190,15 @@
       <c r="I96" s="4" t="n"/>
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="n"/>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="4" t="n"/>
+      <c r="N96" s="4" t="n"/>
+      <c r="O96" s="4" t="n"/>
+      <c r="P96" s="4" t="n"/>
+      <c r="Q96" s="4" t="n"/>
+      <c r="R96" s="4" t="n"/>
+      <c r="S96" s="4" t="n"/>
+      <c r="T96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -2777,6 +4212,15 @@
       <c r="I97" s="4" t="n"/>
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
+      <c r="Q97" s="4" t="n"/>
+      <c r="R97" s="4" t="n"/>
+      <c r="S97" s="4" t="n"/>
+      <c r="T97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
@@ -2790,6 +4234,15 @@
       <c r="I98" s="4" t="n"/>
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="n"/>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="4" t="n"/>
+      <c r="N98" s="4" t="n"/>
+      <c r="O98" s="4" t="n"/>
+      <c r="P98" s="4" t="n"/>
+      <c r="Q98" s="4" t="n"/>
+      <c r="R98" s="4" t="n"/>
+      <c r="S98" s="4" t="n"/>
+      <c r="T98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -2803,6 +4256,15 @@
       <c r="I99" s="4" t="n"/>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n"/>
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="4" t="n"/>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="n"/>
+      <c r="P99" s="4" t="n"/>
+      <c r="Q99" s="4" t="n"/>
+      <c r="R99" s="4" t="n"/>
+      <c r="S99" s="4" t="n"/>
+      <c r="T99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n"/>
@@ -2816,6 +4278,15 @@
       <c r="I100" s="4" t="n"/>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="n"/>
+      <c r="P100" s="4" t="n"/>
+      <c r="Q100" s="4" t="n"/>
+      <c r="R100" s="4" t="n"/>
+      <c r="S100" s="4" t="n"/>
+      <c r="T100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -2829,6 +4300,15 @@
       <c r="I101" s="4" t="n"/>
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="n"/>
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="4" t="n"/>
+      <c r="N101" s="4" t="n"/>
+      <c r="O101" s="4" t="n"/>
+      <c r="P101" s="4" t="n"/>
+      <c r="Q101" s="4" t="n"/>
+      <c r="R101" s="4" t="n"/>
+      <c r="S101" s="4" t="n"/>
+      <c r="T101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
@@ -2842,6 +4322,15 @@
       <c r="I102" s="4" t="n"/>
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="4" t="n"/>
+      <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="n"/>
+      <c r="P102" s="4" t="n"/>
+      <c r="Q102" s="4" t="n"/>
+      <c r="R102" s="4" t="n"/>
+      <c r="S102" s="4" t="n"/>
+      <c r="T102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -2855,6 +4344,15 @@
       <c r="I103" s="4" t="n"/>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
+      <c r="Q103" s="4" t="n"/>
+      <c r="R103" s="4" t="n"/>
+      <c r="S103" s="4" t="n"/>
+      <c r="T103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n"/>
@@ -2868,6 +4366,15 @@
       <c r="I104" s="4" t="n"/>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n"/>
+      <c r="L104" s="4" t="n"/>
+      <c r="M104" s="4" t="n"/>
+      <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
+      <c r="P104" s="4" t="n"/>
+      <c r="Q104" s="4" t="n"/>
+      <c r="R104" s="4" t="n"/>
+      <c r="S104" s="4" t="n"/>
+      <c r="T104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -2881,6 +4388,15 @@
       <c r="I105" s="4" t="n"/>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="n"/>
+      <c r="L105" s="4" t="n"/>
+      <c r="M105" s="4" t="n"/>
+      <c r="N105" s="4" t="n"/>
+      <c r="O105" s="4" t="n"/>
+      <c r="P105" s="4" t="n"/>
+      <c r="Q105" s="4" t="n"/>
+      <c r="R105" s="4" t="n"/>
+      <c r="S105" s="4" t="n"/>
+      <c r="T105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n"/>
@@ -2894,6 +4410,15 @@
       <c r="I106" s="4" t="n"/>
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="n"/>
+      <c r="L106" s="4" t="n"/>
+      <c r="M106" s="4" t="n"/>
+      <c r="N106" s="4" t="n"/>
+      <c r="O106" s="4" t="n"/>
+      <c r="P106" s="4" t="n"/>
+      <c r="Q106" s="4" t="n"/>
+      <c r="R106" s="4" t="n"/>
+      <c r="S106" s="4" t="n"/>
+      <c r="T106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -2907,6 +4432,15 @@
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
+      <c r="L107" s="4" t="n"/>
+      <c r="M107" s="4" t="n"/>
+      <c r="N107" s="4" t="n"/>
+      <c r="O107" s="4" t="n"/>
+      <c r="P107" s="4" t="n"/>
+      <c r="Q107" s="4" t="n"/>
+      <c r="R107" s="4" t="n"/>
+      <c r="S107" s="4" t="n"/>
+      <c r="T107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n"/>
@@ -2920,6 +4454,15 @@
       <c r="I108" s="4" t="n"/>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
+      <c r="L108" s="4" t="n"/>
+      <c r="M108" s="4" t="n"/>
+      <c r="N108" s="4" t="n"/>
+      <c r="O108" s="4" t="n"/>
+      <c r="P108" s="4" t="n"/>
+      <c r="Q108" s="4" t="n"/>
+      <c r="R108" s="4" t="n"/>
+      <c r="S108" s="4" t="n"/>
+      <c r="T108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -2933,6 +4476,15 @@
       <c r="I109" s="4" t="n"/>
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="n"/>
+      <c r="L109" s="4" t="n"/>
+      <c r="M109" s="4" t="n"/>
+      <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="n"/>
+      <c r="P109" s="4" t="n"/>
+      <c r="Q109" s="4" t="n"/>
+      <c r="R109" s="4" t="n"/>
+      <c r="S109" s="4" t="n"/>
+      <c r="T109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n"/>
@@ -2946,6 +4498,15 @@
       <c r="I110" s="4" t="n"/>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
+      <c r="L110" s="4" t="n"/>
+      <c r="M110" s="4" t="n"/>
+      <c r="N110" s="4" t="n"/>
+      <c r="O110" s="4" t="n"/>
+      <c r="P110" s="4" t="n"/>
+      <c r="Q110" s="4" t="n"/>
+      <c r="R110" s="4" t="n"/>
+      <c r="S110" s="4" t="n"/>
+      <c r="T110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -2959,6 +4520,15 @@
       <c r="I111" s="4" t="n"/>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
+      <c r="L111" s="4" t="n"/>
+      <c r="M111" s="4" t="n"/>
+      <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="n"/>
+      <c r="P111" s="4" t="n"/>
+      <c r="Q111" s="4" t="n"/>
+      <c r="R111" s="4" t="n"/>
+      <c r="S111" s="4" t="n"/>
+      <c r="T111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
@@ -2972,6 +4542,15 @@
       <c r="I112" s="4" t="n"/>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="n"/>
+      <c r="L112" s="4" t="n"/>
+      <c r="M112" s="4" t="n"/>
+      <c r="N112" s="4" t="n"/>
+      <c r="O112" s="4" t="n"/>
+      <c r="P112" s="4" t="n"/>
+      <c r="Q112" s="4" t="n"/>
+      <c r="R112" s="4" t="n"/>
+      <c r="S112" s="4" t="n"/>
+      <c r="T112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -2985,6 +4564,15 @@
       <c r="I113" s="4" t="n"/>
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="n"/>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
+      <c r="N113" s="4" t="n"/>
+      <c r="O113" s="4" t="n"/>
+      <c r="P113" s="4" t="n"/>
+      <c r="Q113" s="4" t="n"/>
+      <c r="R113" s="4" t="n"/>
+      <c r="S113" s="4" t="n"/>
+      <c r="T113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n"/>
@@ -2998,6 +4586,15 @@
       <c r="I114" s="4" t="n"/>
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
+      <c r="Q114" s="4" t="n"/>
+      <c r="R114" s="4" t="n"/>
+      <c r="S114" s="4" t="n"/>
+      <c r="T114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -3011,6 +4608,15 @@
       <c r="I115" s="4" t="n"/>
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
+      <c r="Q115" s="4" t="n"/>
+      <c r="R115" s="4" t="n"/>
+      <c r="S115" s="4" t="n"/>
+      <c r="T115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n"/>
@@ -3024,6 +4630,15 @@
       <c r="I116" s="4" t="n"/>
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
+      <c r="L116" s="4" t="n"/>
+      <c r="M116" s="4" t="n"/>
+      <c r="N116" s="4" t="n"/>
+      <c r="O116" s="4" t="n"/>
+      <c r="P116" s="4" t="n"/>
+      <c r="Q116" s="4" t="n"/>
+      <c r="R116" s="4" t="n"/>
+      <c r="S116" s="4" t="n"/>
+      <c r="T116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -3037,6 +4652,15 @@
       <c r="I117" s="4" t="n"/>
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="n"/>
+      <c r="M117" s="4" t="n"/>
+      <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="n"/>
+      <c r="P117" s="4" t="n"/>
+      <c r="Q117" s="4" t="n"/>
+      <c r="R117" s="4" t="n"/>
+      <c r="S117" s="4" t="n"/>
+      <c r="T117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n"/>
@@ -3050,6 +4674,15 @@
       <c r="I118" s="4" t="n"/>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="n"/>
+      <c r="M118" s="4" t="n"/>
+      <c r="N118" s="4" t="n"/>
+      <c r="O118" s="4" t="n"/>
+      <c r="P118" s="4" t="n"/>
+      <c r="Q118" s="4" t="n"/>
+      <c r="R118" s="4" t="n"/>
+      <c r="S118" s="4" t="n"/>
+      <c r="T118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -3063,6 +4696,15 @@
       <c r="I119" s="4" t="n"/>
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="n"/>
+      <c r="L119" s="4" t="n"/>
+      <c r="M119" s="4" t="n"/>
+      <c r="N119" s="4" t="n"/>
+      <c r="O119" s="4" t="n"/>
+      <c r="P119" s="4" t="n"/>
+      <c r="Q119" s="4" t="n"/>
+      <c r="R119" s="4" t="n"/>
+      <c r="S119" s="4" t="n"/>
+      <c r="T119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n"/>
@@ -3076,6 +4718,15 @@
       <c r="I120" s="4" t="n"/>
       <c r="J120" s="4" t="n"/>
       <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
+      <c r="Q120" s="4" t="n"/>
+      <c r="R120" s="4" t="n"/>
+      <c r="S120" s="4" t="n"/>
+      <c r="T120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -3089,6 +4740,15 @@
       <c r="I121" s="4" t="n"/>
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
+      <c r="O121" s="4" t="n"/>
+      <c r="P121" s="4" t="n"/>
+      <c r="Q121" s="4" t="n"/>
+      <c r="R121" s="4" t="n"/>
+      <c r="S121" s="4" t="n"/>
+      <c r="T121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n"/>
@@ -3102,6 +4762,15 @@
       <c r="I122" s="4" t="n"/>
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
+      <c r="O122" s="4" t="n"/>
+      <c r="P122" s="4" t="n"/>
+      <c r="Q122" s="4" t="n"/>
+      <c r="R122" s="4" t="n"/>
+      <c r="S122" s="4" t="n"/>
+      <c r="T122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -3115,6 +4784,15 @@
       <c r="I123" s="4" t="n"/>
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
+      <c r="L123" s="4" t="n"/>
+      <c r="M123" s="4" t="n"/>
+      <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
+      <c r="Q123" s="4" t="n"/>
+      <c r="R123" s="4" t="n"/>
+      <c r="S123" s="4" t="n"/>
+      <c r="T123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n"/>
@@ -3128,6 +4806,15 @@
       <c r="I124" s="4" t="n"/>
       <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
+      <c r="P124" s="4" t="n"/>
+      <c r="Q124" s="4" t="n"/>
+      <c r="R124" s="4" t="n"/>
+      <c r="S124" s="4" t="n"/>
+      <c r="T124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -3141,6 +4828,15 @@
       <c r="I125" s="4" t="n"/>
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
+      <c r="N125" s="4" t="n"/>
+      <c r="O125" s="4" t="n"/>
+      <c r="P125" s="4" t="n"/>
+      <c r="Q125" s="4" t="n"/>
+      <c r="R125" s="4" t="n"/>
+      <c r="S125" s="4" t="n"/>
+      <c r="T125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n"/>
@@ -3154,6 +4850,15 @@
       <c r="I126" s="4" t="n"/>
       <c r="J126" s="4" t="n"/>
       <c r="K126" s="4" t="n"/>
+      <c r="L126" s="4" t="n"/>
+      <c r="M126" s="4" t="n"/>
+      <c r="N126" s="4" t="n"/>
+      <c r="O126" s="4" t="n"/>
+      <c r="P126" s="4" t="n"/>
+      <c r="Q126" s="4" t="n"/>
+      <c r="R126" s="4" t="n"/>
+      <c r="S126" s="4" t="n"/>
+      <c r="T126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -3167,6 +4872,15 @@
       <c r="I127" s="4" t="n"/>
       <c r="J127" s="4" t="n"/>
       <c r="K127" s="4" t="n"/>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
+      <c r="N127" s="4" t="n"/>
+      <c r="O127" s="4" t="n"/>
+      <c r="P127" s="4" t="n"/>
+      <c r="Q127" s="4" t="n"/>
+      <c r="R127" s="4" t="n"/>
+      <c r="S127" s="4" t="n"/>
+      <c r="T127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n"/>
@@ -3180,6 +4894,15 @@
       <c r="I128" s="4" t="n"/>
       <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
+      <c r="L128" s="4" t="n"/>
+      <c r="M128" s="4" t="n"/>
+      <c r="N128" s="4" t="n"/>
+      <c r="O128" s="4" t="n"/>
+      <c r="P128" s="4" t="n"/>
+      <c r="Q128" s="4" t="n"/>
+      <c r="R128" s="4" t="n"/>
+      <c r="S128" s="4" t="n"/>
+      <c r="T128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -3193,6 +4916,15 @@
       <c r="I129" s="4" t="n"/>
       <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
+      <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
+      <c r="Q129" s="4" t="n"/>
+      <c r="R129" s="4" t="n"/>
+      <c r="S129" s="4" t="n"/>
+      <c r="T129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n"/>
@@ -3206,6 +4938,15 @@
       <c r="I130" s="4" t="n"/>
       <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
+      <c r="L130" s="4" t="n"/>
+      <c r="M130" s="4" t="n"/>
+      <c r="N130" s="4" t="n"/>
+      <c r="O130" s="4" t="n"/>
+      <c r="P130" s="4" t="n"/>
+      <c r="Q130" s="4" t="n"/>
+      <c r="R130" s="4" t="n"/>
+      <c r="S130" s="4" t="n"/>
+      <c r="T130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -3219,6 +4960,15 @@
       <c r="I131" s="4" t="n"/>
       <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
+      <c r="L131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
+      <c r="P131" s="4" t="n"/>
+      <c r="Q131" s="4" t="n"/>
+      <c r="R131" s="4" t="n"/>
+      <c r="S131" s="4" t="n"/>
+      <c r="T131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n"/>
@@ -3232,6 +4982,15 @@
       <c r="I132" s="4" t="n"/>
       <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
+      <c r="L132" s="4" t="n"/>
+      <c r="M132" s="4" t="n"/>
+      <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
+      <c r="P132" s="4" t="n"/>
+      <c r="Q132" s="4" t="n"/>
+      <c r="R132" s="4" t="n"/>
+      <c r="S132" s="4" t="n"/>
+      <c r="T132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -3245,6 +5004,15 @@
       <c r="I133" s="4" t="n"/>
       <c r="J133" s="4" t="n"/>
       <c r="K133" s="4" t="n"/>
+      <c r="L133" s="4" t="n"/>
+      <c r="M133" s="4" t="n"/>
+      <c r="N133" s="4" t="n"/>
+      <c r="O133" s="4" t="n"/>
+      <c r="P133" s="4" t="n"/>
+      <c r="Q133" s="4" t="n"/>
+      <c r="R133" s="4" t="n"/>
+      <c r="S133" s="4" t="n"/>
+      <c r="T133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n"/>
@@ -3258,6 +5026,15 @@
       <c r="I134" s="4" t="n"/>
       <c r="J134" s="4" t="n"/>
       <c r="K134" s="4" t="n"/>
+      <c r="L134" s="4" t="n"/>
+      <c r="M134" s="4" t="n"/>
+      <c r="N134" s="4" t="n"/>
+      <c r="O134" s="4" t="n"/>
+      <c r="P134" s="4" t="n"/>
+      <c r="Q134" s="4" t="n"/>
+      <c r="R134" s="4" t="n"/>
+      <c r="S134" s="4" t="n"/>
+      <c r="T134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -3271,6 +5048,15 @@
       <c r="I135" s="4" t="n"/>
       <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
+      <c r="Q135" s="4" t="n"/>
+      <c r="R135" s="4" t="n"/>
+      <c r="S135" s="4" t="n"/>
+      <c r="T135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n"/>
@@ -3284,6 +5070,15 @@
       <c r="I136" s="4" t="n"/>
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
+      <c r="M136" s="4" t="n"/>
+      <c r="N136" s="4" t="n"/>
+      <c r="O136" s="4" t="n"/>
+      <c r="P136" s="4" t="n"/>
+      <c r="Q136" s="4" t="n"/>
+      <c r="R136" s="4" t="n"/>
+      <c r="S136" s="4" t="n"/>
+      <c r="T136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -3297,6 +5092,15 @@
       <c r="I137" s="4" t="n"/>
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
+      <c r="Q137" s="4" t="n"/>
+      <c r="R137" s="4" t="n"/>
+      <c r="S137" s="4" t="n"/>
+      <c r="T137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n"/>
@@ -3310,6 +5114,15 @@
       <c r="I138" s="4" t="n"/>
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
+      <c r="L138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
+      <c r="N138" s="4" t="n"/>
+      <c r="O138" s="4" t="n"/>
+      <c r="P138" s="4" t="n"/>
+      <c r="Q138" s="4" t="n"/>
+      <c r="R138" s="4" t="n"/>
+      <c r="S138" s="4" t="n"/>
+      <c r="T138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -3323,6 +5136,15 @@
       <c r="I139" s="4" t="n"/>
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
+      <c r="L139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
+      <c r="P139" s="4" t="n"/>
+      <c r="Q139" s="4" t="n"/>
+      <c r="R139" s="4" t="n"/>
+      <c r="S139" s="4" t="n"/>
+      <c r="T139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n"/>
@@ -3336,6 +5158,15 @@
       <c r="I140" s="4" t="n"/>
       <c r="J140" s="4" t="n"/>
       <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
+      <c r="Q140" s="4" t="n"/>
+      <c r="R140" s="4" t="n"/>
+      <c r="S140" s="4" t="n"/>
+      <c r="T140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -3349,6 +5180,15 @@
       <c r="I141" s="4" t="n"/>
       <c r="J141" s="4" t="n"/>
       <c r="K141" s="4" t="n"/>
+      <c r="L141" s="4" t="n"/>
+      <c r="M141" s="4" t="n"/>
+      <c r="N141" s="4" t="n"/>
+      <c r="O141" s="4" t="n"/>
+      <c r="P141" s="4" t="n"/>
+      <c r="Q141" s="4" t="n"/>
+      <c r="R141" s="4" t="n"/>
+      <c r="S141" s="4" t="n"/>
+      <c r="T141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n"/>
@@ -3362,6 +5202,15 @@
       <c r="I142" s="4" t="n"/>
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
+      <c r="N142" s="4" t="n"/>
+      <c r="O142" s="4" t="n"/>
+      <c r="P142" s="4" t="n"/>
+      <c r="Q142" s="4" t="n"/>
+      <c r="R142" s="4" t="n"/>
+      <c r="S142" s="4" t="n"/>
+      <c r="T142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -3375,6 +5224,15 @@
       <c r="I143" s="4" t="n"/>
       <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
+      <c r="L143" s="4" t="n"/>
+      <c r="M143" s="4" t="n"/>
+      <c r="N143" s="4" t="n"/>
+      <c r="O143" s="4" t="n"/>
+      <c r="P143" s="4" t="n"/>
+      <c r="Q143" s="4" t="n"/>
+      <c r="R143" s="4" t="n"/>
+      <c r="S143" s="4" t="n"/>
+      <c r="T143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
@@ -3388,6 +5246,15 @@
       <c r="I144" s="4" t="n"/>
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="n"/>
+      <c r="L144" s="4" t="n"/>
+      <c r="M144" s="4" t="n"/>
+      <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
+      <c r="P144" s="4" t="n"/>
+      <c r="Q144" s="4" t="n"/>
+      <c r="R144" s="4" t="n"/>
+      <c r="S144" s="4" t="n"/>
+      <c r="T144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -3401,6 +5268,15 @@
       <c r="I145" s="4" t="n"/>
       <c r="J145" s="4" t="n"/>
       <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="n"/>
+      <c r="Q145" s="4" t="n"/>
+      <c r="R145" s="4" t="n"/>
+      <c r="S145" s="4" t="n"/>
+      <c r="T145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
@@ -3414,6 +5290,15 @@
       <c r="I146" s="4" t="n"/>
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
+      <c r="Q146" s="4" t="n"/>
+      <c r="R146" s="4" t="n"/>
+      <c r="S146" s="4" t="n"/>
+      <c r="T146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -3427,6 +5312,15 @@
       <c r="I147" s="4" t="n"/>
       <c r="J147" s="4" t="n"/>
       <c r="K147" s="4" t="n"/>
+      <c r="L147" s="4" t="n"/>
+      <c r="M147" s="4" t="n"/>
+      <c r="N147" s="4" t="n"/>
+      <c r="O147" s="4" t="n"/>
+      <c r="P147" s="4" t="n"/>
+      <c r="Q147" s="4" t="n"/>
+      <c r="R147" s="4" t="n"/>
+      <c r="S147" s="4" t="n"/>
+      <c r="T147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n"/>
@@ -3440,6 +5334,15 @@
       <c r="I148" s="4" t="n"/>
       <c r="J148" s="4" t="n"/>
       <c r="K148" s="4" t="n"/>
+      <c r="L148" s="4" t="n"/>
+      <c r="M148" s="4" t="n"/>
+      <c r="N148" s="4" t="n"/>
+      <c r="O148" s="4" t="n"/>
+      <c r="P148" s="4" t="n"/>
+      <c r="Q148" s="4" t="n"/>
+      <c r="R148" s="4" t="n"/>
+      <c r="S148" s="4" t="n"/>
+      <c r="T148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -3453,6 +5356,15 @@
       <c r="I149" s="4" t="n"/>
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
+      <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
+      <c r="Q149" s="4" t="n"/>
+      <c r="R149" s="4" t="n"/>
+      <c r="S149" s="4" t="n"/>
+      <c r="T149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n"/>
@@ -3466,6 +5378,15 @@
       <c r="I150" s="4" t="n"/>
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
+      <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
+      <c r="Q150" s="4" t="n"/>
+      <c r="R150" s="4" t="n"/>
+      <c r="S150" s="4" t="n"/>
+      <c r="T150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -3479,6 +5400,15 @@
       <c r="I151" s="4" t="n"/>
       <c r="J151" s="4" t="n"/>
       <c r="K151" s="4" t="n"/>
+      <c r="L151" s="4" t="n"/>
+      <c r="M151" s="4" t="n"/>
+      <c r="N151" s="4" t="n"/>
+      <c r="O151" s="4" t="n"/>
+      <c r="P151" s="4" t="n"/>
+      <c r="Q151" s="4" t="n"/>
+      <c r="R151" s="4" t="n"/>
+      <c r="S151" s="4" t="n"/>
+      <c r="T151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
@@ -3492,6 +5422,15 @@
       <c r="I152" s="4" t="n"/>
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n"/>
+      <c r="L152" s="4" t="n"/>
+      <c r="M152" s="4" t="n"/>
+      <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
+      <c r="P152" s="4" t="n"/>
+      <c r="Q152" s="4" t="n"/>
+      <c r="R152" s="4" t="n"/>
+      <c r="S152" s="4" t="n"/>
+      <c r="T152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -3505,6 +5444,15 @@
       <c r="I153" s="4" t="n"/>
       <c r="J153" s="4" t="n"/>
       <c r="K153" s="4" t="n"/>
+      <c r="L153" s="4" t="n"/>
+      <c r="M153" s="4" t="n"/>
+      <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
+      <c r="P153" s="4" t="n"/>
+      <c r="Q153" s="4" t="n"/>
+      <c r="R153" s="4" t="n"/>
+      <c r="S153" s="4" t="n"/>
+      <c r="T153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
@@ -3518,6 +5466,15 @@
       <c r="I154" s="4" t="n"/>
       <c r="J154" s="4" t="n"/>
       <c r="K154" s="4" t="n"/>
+      <c r="L154" s="4" t="n"/>
+      <c r="M154" s="4" t="n"/>
+      <c r="N154" s="4" t="n"/>
+      <c r="O154" s="4" t="n"/>
+      <c r="P154" s="4" t="n"/>
+      <c r="Q154" s="4" t="n"/>
+      <c r="R154" s="4" t="n"/>
+      <c r="S154" s="4" t="n"/>
+      <c r="T154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -3531,6 +5488,15 @@
       <c r="I155" s="4" t="n"/>
       <c r="J155" s="4" t="n"/>
       <c r="K155" s="4" t="n"/>
+      <c r="L155" s="4" t="n"/>
+      <c r="M155" s="4" t="n"/>
+      <c r="N155" s="4" t="n"/>
+      <c r="O155" s="4" t="n"/>
+      <c r="P155" s="4" t="n"/>
+      <c r="Q155" s="4" t="n"/>
+      <c r="R155" s="4" t="n"/>
+      <c r="S155" s="4" t="n"/>
+      <c r="T155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
@@ -3544,6 +5510,15 @@
       <c r="I156" s="4" t="n"/>
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
+      <c r="L156" s="4" t="n"/>
+      <c r="M156" s="4" t="n"/>
+      <c r="N156" s="4" t="n"/>
+      <c r="O156" s="4" t="n"/>
+      <c r="P156" s="4" t="n"/>
+      <c r="Q156" s="4" t="n"/>
+      <c r="R156" s="4" t="n"/>
+      <c r="S156" s="4" t="n"/>
+      <c r="T156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -3557,6 +5532,15 @@
       <c r="I157" s="4" t="n"/>
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
+      <c r="L157" s="4" t="n"/>
+      <c r="M157" s="4" t="n"/>
+      <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
+      <c r="P157" s="4" t="n"/>
+      <c r="Q157" s="4" t="n"/>
+      <c r="R157" s="4" t="n"/>
+      <c r="S157" s="4" t="n"/>
+      <c r="T157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -3570,6 +5554,15 @@
       <c r="I158" s="4" t="n"/>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
+      <c r="L158" s="4" t="n"/>
+      <c r="M158" s="4" t="n"/>
+      <c r="N158" s="4" t="n"/>
+      <c r="O158" s="4" t="n"/>
+      <c r="P158" s="4" t="n"/>
+      <c r="Q158" s="4" t="n"/>
+      <c r="R158" s="4" t="n"/>
+      <c r="S158" s="4" t="n"/>
+      <c r="T158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -3583,6 +5576,15 @@
       <c r="I159" s="4" t="n"/>
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
+      <c r="L159" s="4" t="n"/>
+      <c r="M159" s="4" t="n"/>
+      <c r="N159" s="4" t="n"/>
+      <c r="O159" s="4" t="n"/>
+      <c r="P159" s="4" t="n"/>
+      <c r="Q159" s="4" t="n"/>
+      <c r="R159" s="4" t="n"/>
+      <c r="S159" s="4" t="n"/>
+      <c r="T159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n"/>
@@ -3596,6 +5598,15 @@
       <c r="I160" s="4" t="n"/>
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="n"/>
+      <c r="Q160" s="4" t="n"/>
+      <c r="R160" s="4" t="n"/>
+      <c r="S160" s="4" t="n"/>
+      <c r="T160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -3609,6 +5620,15 @@
       <c r="I161" s="4" t="n"/>
       <c r="J161" s="4" t="n"/>
       <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
+      <c r="Q161" s="4" t="n"/>
+      <c r="R161" s="4" t="n"/>
+      <c r="S161" s="4" t="n"/>
+      <c r="T161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
@@ -3622,6 +5642,15 @@
       <c r="I162" s="4" t="n"/>
       <c r="J162" s="4" t="n"/>
       <c r="K162" s="4" t="n"/>
+      <c r="L162" s="4" t="n"/>
+      <c r="M162" s="4" t="n"/>
+      <c r="N162" s="4" t="n"/>
+      <c r="O162" s="4" t="n"/>
+      <c r="P162" s="4" t="n"/>
+      <c r="Q162" s="4" t="n"/>
+      <c r="R162" s="4" t="n"/>
+      <c r="S162" s="4" t="n"/>
+      <c r="T162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -3635,6 +5664,15 @@
       <c r="I163" s="4" t="n"/>
       <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
+      <c r="L163" s="4" t="n"/>
+      <c r="M163" s="4" t="n"/>
+      <c r="N163" s="4" t="n"/>
+      <c r="O163" s="4" t="n"/>
+      <c r="P163" s="4" t="n"/>
+      <c r="Q163" s="4" t="n"/>
+      <c r="R163" s="4" t="n"/>
+      <c r="S163" s="4" t="n"/>
+      <c r="T163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -3648,6 +5686,15 @@
       <c r="I164" s="4" t="n"/>
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
+      <c r="L164" s="4" t="n"/>
+      <c r="M164" s="4" t="n"/>
+      <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
+      <c r="P164" s="4" t="n"/>
+      <c r="Q164" s="4" t="n"/>
+      <c r="R164" s="4" t="n"/>
+      <c r="S164" s="4" t="n"/>
+      <c r="T164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -3661,6 +5708,15 @@
       <c r="I165" s="4" t="n"/>
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
+      <c r="L165" s="4" t="n"/>
+      <c r="M165" s="4" t="n"/>
+      <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
+      <c r="P165" s="4" t="n"/>
+      <c r="Q165" s="4" t="n"/>
+      <c r="R165" s="4" t="n"/>
+      <c r="S165" s="4" t="n"/>
+      <c r="T165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n"/>
@@ -3674,6 +5730,15 @@
       <c r="I166" s="4" t="n"/>
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
+      <c r="L166" s="4" t="n"/>
+      <c r="M166" s="4" t="n"/>
+      <c r="N166" s="4" t="n"/>
+      <c r="O166" s="4" t="n"/>
+      <c r="P166" s="4" t="n"/>
+      <c r="Q166" s="4" t="n"/>
+      <c r="R166" s="4" t="n"/>
+      <c r="S166" s="4" t="n"/>
+      <c r="T166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -3687,6 +5752,15 @@
       <c r="I167" s="4" t="n"/>
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
+      <c r="L167" s="4" t="n"/>
+      <c r="M167" s="4" t="n"/>
+      <c r="N167" s="4" t="n"/>
+      <c r="O167" s="4" t="n"/>
+      <c r="P167" s="4" t="n"/>
+      <c r="Q167" s="4" t="n"/>
+      <c r="R167" s="4" t="n"/>
+      <c r="S167" s="4" t="n"/>
+      <c r="T167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
@@ -3700,6 +5774,15 @@
       <c r="I168" s="4" t="n"/>
       <c r="J168" s="4" t="n"/>
       <c r="K168" s="4" t="n"/>
+      <c r="L168" s="4" t="n"/>
+      <c r="M168" s="4" t="n"/>
+      <c r="N168" s="4" t="n"/>
+      <c r="O168" s="4" t="n"/>
+      <c r="P168" s="4" t="n"/>
+      <c r="Q168" s="4" t="n"/>
+      <c r="R168" s="4" t="n"/>
+      <c r="S168" s="4" t="n"/>
+      <c r="T168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -3713,6 +5796,15 @@
       <c r="I169" s="4" t="n"/>
       <c r="J169" s="4" t="n"/>
       <c r="K169" s="4" t="n"/>
+      <c r="L169" s="4" t="n"/>
+      <c r="M169" s="4" t="n"/>
+      <c r="N169" s="4" t="n"/>
+      <c r="O169" s="4" t="n"/>
+      <c r="P169" s="4" t="n"/>
+      <c r="Q169" s="4" t="n"/>
+      <c r="R169" s="4" t="n"/>
+      <c r="S169" s="4" t="n"/>
+      <c r="T169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
@@ -3726,6 +5818,15 @@
       <c r="I170" s="4" t="n"/>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
+      <c r="L170" s="4" t="n"/>
+      <c r="M170" s="4" t="n"/>
+      <c r="N170" s="4" t="n"/>
+      <c r="O170" s="4" t="n"/>
+      <c r="P170" s="4" t="n"/>
+      <c r="Q170" s="4" t="n"/>
+      <c r="R170" s="4" t="n"/>
+      <c r="S170" s="4" t="n"/>
+      <c r="T170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -3739,6 +5840,15 @@
       <c r="I171" s="4" t="n"/>
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
+      <c r="L171" s="4" t="n"/>
+      <c r="M171" s="4" t="n"/>
+      <c r="N171" s="4" t="n"/>
+      <c r="O171" s="4" t="n"/>
+      <c r="P171" s="4" t="n"/>
+      <c r="Q171" s="4" t="n"/>
+      <c r="R171" s="4" t="n"/>
+      <c r="S171" s="4" t="n"/>
+      <c r="T171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n"/>
@@ -3752,6 +5862,15 @@
       <c r="I172" s="4" t="n"/>
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
+      <c r="L172" s="4" t="n"/>
+      <c r="M172" s="4" t="n"/>
+      <c r="N172" s="4" t="n"/>
+      <c r="O172" s="4" t="n"/>
+      <c r="P172" s="4" t="n"/>
+      <c r="Q172" s="4" t="n"/>
+      <c r="R172" s="4" t="n"/>
+      <c r="S172" s="4" t="n"/>
+      <c r="T172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -3765,6 +5884,15 @@
       <c r="I173" s="4" t="n"/>
       <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
+      <c r="L173" s="4" t="n"/>
+      <c r="M173" s="4" t="n"/>
+      <c r="N173" s="4" t="n"/>
+      <c r="O173" s="4" t="n"/>
+      <c r="P173" s="4" t="n"/>
+      <c r="Q173" s="4" t="n"/>
+      <c r="R173" s="4" t="n"/>
+      <c r="S173" s="4" t="n"/>
+      <c r="T173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n"/>
@@ -3778,6 +5906,15 @@
       <c r="I174" s="4" t="n"/>
       <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
+      <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
+      <c r="Q174" s="4" t="n"/>
+      <c r="R174" s="4" t="n"/>
+      <c r="S174" s="4" t="n"/>
+      <c r="T174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -3791,6 +5928,15 @@
       <c r="I175" s="4" t="n"/>
       <c r="J175" s="4" t="n"/>
       <c r="K175" s="4" t="n"/>
+      <c r="L175" s="4" t="n"/>
+      <c r="M175" s="4" t="n"/>
+      <c r="N175" s="4" t="n"/>
+      <c r="O175" s="4" t="n"/>
+      <c r="P175" s="4" t="n"/>
+      <c r="Q175" s="4" t="n"/>
+      <c r="R175" s="4" t="n"/>
+      <c r="S175" s="4" t="n"/>
+      <c r="T175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -3804,6 +5950,15 @@
       <c r="I176" s="4" t="n"/>
       <c r="J176" s="4" t="n"/>
       <c r="K176" s="4" t="n"/>
+      <c r="L176" s="4" t="n"/>
+      <c r="M176" s="4" t="n"/>
+      <c r="N176" s="4" t="n"/>
+      <c r="O176" s="4" t="n"/>
+      <c r="P176" s="4" t="n"/>
+      <c r="Q176" s="4" t="n"/>
+      <c r="R176" s="4" t="n"/>
+      <c r="S176" s="4" t="n"/>
+      <c r="T176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -3817,6 +5972,15 @@
       <c r="I177" s="4" t="n"/>
       <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
+      <c r="L177" s="4" t="n"/>
+      <c r="M177" s="4" t="n"/>
+      <c r="N177" s="4" t="n"/>
+      <c r="O177" s="4" t="n"/>
+      <c r="P177" s="4" t="n"/>
+      <c r="Q177" s="4" t="n"/>
+      <c r="R177" s="4" t="n"/>
+      <c r="S177" s="4" t="n"/>
+      <c r="T177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n"/>
@@ -3830,6 +5994,15 @@
       <c r="I178" s="4" t="n"/>
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
+      <c r="L178" s="4" t="n"/>
+      <c r="M178" s="4" t="n"/>
+      <c r="N178" s="4" t="n"/>
+      <c r="O178" s="4" t="n"/>
+      <c r="P178" s="4" t="n"/>
+      <c r="Q178" s="4" t="n"/>
+      <c r="R178" s="4" t="n"/>
+      <c r="S178" s="4" t="n"/>
+      <c r="T178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -3843,6 +6016,15 @@
       <c r="I179" s="4" t="n"/>
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
+      <c r="P179" s="4" t="n"/>
+      <c r="Q179" s="4" t="n"/>
+      <c r="R179" s="4" t="n"/>
+      <c r="S179" s="4" t="n"/>
+      <c r="T179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n"/>
@@ -3856,6 +6038,15 @@
       <c r="I180" s="4" t="n"/>
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
+      <c r="L180" s="4" t="n"/>
+      <c r="M180" s="4" t="n"/>
+      <c r="N180" s="4" t="n"/>
+      <c r="O180" s="4" t="n"/>
+      <c r="P180" s="4" t="n"/>
+      <c r="Q180" s="4" t="n"/>
+      <c r="R180" s="4" t="n"/>
+      <c r="S180" s="4" t="n"/>
+      <c r="T180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -3869,6 +6060,15 @@
       <c r="I181" s="4" t="n"/>
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
+      <c r="Q181" s="4" t="n"/>
+      <c r="R181" s="4" t="n"/>
+      <c r="S181" s="4" t="n"/>
+      <c r="T181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -3882,6 +6082,15 @@
       <c r="I182" s="4" t="n"/>
       <c r="J182" s="4" t="n"/>
       <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="n"/>
+      <c r="M182" s="4" t="n"/>
+      <c r="N182" s="4" t="n"/>
+      <c r="O182" s="4" t="n"/>
+      <c r="P182" s="4" t="n"/>
+      <c r="Q182" s="4" t="n"/>
+      <c r="R182" s="4" t="n"/>
+      <c r="S182" s="4" t="n"/>
+      <c r="T182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -3895,6 +6104,15 @@
       <c r="I183" s="4" t="n"/>
       <c r="J183" s="4" t="n"/>
       <c r="K183" s="4" t="n"/>
+      <c r="L183" s="4" t="n"/>
+      <c r="M183" s="4" t="n"/>
+      <c r="N183" s="4" t="n"/>
+      <c r="O183" s="4" t="n"/>
+      <c r="P183" s="4" t="n"/>
+      <c r="Q183" s="4" t="n"/>
+      <c r="R183" s="4" t="n"/>
+      <c r="S183" s="4" t="n"/>
+      <c r="T183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -3908,6 +6126,15 @@
       <c r="I184" s="4" t="n"/>
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
+      <c r="L184" s="4" t="n"/>
+      <c r="M184" s="4" t="n"/>
+      <c r="N184" s="4" t="n"/>
+      <c r="O184" s="4" t="n"/>
+      <c r="P184" s="4" t="n"/>
+      <c r="Q184" s="4" t="n"/>
+      <c r="R184" s="4" t="n"/>
+      <c r="S184" s="4" t="n"/>
+      <c r="T184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -3921,6 +6148,15 @@
       <c r="I185" s="4" t="n"/>
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
+      <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
+      <c r="P185" s="4" t="n"/>
+      <c r="Q185" s="4" t="n"/>
+      <c r="R185" s="4" t="n"/>
+      <c r="S185" s="4" t="n"/>
+      <c r="T185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n"/>
@@ -3934,6 +6170,15 @@
       <c r="I186" s="4" t="n"/>
       <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
+      <c r="L186" s="4" t="n"/>
+      <c r="M186" s="4" t="n"/>
+      <c r="N186" s="4" t="n"/>
+      <c r="O186" s="4" t="n"/>
+      <c r="P186" s="4" t="n"/>
+      <c r="Q186" s="4" t="n"/>
+      <c r="R186" s="4" t="n"/>
+      <c r="S186" s="4" t="n"/>
+      <c r="T186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -3947,6 +6192,15 @@
       <c r="I187" s="4" t="n"/>
       <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
+      <c r="P187" s="4" t="n"/>
+      <c r="Q187" s="4" t="n"/>
+      <c r="R187" s="4" t="n"/>
+      <c r="S187" s="4" t="n"/>
+      <c r="T187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -3960,6 +6214,15 @@
       <c r="I188" s="4" t="n"/>
       <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
+      <c r="L188" s="4" t="n"/>
+      <c r="M188" s="4" t="n"/>
+      <c r="N188" s="4" t="n"/>
+      <c r="O188" s="4" t="n"/>
+      <c r="P188" s="4" t="n"/>
+      <c r="Q188" s="4" t="n"/>
+      <c r="R188" s="4" t="n"/>
+      <c r="S188" s="4" t="n"/>
+      <c r="T188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -3973,6 +6236,15 @@
       <c r="I189" s="4" t="n"/>
       <c r="J189" s="4" t="n"/>
       <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="n"/>
+      <c r="M189" s="4" t="n"/>
+      <c r="N189" s="4" t="n"/>
+      <c r="O189" s="4" t="n"/>
+      <c r="P189" s="4" t="n"/>
+      <c r="Q189" s="4" t="n"/>
+      <c r="R189" s="4" t="n"/>
+      <c r="S189" s="4" t="n"/>
+      <c r="T189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n"/>
@@ -3986,6 +6258,15 @@
       <c r="I190" s="4" t="n"/>
       <c r="J190" s="4" t="n"/>
       <c r="K190" s="4" t="n"/>
+      <c r="L190" s="4" t="n"/>
+      <c r="M190" s="4" t="n"/>
+      <c r="N190" s="4" t="n"/>
+      <c r="O190" s="4" t="n"/>
+      <c r="P190" s="4" t="n"/>
+      <c r="Q190" s="4" t="n"/>
+      <c r="R190" s="4" t="n"/>
+      <c r="S190" s="4" t="n"/>
+      <c r="T190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -3999,6 +6280,15 @@
       <c r="I191" s="4" t="n"/>
       <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
+      <c r="P191" s="4" t="n"/>
+      <c r="Q191" s="4" t="n"/>
+      <c r="R191" s="4" t="n"/>
+      <c r="S191" s="4" t="n"/>
+      <c r="T191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -4012,6 +6302,15 @@
       <c r="I192" s="4" t="n"/>
       <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
+      <c r="L192" s="4" t="n"/>
+      <c r="M192" s="4" t="n"/>
+      <c r="N192" s="4" t="n"/>
+      <c r="O192" s="4" t="n"/>
+      <c r="P192" s="4" t="n"/>
+      <c r="Q192" s="4" t="n"/>
+      <c r="R192" s="4" t="n"/>
+      <c r="S192" s="4" t="n"/>
+      <c r="T192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -4025,6 +6324,15 @@
       <c r="I193" s="4" t="n"/>
       <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="n"/>
+      <c r="M193" s="4" t="n"/>
+      <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
+      <c r="P193" s="4" t="n"/>
+      <c r="Q193" s="4" t="n"/>
+      <c r="R193" s="4" t="n"/>
+      <c r="S193" s="4" t="n"/>
+      <c r="T193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n"/>
@@ -4038,6 +6346,15 @@
       <c r="I194" s="4" t="n"/>
       <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
+      <c r="L194" s="4" t="n"/>
+      <c r="M194" s="4" t="n"/>
+      <c r="N194" s="4" t="n"/>
+      <c r="O194" s="4" t="n"/>
+      <c r="P194" s="4" t="n"/>
+      <c r="Q194" s="4" t="n"/>
+      <c r="R194" s="4" t="n"/>
+      <c r="S194" s="4" t="n"/>
+      <c r="T194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -4051,6 +6368,15 @@
       <c r="I195" s="4" t="n"/>
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
+      <c r="P195" s="4" t="n"/>
+      <c r="Q195" s="4" t="n"/>
+      <c r="R195" s="4" t="n"/>
+      <c r="S195" s="4" t="n"/>
+      <c r="T195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n"/>
@@ -4064,6 +6390,15 @@
       <c r="I196" s="4" t="n"/>
       <c r="J196" s="4" t="n"/>
       <c r="K196" s="4" t="n"/>
+      <c r="L196" s="4" t="n"/>
+      <c r="M196" s="4" t="n"/>
+      <c r="N196" s="4" t="n"/>
+      <c r="O196" s="4" t="n"/>
+      <c r="P196" s="4" t="n"/>
+      <c r="Q196" s="4" t="n"/>
+      <c r="R196" s="4" t="n"/>
+      <c r="S196" s="4" t="n"/>
+      <c r="T196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -4077,6 +6412,15 @@
       <c r="I197" s="4" t="n"/>
       <c r="J197" s="4" t="n"/>
       <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="n"/>
+      <c r="M197" s="4" t="n"/>
+      <c r="N197" s="4" t="n"/>
+      <c r="O197" s="4" t="n"/>
+      <c r="P197" s="4" t="n"/>
+      <c r="Q197" s="4" t="n"/>
+      <c r="R197" s="4" t="n"/>
+      <c r="S197" s="4" t="n"/>
+      <c r="T197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -4090,6 +6434,15 @@
       <c r="I198" s="4" t="n"/>
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="n"/>
+      <c r="M198" s="4" t="n"/>
+      <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
+      <c r="P198" s="4" t="n"/>
+      <c r="Q198" s="4" t="n"/>
+      <c r="R198" s="4" t="n"/>
+      <c r="S198" s="4" t="n"/>
+      <c r="T198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -4103,6 +6456,15 @@
       <c r="I199" s="4" t="n"/>
       <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
+      <c r="L199" s="4" t="n"/>
+      <c r="M199" s="4" t="n"/>
+      <c r="N199" s="4" t="n"/>
+      <c r="O199" s="4" t="n"/>
+      <c r="P199" s="4" t="n"/>
+      <c r="Q199" s="4" t="n"/>
+      <c r="R199" s="4" t="n"/>
+      <c r="S199" s="4" t="n"/>
+      <c r="T199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n"/>
@@ -4116,6 +6478,15 @@
       <c r="I200" s="4" t="n"/>
       <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
+      <c r="L200" s="4" t="n"/>
+      <c r="M200" s="4" t="n"/>
+      <c r="N200" s="4" t="n"/>
+      <c r="O200" s="4" t="n"/>
+      <c r="P200" s="4" t="n"/>
+      <c r="Q200" s="4" t="n"/>
+      <c r="R200" s="4" t="n"/>
+      <c r="S200" s="4" t="n"/>
+      <c r="T200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -4129,6 +6500,15 @@
       <c r="I201" s="4" t="n"/>
       <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
+      <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
+      <c r="P201" s="4" t="n"/>
+      <c r="Q201" s="4" t="n"/>
+      <c r="R201" s="4" t="n"/>
+      <c r="S201" s="4" t="n"/>
+      <c r="T201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -4142,6 +6522,15 @@
       <c r="I202" s="4" t="n"/>
       <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
+      <c r="L202" s="4" t="n"/>
+      <c r="M202" s="4" t="n"/>
+      <c r="N202" s="4" t="n"/>
+      <c r="O202" s="4" t="n"/>
+      <c r="P202" s="4" t="n"/>
+      <c r="Q202" s="4" t="n"/>
+      <c r="R202" s="4" t="n"/>
+      <c r="S202" s="4" t="n"/>
+      <c r="T202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -4155,6 +6544,15 @@
       <c r="I203" s="4" t="n"/>
       <c r="J203" s="4" t="n"/>
       <c r="K203" s="4" t="n"/>
+      <c r="L203" s="4" t="n"/>
+      <c r="M203" s="4" t="n"/>
+      <c r="N203" s="4" t="n"/>
+      <c r="O203" s="4" t="n"/>
+      <c r="P203" s="4" t="n"/>
+      <c r="Q203" s="4" t="n"/>
+      <c r="R203" s="4" t="n"/>
+      <c r="S203" s="4" t="n"/>
+      <c r="T203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n"/>
@@ -4168,6 +6566,15 @@
       <c r="I204" s="4" t="n"/>
       <c r="J204" s="4" t="n"/>
       <c r="K204" s="4" t="n"/>
+      <c r="L204" s="4" t="n"/>
+      <c r="M204" s="4" t="n"/>
+      <c r="N204" s="4" t="n"/>
+      <c r="O204" s="4" t="n"/>
+      <c r="P204" s="4" t="n"/>
+      <c r="Q204" s="4" t="n"/>
+      <c r="R204" s="4" t="n"/>
+      <c r="S204" s="4" t="n"/>
+      <c r="T204" s="4" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n"/>
@@ -4181,6 +6588,15 @@
       <c r="I205" s="4" t="n"/>
       <c r="J205" s="4" t="n"/>
       <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
+      <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
+      <c r="P205" s="4" t="n"/>
+      <c r="Q205" s="4" t="n"/>
+      <c r="R205" s="4" t="n"/>
+      <c r="S205" s="4" t="n"/>
+      <c r="T205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n"/>
@@ -4194,6 +6610,15 @@
       <c r="I206" s="4" t="n"/>
       <c r="J206" s="4" t="n"/>
       <c r="K206" s="4" t="n"/>
+      <c r="L206" s="4" t="n"/>
+      <c r="M206" s="4" t="n"/>
+      <c r="N206" s="4" t="n"/>
+      <c r="O206" s="4" t="n"/>
+      <c r="P206" s="4" t="n"/>
+      <c r="Q206" s="4" t="n"/>
+      <c r="R206" s="4" t="n"/>
+      <c r="S206" s="4" t="n"/>
+      <c r="T206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n"/>
@@ -4207,6 +6632,15 @@
       <c r="I207" s="4" t="n"/>
       <c r="J207" s="4" t="n"/>
       <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
+      <c r="P207" s="4" t="n"/>
+      <c r="Q207" s="4" t="n"/>
+      <c r="R207" s="4" t="n"/>
+      <c r="S207" s="4" t="n"/>
+      <c r="T207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n"/>
@@ -4220,6 +6654,15 @@
       <c r="I208" s="4" t="n"/>
       <c r="J208" s="4" t="n"/>
       <c r="K208" s="4" t="n"/>
+      <c r="L208" s="4" t="n"/>
+      <c r="M208" s="4" t="n"/>
+      <c r="N208" s="4" t="n"/>
+      <c r="O208" s="4" t="n"/>
+      <c r="P208" s="4" t="n"/>
+      <c r="Q208" s="4" t="n"/>
+      <c r="R208" s="4" t="n"/>
+      <c r="S208" s="4" t="n"/>
+      <c r="T208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -4233,6 +6676,15 @@
       <c r="I209" s="4" t="n"/>
       <c r="J209" s="4" t="n"/>
       <c r="K209" s="4" t="n"/>
+      <c r="L209" s="4" t="n"/>
+      <c r="M209" s="4" t="n"/>
+      <c r="N209" s="4" t="n"/>
+      <c r="O209" s="4" t="n"/>
+      <c r="P209" s="4" t="n"/>
+      <c r="Q209" s="4" t="n"/>
+      <c r="R209" s="4" t="n"/>
+      <c r="S209" s="4" t="n"/>
+      <c r="T209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="n"/>
@@ -4246,6 +6698,15 @@
       <c r="I210" s="4" t="n"/>
       <c r="J210" s="4" t="n"/>
       <c r="K210" s="4" t="n"/>
+      <c r="L210" s="4" t="n"/>
+      <c r="M210" s="4" t="n"/>
+      <c r="N210" s="4" t="n"/>
+      <c r="O210" s="4" t="n"/>
+      <c r="P210" s="4" t="n"/>
+      <c r="Q210" s="4" t="n"/>
+      <c r="R210" s="4" t="n"/>
+      <c r="S210" s="4" t="n"/>
+      <c r="T210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
@@ -4259,6 +6720,15 @@
       <c r="I211" s="4" t="n"/>
       <c r="J211" s="4" t="n"/>
       <c r="K211" s="4" t="n"/>
+      <c r="L211" s="4" t="n"/>
+      <c r="M211" s="4" t="n"/>
+      <c r="N211" s="4" t="n"/>
+      <c r="O211" s="4" t="n"/>
+      <c r="P211" s="4" t="n"/>
+      <c r="Q211" s="4" t="n"/>
+      <c r="R211" s="4" t="n"/>
+      <c r="S211" s="4" t="n"/>
+      <c r="T211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n"/>
@@ -4272,6 +6742,15 @@
       <c r="I212" s="4" t="n"/>
       <c r="J212" s="4" t="n"/>
       <c r="K212" s="4" t="n"/>
+      <c r="L212" s="4" t="n"/>
+      <c r="M212" s="4" t="n"/>
+      <c r="N212" s="4" t="n"/>
+      <c r="O212" s="4" t="n"/>
+      <c r="P212" s="4" t="n"/>
+      <c r="Q212" s="4" t="n"/>
+      <c r="R212" s="4" t="n"/>
+      <c r="S212" s="4" t="n"/>
+      <c r="T212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n"/>
@@ -4285,6 +6764,15 @@
       <c r="I213" s="4" t="n"/>
       <c r="J213" s="4" t="n"/>
       <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
+      <c r="N213" s="4" t="n"/>
+      <c r="O213" s="4" t="n"/>
+      <c r="P213" s="4" t="n"/>
+      <c r="Q213" s="4" t="n"/>
+      <c r="R213" s="4" t="n"/>
+      <c r="S213" s="4" t="n"/>
+      <c r="T213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="n"/>
@@ -4298,6 +6786,15 @@
       <c r="I214" s="4" t="n"/>
       <c r="J214" s="4" t="n"/>
       <c r="K214" s="4" t="n"/>
+      <c r="L214" s="4" t="n"/>
+      <c r="M214" s="4" t="n"/>
+      <c r="N214" s="4" t="n"/>
+      <c r="O214" s="4" t="n"/>
+      <c r="P214" s="4" t="n"/>
+      <c r="Q214" s="4" t="n"/>
+      <c r="R214" s="4" t="n"/>
+      <c r="S214" s="4" t="n"/>
+      <c r="T214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -4311,6 +6808,15 @@
       <c r="I215" s="4" t="n"/>
       <c r="J215" s="4" t="n"/>
       <c r="K215" s="4" t="n"/>
+      <c r="L215" s="4" t="n"/>
+      <c r="M215" s="4" t="n"/>
+      <c r="N215" s="4" t="n"/>
+      <c r="O215" s="4" t="n"/>
+      <c r="P215" s="4" t="n"/>
+      <c r="Q215" s="4" t="n"/>
+      <c r="R215" s="4" t="n"/>
+      <c r="S215" s="4" t="n"/>
+      <c r="T215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="n"/>
@@ -4324,6 +6830,15 @@
       <c r="I216" s="4" t="n"/>
       <c r="J216" s="4" t="n"/>
       <c r="K216" s="4" t="n"/>
+      <c r="L216" s="4" t="n"/>
+      <c r="M216" s="4" t="n"/>
+      <c r="N216" s="4" t="n"/>
+      <c r="O216" s="4" t="n"/>
+      <c r="P216" s="4" t="n"/>
+      <c r="Q216" s="4" t="n"/>
+      <c r="R216" s="4" t="n"/>
+      <c r="S216" s="4" t="n"/>
+      <c r="T216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -4337,6 +6852,15 @@
       <c r="I217" s="4" t="n"/>
       <c r="J217" s="4" t="n"/>
       <c r="K217" s="4" t="n"/>
+      <c r="L217" s="4" t="n"/>
+      <c r="M217" s="4" t="n"/>
+      <c r="N217" s="4" t="n"/>
+      <c r="O217" s="4" t="n"/>
+      <c r="P217" s="4" t="n"/>
+      <c r="Q217" s="4" t="n"/>
+      <c r="R217" s="4" t="n"/>
+      <c r="S217" s="4" t="n"/>
+      <c r="T217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="n"/>
@@ -4350,6 +6874,15 @@
       <c r="I218" s="4" t="n"/>
       <c r="J218" s="4" t="n"/>
       <c r="K218" s="4" t="n"/>
+      <c r="L218" s="4" t="n"/>
+      <c r="M218" s="4" t="n"/>
+      <c r="N218" s="4" t="n"/>
+      <c r="O218" s="4" t="n"/>
+      <c r="P218" s="4" t="n"/>
+      <c r="Q218" s="4" t="n"/>
+      <c r="R218" s="4" t="n"/>
+      <c r="S218" s="4" t="n"/>
+      <c r="T218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n"/>
@@ -4363,6 +6896,15 @@
       <c r="I219" s="4" t="n"/>
       <c r="J219" s="4" t="n"/>
       <c r="K219" s="4" t="n"/>
+      <c r="L219" s="4" t="n"/>
+      <c r="M219" s="4" t="n"/>
+      <c r="N219" s="4" t="n"/>
+      <c r="O219" s="4" t="n"/>
+      <c r="P219" s="4" t="n"/>
+      <c r="Q219" s="4" t="n"/>
+      <c r="R219" s="4" t="n"/>
+      <c r="S219" s="4" t="n"/>
+      <c r="T219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n"/>
@@ -4376,6 +6918,15 @@
       <c r="I220" s="4" t="n"/>
       <c r="J220" s="4" t="n"/>
       <c r="K220" s="4" t="n"/>
+      <c r="L220" s="4" t="n"/>
+      <c r="M220" s="4" t="n"/>
+      <c r="N220" s="4" t="n"/>
+      <c r="O220" s="4" t="n"/>
+      <c r="P220" s="4" t="n"/>
+      <c r="Q220" s="4" t="n"/>
+      <c r="R220" s="4" t="n"/>
+      <c r="S220" s="4" t="n"/>
+      <c r="T220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n"/>
@@ -4389,6 +6940,15 @@
       <c r="I221" s="4" t="n"/>
       <c r="J221" s="4" t="n"/>
       <c r="K221" s="4" t="n"/>
+      <c r="L221" s="4" t="n"/>
+      <c r="M221" s="4" t="n"/>
+      <c r="N221" s="4" t="n"/>
+      <c r="O221" s="4" t="n"/>
+      <c r="P221" s="4" t="n"/>
+      <c r="Q221" s="4" t="n"/>
+      <c r="R221" s="4" t="n"/>
+      <c r="S221" s="4" t="n"/>
+      <c r="T221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="n"/>
@@ -4402,6 +6962,15 @@
       <c r="I222" s="4" t="n"/>
       <c r="J222" s="4" t="n"/>
       <c r="K222" s="4" t="n"/>
+      <c r="L222" s="4" t="n"/>
+      <c r="M222" s="4" t="n"/>
+      <c r="N222" s="4" t="n"/>
+      <c r="O222" s="4" t="n"/>
+      <c r="P222" s="4" t="n"/>
+      <c r="Q222" s="4" t="n"/>
+      <c r="R222" s="4" t="n"/>
+      <c r="S222" s="4" t="n"/>
+      <c r="T222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n"/>
@@ -4415,6 +6984,15 @@
       <c r="I223" s="4" t="n"/>
       <c r="J223" s="4" t="n"/>
       <c r="K223" s="4" t="n"/>
+      <c r="L223" s="4" t="n"/>
+      <c r="M223" s="4" t="n"/>
+      <c r="N223" s="4" t="n"/>
+      <c r="O223" s="4" t="n"/>
+      <c r="P223" s="4" t="n"/>
+      <c r="Q223" s="4" t="n"/>
+      <c r="R223" s="4" t="n"/>
+      <c r="S223" s="4" t="n"/>
+      <c r="T223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n"/>
@@ -4428,6 +7006,15 @@
       <c r="I224" s="4" t="n"/>
       <c r="J224" s="4" t="n"/>
       <c r="K224" s="4" t="n"/>
+      <c r="L224" s="4" t="n"/>
+      <c r="M224" s="4" t="n"/>
+      <c r="N224" s="4" t="n"/>
+      <c r="O224" s="4" t="n"/>
+      <c r="P224" s="4" t="n"/>
+      <c r="Q224" s="4" t="n"/>
+      <c r="R224" s="4" t="n"/>
+      <c r="S224" s="4" t="n"/>
+      <c r="T224" s="4" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n"/>
@@ -4441,6 +7028,15 @@
       <c r="I225" s="4" t="n"/>
       <c r="J225" s="4" t="n"/>
       <c r="K225" s="4" t="n"/>
+      <c r="L225" s="4" t="n"/>
+      <c r="M225" s="4" t="n"/>
+      <c r="N225" s="4" t="n"/>
+      <c r="O225" s="4" t="n"/>
+      <c r="P225" s="4" t="n"/>
+      <c r="Q225" s="4" t="n"/>
+      <c r="R225" s="4" t="n"/>
+      <c r="S225" s="4" t="n"/>
+      <c r="T225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="n"/>
@@ -4454,6 +7050,15 @@
       <c r="I226" s="4" t="n"/>
       <c r="J226" s="4" t="n"/>
       <c r="K226" s="4" t="n"/>
+      <c r="L226" s="4" t="n"/>
+      <c r="M226" s="4" t="n"/>
+      <c r="N226" s="4" t="n"/>
+      <c r="O226" s="4" t="n"/>
+      <c r="P226" s="4" t="n"/>
+      <c r="Q226" s="4" t="n"/>
+      <c r="R226" s="4" t="n"/>
+      <c r="S226" s="4" t="n"/>
+      <c r="T226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n"/>
@@ -4467,6 +7072,15 @@
       <c r="I227" s="4" t="n"/>
       <c r="J227" s="4" t="n"/>
       <c r="K227" s="4" t="n"/>
+      <c r="L227" s="4" t="n"/>
+      <c r="M227" s="4" t="n"/>
+      <c r="N227" s="4" t="n"/>
+      <c r="O227" s="4" t="n"/>
+      <c r="P227" s="4" t="n"/>
+      <c r="Q227" s="4" t="n"/>
+      <c r="R227" s="4" t="n"/>
+      <c r="S227" s="4" t="n"/>
+      <c r="T227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n"/>
@@ -4480,6 +7094,15 @@
       <c r="I228" s="4" t="n"/>
       <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
+      <c r="L228" s="4" t="n"/>
+      <c r="M228" s="4" t="n"/>
+      <c r="N228" s="4" t="n"/>
+      <c r="O228" s="4" t="n"/>
+      <c r="P228" s="4" t="n"/>
+      <c r="Q228" s="4" t="n"/>
+      <c r="R228" s="4" t="n"/>
+      <c r="S228" s="4" t="n"/>
+      <c r="T228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n"/>
@@ -4493,6 +7116,15 @@
       <c r="I229" s="4" t="n"/>
       <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
+      <c r="L229" s="4" t="n"/>
+      <c r="M229" s="4" t="n"/>
+      <c r="N229" s="4" t="n"/>
+      <c r="O229" s="4" t="n"/>
+      <c r="P229" s="4" t="n"/>
+      <c r="Q229" s="4" t="n"/>
+      <c r="R229" s="4" t="n"/>
+      <c r="S229" s="4" t="n"/>
+      <c r="T229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n"/>
@@ -4506,6 +7138,15 @@
       <c r="I230" s="4" t="n"/>
       <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
+      <c r="L230" s="4" t="n"/>
+      <c r="M230" s="4" t="n"/>
+      <c r="N230" s="4" t="n"/>
+      <c r="O230" s="4" t="n"/>
+      <c r="P230" s="4" t="n"/>
+      <c r="Q230" s="4" t="n"/>
+      <c r="R230" s="4" t="n"/>
+      <c r="S230" s="4" t="n"/>
+      <c r="T230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n"/>
@@ -4519,6 +7160,15 @@
       <c r="I231" s="4" t="n"/>
       <c r="J231" s="4" t="n"/>
       <c r="K231" s="4" t="n"/>
+      <c r="L231" s="4" t="n"/>
+      <c r="M231" s="4" t="n"/>
+      <c r="N231" s="4" t="n"/>
+      <c r="O231" s="4" t="n"/>
+      <c r="P231" s="4" t="n"/>
+      <c r="Q231" s="4" t="n"/>
+      <c r="R231" s="4" t="n"/>
+      <c r="S231" s="4" t="n"/>
+      <c r="T231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="n"/>
@@ -4532,6 +7182,15 @@
       <c r="I232" s="4" t="n"/>
       <c r="J232" s="4" t="n"/>
       <c r="K232" s="4" t="n"/>
+      <c r="L232" s="4" t="n"/>
+      <c r="M232" s="4" t="n"/>
+      <c r="N232" s="4" t="n"/>
+      <c r="O232" s="4" t="n"/>
+      <c r="P232" s="4" t="n"/>
+      <c r="Q232" s="4" t="n"/>
+      <c r="R232" s="4" t="n"/>
+      <c r="S232" s="4" t="n"/>
+      <c r="T232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n"/>
@@ -4545,6 +7204,15 @@
       <c r="I233" s="4" t="n"/>
       <c r="J233" s="4" t="n"/>
       <c r="K233" s="4" t="n"/>
+      <c r="L233" s="4" t="n"/>
+      <c r="M233" s="4" t="n"/>
+      <c r="N233" s="4" t="n"/>
+      <c r="O233" s="4" t="n"/>
+      <c r="P233" s="4" t="n"/>
+      <c r="Q233" s="4" t="n"/>
+      <c r="R233" s="4" t="n"/>
+      <c r="S233" s="4" t="n"/>
+      <c r="T233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="n"/>
@@ -4558,6 +7226,15 @@
       <c r="I234" s="4" t="n"/>
       <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
+      <c r="L234" s="4" t="n"/>
+      <c r="M234" s="4" t="n"/>
+      <c r="N234" s="4" t="n"/>
+      <c r="O234" s="4" t="n"/>
+      <c r="P234" s="4" t="n"/>
+      <c r="Q234" s="4" t="n"/>
+      <c r="R234" s="4" t="n"/>
+      <c r="S234" s="4" t="n"/>
+      <c r="T234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
@@ -4571,6 +7248,15 @@
       <c r="I235" s="4" t="n"/>
       <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
+      <c r="L235" s="4" t="n"/>
+      <c r="M235" s="4" t="n"/>
+      <c r="N235" s="4" t="n"/>
+      <c r="O235" s="4" t="n"/>
+      <c r="P235" s="4" t="n"/>
+      <c r="Q235" s="4" t="n"/>
+      <c r="R235" s="4" t="n"/>
+      <c r="S235" s="4" t="n"/>
+      <c r="T235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="n"/>
@@ -4584,6 +7270,15 @@
       <c r="I236" s="4" t="n"/>
       <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
+      <c r="L236" s="4" t="n"/>
+      <c r="M236" s="4" t="n"/>
+      <c r="N236" s="4" t="n"/>
+      <c r="O236" s="4" t="n"/>
+      <c r="P236" s="4" t="n"/>
+      <c r="Q236" s="4" t="n"/>
+      <c r="R236" s="4" t="n"/>
+      <c r="S236" s="4" t="n"/>
+      <c r="T236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n"/>
@@ -4597,6 +7292,15 @@
       <c r="I237" s="4" t="n"/>
       <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
+      <c r="L237" s="4" t="n"/>
+      <c r="M237" s="4" t="n"/>
+      <c r="N237" s="4" t="n"/>
+      <c r="O237" s="4" t="n"/>
+      <c r="P237" s="4" t="n"/>
+      <c r="Q237" s="4" t="n"/>
+      <c r="R237" s="4" t="n"/>
+      <c r="S237" s="4" t="n"/>
+      <c r="T237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="n"/>
@@ -4610,6 +7314,15 @@
       <c r="I238" s="4" t="n"/>
       <c r="J238" s="4" t="n"/>
       <c r="K238" s="4" t="n"/>
+      <c r="L238" s="4" t="n"/>
+      <c r="M238" s="4" t="n"/>
+      <c r="N238" s="4" t="n"/>
+      <c r="O238" s="4" t="n"/>
+      <c r="P238" s="4" t="n"/>
+      <c r="Q238" s="4" t="n"/>
+      <c r="R238" s="4" t="n"/>
+      <c r="S238" s="4" t="n"/>
+      <c r="T238" s="4" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n"/>
@@ -4623,6 +7336,15 @@
       <c r="I239" s="4" t="n"/>
       <c r="J239" s="4" t="n"/>
       <c r="K239" s="4" t="n"/>
+      <c r="L239" s="4" t="n"/>
+      <c r="M239" s="4" t="n"/>
+      <c r="N239" s="4" t="n"/>
+      <c r="O239" s="4" t="n"/>
+      <c r="P239" s="4" t="n"/>
+      <c r="Q239" s="4" t="n"/>
+      <c r="R239" s="4" t="n"/>
+      <c r="S239" s="4" t="n"/>
+      <c r="T239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n"/>
@@ -4636,6 +7358,15 @@
       <c r="I240" s="4" t="n"/>
       <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="n"/>
+      <c r="L240" s="4" t="n"/>
+      <c r="M240" s="4" t="n"/>
+      <c r="N240" s="4" t="n"/>
+      <c r="O240" s="4" t="n"/>
+      <c r="P240" s="4" t="n"/>
+      <c r="Q240" s="4" t="n"/>
+      <c r="R240" s="4" t="n"/>
+      <c r="S240" s="4" t="n"/>
+      <c r="T240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n"/>
@@ -4649,6 +7380,15 @@
       <c r="I241" s="4" t="n"/>
       <c r="J241" s="4" t="n"/>
       <c r="K241" s="4" t="n"/>
+      <c r="L241" s="4" t="n"/>
+      <c r="M241" s="4" t="n"/>
+      <c r="N241" s="4" t="n"/>
+      <c r="O241" s="4" t="n"/>
+      <c r="P241" s="4" t="n"/>
+      <c r="Q241" s="4" t="n"/>
+      <c r="R241" s="4" t="n"/>
+      <c r="S241" s="4" t="n"/>
+      <c r="T241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="n"/>
@@ -4662,6 +7402,15 @@
       <c r="I242" s="4" t="n"/>
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
+      <c r="L242" s="4" t="n"/>
+      <c r="M242" s="4" t="n"/>
+      <c r="N242" s="4" t="n"/>
+      <c r="O242" s="4" t="n"/>
+      <c r="P242" s="4" t="n"/>
+      <c r="Q242" s="4" t="n"/>
+      <c r="R242" s="4" t="n"/>
+      <c r="S242" s="4" t="n"/>
+      <c r="T242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n"/>
@@ -4675,6 +7424,15 @@
       <c r="I243" s="4" t="n"/>
       <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
+      <c r="L243" s="4" t="n"/>
+      <c r="M243" s="4" t="n"/>
+      <c r="N243" s="4" t="n"/>
+      <c r="O243" s="4" t="n"/>
+      <c r="P243" s="4" t="n"/>
+      <c r="Q243" s="4" t="n"/>
+      <c r="R243" s="4" t="n"/>
+      <c r="S243" s="4" t="n"/>
+      <c r="T243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="n"/>
@@ -4688,6 +7446,15 @@
       <c r="I244" s="4" t="n"/>
       <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
+      <c r="L244" s="4" t="n"/>
+      <c r="M244" s="4" t="n"/>
+      <c r="N244" s="4" t="n"/>
+      <c r="O244" s="4" t="n"/>
+      <c r="P244" s="4" t="n"/>
+      <c r="Q244" s="4" t="n"/>
+      <c r="R244" s="4" t="n"/>
+      <c r="S244" s="4" t="n"/>
+      <c r="T244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n"/>
@@ -4701,6 +7468,15 @@
       <c r="I245" s="4" t="n"/>
       <c r="J245" s="4" t="n"/>
       <c r="K245" s="4" t="n"/>
+      <c r="L245" s="4" t="n"/>
+      <c r="M245" s="4" t="n"/>
+      <c r="N245" s="4" t="n"/>
+      <c r="O245" s="4" t="n"/>
+      <c r="P245" s="4" t="n"/>
+      <c r="Q245" s="4" t="n"/>
+      <c r="R245" s="4" t="n"/>
+      <c r="S245" s="4" t="n"/>
+      <c r="T245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n"/>
@@ -4714,6 +7490,15 @@
       <c r="I246" s="4" t="n"/>
       <c r="J246" s="4" t="n"/>
       <c r="K246" s="4" t="n"/>
+      <c r="L246" s="4" t="n"/>
+      <c r="M246" s="4" t="n"/>
+      <c r="N246" s="4" t="n"/>
+      <c r="O246" s="4" t="n"/>
+      <c r="P246" s="4" t="n"/>
+      <c r="Q246" s="4" t="n"/>
+      <c r="R246" s="4" t="n"/>
+      <c r="S246" s="4" t="n"/>
+      <c r="T246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
@@ -4727,6 +7512,15 @@
       <c r="I247" s="4" t="n"/>
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
+      <c r="L247" s="4" t="n"/>
+      <c r="M247" s="4" t="n"/>
+      <c r="N247" s="4" t="n"/>
+      <c r="O247" s="4" t="n"/>
+      <c r="P247" s="4" t="n"/>
+      <c r="Q247" s="4" t="n"/>
+      <c r="R247" s="4" t="n"/>
+      <c r="S247" s="4" t="n"/>
+      <c r="T247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="n"/>
@@ -4740,6 +7534,15 @@
       <c r="I248" s="4" t="n"/>
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
+      <c r="L248" s="4" t="n"/>
+      <c r="M248" s="4" t="n"/>
+      <c r="N248" s="4" t="n"/>
+      <c r="O248" s="4" t="n"/>
+      <c r="P248" s="4" t="n"/>
+      <c r="Q248" s="4" t="n"/>
+      <c r="R248" s="4" t="n"/>
+      <c r="S248" s="4" t="n"/>
+      <c r="T248" s="4" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n"/>
@@ -4753,6 +7556,15 @@
       <c r="I249" s="4" t="n"/>
       <c r="J249" s="4" t="n"/>
       <c r="K249" s="4" t="n"/>
+      <c r="L249" s="4" t="n"/>
+      <c r="M249" s="4" t="n"/>
+      <c r="N249" s="4" t="n"/>
+      <c r="O249" s="4" t="n"/>
+      <c r="P249" s="4" t="n"/>
+      <c r="Q249" s="4" t="n"/>
+      <c r="R249" s="4" t="n"/>
+      <c r="S249" s="4" t="n"/>
+      <c r="T249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n"/>
@@ -4766,6 +7578,15 @@
       <c r="I250" s="4" t="n"/>
       <c r="J250" s="4" t="n"/>
       <c r="K250" s="4" t="n"/>
+      <c r="L250" s="4" t="n"/>
+      <c r="M250" s="4" t="n"/>
+      <c r="N250" s="4" t="n"/>
+      <c r="O250" s="4" t="n"/>
+      <c r="P250" s="4" t="n"/>
+      <c r="Q250" s="4" t="n"/>
+      <c r="R250" s="4" t="n"/>
+      <c r="S250" s="4" t="n"/>
+      <c r="T250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n"/>
@@ -4779,6 +7600,15 @@
       <c r="I251" s="4" t="n"/>
       <c r="J251" s="4" t="n"/>
       <c r="K251" s="4" t="n"/>
+      <c r="L251" s="4" t="n"/>
+      <c r="M251" s="4" t="n"/>
+      <c r="N251" s="4" t="n"/>
+      <c r="O251" s="4" t="n"/>
+      <c r="P251" s="4" t="n"/>
+      <c r="Q251" s="4" t="n"/>
+      <c r="R251" s="4" t="n"/>
+      <c r="S251" s="4" t="n"/>
+      <c r="T251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="n"/>
@@ -4792,6 +7622,15 @@
       <c r="I252" s="4" t="n"/>
       <c r="J252" s="4" t="n"/>
       <c r="K252" s="4" t="n"/>
+      <c r="L252" s="4" t="n"/>
+      <c r="M252" s="4" t="n"/>
+      <c r="N252" s="4" t="n"/>
+      <c r="O252" s="4" t="n"/>
+      <c r="P252" s="4" t="n"/>
+      <c r="Q252" s="4" t="n"/>
+      <c r="R252" s="4" t="n"/>
+      <c r="S252" s="4" t="n"/>
+      <c r="T252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n"/>
@@ -4805,6 +7644,15 @@
       <c r="I253" s="4" t="n"/>
       <c r="J253" s="4" t="n"/>
       <c r="K253" s="4" t="n"/>
+      <c r="L253" s="4" t="n"/>
+      <c r="M253" s="4" t="n"/>
+      <c r="N253" s="4" t="n"/>
+      <c r="O253" s="4" t="n"/>
+      <c r="P253" s="4" t="n"/>
+      <c r="Q253" s="4" t="n"/>
+      <c r="R253" s="4" t="n"/>
+      <c r="S253" s="4" t="n"/>
+      <c r="T253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n"/>
@@ -4818,6 +7666,15 @@
       <c r="I254" s="4" t="n"/>
       <c r="J254" s="4" t="n"/>
       <c r="K254" s="4" t="n"/>
+      <c r="L254" s="4" t="n"/>
+      <c r="M254" s="4" t="n"/>
+      <c r="N254" s="4" t="n"/>
+      <c r="O254" s="4" t="n"/>
+      <c r="P254" s="4" t="n"/>
+      <c r="Q254" s="4" t="n"/>
+      <c r="R254" s="4" t="n"/>
+      <c r="S254" s="4" t="n"/>
+      <c r="T254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n"/>
@@ -4831,6 +7688,15 @@
       <c r="I255" s="4" t="n"/>
       <c r="J255" s="4" t="n"/>
       <c r="K255" s="4" t="n"/>
+      <c r="L255" s="4" t="n"/>
+      <c r="M255" s="4" t="n"/>
+      <c r="N255" s="4" t="n"/>
+      <c r="O255" s="4" t="n"/>
+      <c r="P255" s="4" t="n"/>
+      <c r="Q255" s="4" t="n"/>
+      <c r="R255" s="4" t="n"/>
+      <c r="S255" s="4" t="n"/>
+      <c r="T255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="n"/>
@@ -4844,6 +7710,15 @@
       <c r="I256" s="4" t="n"/>
       <c r="J256" s="4" t="n"/>
       <c r="K256" s="4" t="n"/>
+      <c r="L256" s="4" t="n"/>
+      <c r="M256" s="4" t="n"/>
+      <c r="N256" s="4" t="n"/>
+      <c r="O256" s="4" t="n"/>
+      <c r="P256" s="4" t="n"/>
+      <c r="Q256" s="4" t="n"/>
+      <c r="R256" s="4" t="n"/>
+      <c r="S256" s="4" t="n"/>
+      <c r="T256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
@@ -4857,6 +7732,15 @@
       <c r="I257" s="4" t="n"/>
       <c r="J257" s="4" t="n"/>
       <c r="K257" s="4" t="n"/>
+      <c r="L257" s="4" t="n"/>
+      <c r="M257" s="4" t="n"/>
+      <c r="N257" s="4" t="n"/>
+      <c r="O257" s="4" t="n"/>
+      <c r="P257" s="4" t="n"/>
+      <c r="Q257" s="4" t="n"/>
+      <c r="R257" s="4" t="n"/>
+      <c r="S257" s="4" t="n"/>
+      <c r="T257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="n"/>
@@ -4870,6 +7754,15 @@
       <c r="I258" s="4" t="n"/>
       <c r="J258" s="4" t="n"/>
       <c r="K258" s="4" t="n"/>
+      <c r="L258" s="4" t="n"/>
+      <c r="M258" s="4" t="n"/>
+      <c r="N258" s="4" t="n"/>
+      <c r="O258" s="4" t="n"/>
+      <c r="P258" s="4" t="n"/>
+      <c r="Q258" s="4" t="n"/>
+      <c r="R258" s="4" t="n"/>
+      <c r="S258" s="4" t="n"/>
+      <c r="T258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
@@ -4883,6 +7776,15 @@
       <c r="I259" s="4" t="n"/>
       <c r="J259" s="4" t="n"/>
       <c r="K259" s="4" t="n"/>
+      <c r="L259" s="4" t="n"/>
+      <c r="M259" s="4" t="n"/>
+      <c r="N259" s="4" t="n"/>
+      <c r="O259" s="4" t="n"/>
+      <c r="P259" s="4" t="n"/>
+      <c r="Q259" s="4" t="n"/>
+      <c r="R259" s="4" t="n"/>
+      <c r="S259" s="4" t="n"/>
+      <c r="T259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
@@ -4896,6 +7798,15 @@
       <c r="I260" s="4" t="n"/>
       <c r="J260" s="4" t="n"/>
       <c r="K260" s="4" t="n"/>
+      <c r="L260" s="4" t="n"/>
+      <c r="M260" s="4" t="n"/>
+      <c r="N260" s="4" t="n"/>
+      <c r="O260" s="4" t="n"/>
+      <c r="P260" s="4" t="n"/>
+      <c r="Q260" s="4" t="n"/>
+      <c r="R260" s="4" t="n"/>
+      <c r="S260" s="4" t="n"/>
+      <c r="T260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
@@ -4909,6 +7820,15 @@
       <c r="I261" s="4" t="n"/>
       <c r="J261" s="4" t="n"/>
       <c r="K261" s="4" t="n"/>
+      <c r="L261" s="4" t="n"/>
+      <c r="M261" s="4" t="n"/>
+      <c r="N261" s="4" t="n"/>
+      <c r="O261" s="4" t="n"/>
+      <c r="P261" s="4" t="n"/>
+      <c r="Q261" s="4" t="n"/>
+      <c r="R261" s="4" t="n"/>
+      <c r="S261" s="4" t="n"/>
+      <c r="T261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
@@ -4922,6 +7842,15 @@
       <c r="I262" s="4" t="n"/>
       <c r="J262" s="4" t="n"/>
       <c r="K262" s="4" t="n"/>
+      <c r="L262" s="4" t="n"/>
+      <c r="M262" s="4" t="n"/>
+      <c r="N262" s="4" t="n"/>
+      <c r="O262" s="4" t="n"/>
+      <c r="P262" s="4" t="n"/>
+      <c r="Q262" s="4" t="n"/>
+      <c r="R262" s="4" t="n"/>
+      <c r="S262" s="4" t="n"/>
+      <c r="T262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n"/>
@@ -4935,6 +7864,15 @@
       <c r="I263" s="4" t="n"/>
       <c r="J263" s="4" t="n"/>
       <c r="K263" s="4" t="n"/>
+      <c r="L263" s="4" t="n"/>
+      <c r="M263" s="4" t="n"/>
+      <c r="N263" s="4" t="n"/>
+      <c r="O263" s="4" t="n"/>
+      <c r="P263" s="4" t="n"/>
+      <c r="Q263" s="4" t="n"/>
+      <c r="R263" s="4" t="n"/>
+      <c r="S263" s="4" t="n"/>
+      <c r="T263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n"/>
@@ -4948,6 +7886,15 @@
       <c r="I264" s="4" t="n"/>
       <c r="J264" s="4" t="n"/>
       <c r="K264" s="4" t="n"/>
+      <c r="L264" s="4" t="n"/>
+      <c r="M264" s="4" t="n"/>
+      <c r="N264" s="4" t="n"/>
+      <c r="O264" s="4" t="n"/>
+      <c r="P264" s="4" t="n"/>
+      <c r="Q264" s="4" t="n"/>
+      <c r="R264" s="4" t="n"/>
+      <c r="S264" s="4" t="n"/>
+      <c r="T264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
@@ -4961,6 +7908,15 @@
       <c r="I265" s="4" t="n"/>
       <c r="J265" s="4" t="n"/>
       <c r="K265" s="4" t="n"/>
+      <c r="L265" s="4" t="n"/>
+      <c r="M265" s="4" t="n"/>
+      <c r="N265" s="4" t="n"/>
+      <c r="O265" s="4" t="n"/>
+      <c r="P265" s="4" t="n"/>
+      <c r="Q265" s="4" t="n"/>
+      <c r="R265" s="4" t="n"/>
+      <c r="S265" s="4" t="n"/>
+      <c r="T265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n"/>
@@ -4974,6 +7930,15 @@
       <c r="I266" s="4" t="n"/>
       <c r="J266" s="4" t="n"/>
       <c r="K266" s="4" t="n"/>
+      <c r="L266" s="4" t="n"/>
+      <c r="M266" s="4" t="n"/>
+      <c r="N266" s="4" t="n"/>
+      <c r="O266" s="4" t="n"/>
+      <c r="P266" s="4" t="n"/>
+      <c r="Q266" s="4" t="n"/>
+      <c r="R266" s="4" t="n"/>
+      <c r="S266" s="4" t="n"/>
+      <c r="T266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n"/>
@@ -4987,6 +7952,15 @@
       <c r="I267" s="4" t="n"/>
       <c r="J267" s="4" t="n"/>
       <c r="K267" s="4" t="n"/>
+      <c r="L267" s="4" t="n"/>
+      <c r="M267" s="4" t="n"/>
+      <c r="N267" s="4" t="n"/>
+      <c r="O267" s="4" t="n"/>
+      <c r="P267" s="4" t="n"/>
+      <c r="Q267" s="4" t="n"/>
+      <c r="R267" s="4" t="n"/>
+      <c r="S267" s="4" t="n"/>
+      <c r="T267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n"/>
@@ -5000,6 +7974,15 @@
       <c r="I268" s="4" t="n"/>
       <c r="J268" s="4" t="n"/>
       <c r="K268" s="4" t="n"/>
+      <c r="L268" s="4" t="n"/>
+      <c r="M268" s="4" t="n"/>
+      <c r="N268" s="4" t="n"/>
+      <c r="O268" s="4" t="n"/>
+      <c r="P268" s="4" t="n"/>
+      <c r="Q268" s="4" t="n"/>
+      <c r="R268" s="4" t="n"/>
+      <c r="S268" s="4" t="n"/>
+      <c r="T268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n"/>
@@ -5013,6 +7996,15 @@
       <c r="I269" s="4" t="n"/>
       <c r="J269" s="4" t="n"/>
       <c r="K269" s="4" t="n"/>
+      <c r="L269" s="4" t="n"/>
+      <c r="M269" s="4" t="n"/>
+      <c r="N269" s="4" t="n"/>
+      <c r="O269" s="4" t="n"/>
+      <c r="P269" s="4" t="n"/>
+      <c r="Q269" s="4" t="n"/>
+      <c r="R269" s="4" t="n"/>
+      <c r="S269" s="4" t="n"/>
+      <c r="T269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n"/>
@@ -5026,6 +8018,15 @@
       <c r="I270" s="4" t="n"/>
       <c r="J270" s="4" t="n"/>
       <c r="K270" s="4" t="n"/>
+      <c r="L270" s="4" t="n"/>
+      <c r="M270" s="4" t="n"/>
+      <c r="N270" s="4" t="n"/>
+      <c r="O270" s="4" t="n"/>
+      <c r="P270" s="4" t="n"/>
+      <c r="Q270" s="4" t="n"/>
+      <c r="R270" s="4" t="n"/>
+      <c r="S270" s="4" t="n"/>
+      <c r="T270" s="4" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
@@ -5039,6 +8040,15 @@
       <c r="I271" s="4" t="n"/>
       <c r="J271" s="4" t="n"/>
       <c r="K271" s="4" t="n"/>
+      <c r="L271" s="4" t="n"/>
+      <c r="M271" s="4" t="n"/>
+      <c r="N271" s="4" t="n"/>
+      <c r="O271" s="4" t="n"/>
+      <c r="P271" s="4" t="n"/>
+      <c r="Q271" s="4" t="n"/>
+      <c r="R271" s="4" t="n"/>
+      <c r="S271" s="4" t="n"/>
+      <c r="T271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="n"/>
@@ -5052,6 +8062,15 @@
       <c r="I272" s="4" t="n"/>
       <c r="J272" s="4" t="n"/>
       <c r="K272" s="4" t="n"/>
+      <c r="L272" s="4" t="n"/>
+      <c r="M272" s="4" t="n"/>
+      <c r="N272" s="4" t="n"/>
+      <c r="O272" s="4" t="n"/>
+      <c r="P272" s="4" t="n"/>
+      <c r="Q272" s="4" t="n"/>
+      <c r="R272" s="4" t="n"/>
+      <c r="S272" s="4" t="n"/>
+      <c r="T272" s="4" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n"/>
@@ -5065,6 +8084,15 @@
       <c r="I273" s="4" t="n"/>
       <c r="J273" s="4" t="n"/>
       <c r="K273" s="4" t="n"/>
+      <c r="L273" s="4" t="n"/>
+      <c r="M273" s="4" t="n"/>
+      <c r="N273" s="4" t="n"/>
+      <c r="O273" s="4" t="n"/>
+      <c r="P273" s="4" t="n"/>
+      <c r="Q273" s="4" t="n"/>
+      <c r="R273" s="4" t="n"/>
+      <c r="S273" s="4" t="n"/>
+      <c r="T273" s="4" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="n"/>
@@ -5078,6 +8106,15 @@
       <c r="I274" s="4" t="n"/>
       <c r="J274" s="4" t="n"/>
       <c r="K274" s="4" t="n"/>
+      <c r="L274" s="4" t="n"/>
+      <c r="M274" s="4" t="n"/>
+      <c r="N274" s="4" t="n"/>
+      <c r="O274" s="4" t="n"/>
+      <c r="P274" s="4" t="n"/>
+      <c r="Q274" s="4" t="n"/>
+      <c r="R274" s="4" t="n"/>
+      <c r="S274" s="4" t="n"/>
+      <c r="T274" s="4" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n"/>
@@ -5091,6 +8128,15 @@
       <c r="I275" s="4" t="n"/>
       <c r="J275" s="4" t="n"/>
       <c r="K275" s="4" t="n"/>
+      <c r="L275" s="4" t="n"/>
+      <c r="M275" s="4" t="n"/>
+      <c r="N275" s="4" t="n"/>
+      <c r="O275" s="4" t="n"/>
+      <c r="P275" s="4" t="n"/>
+      <c r="Q275" s="4" t="n"/>
+      <c r="R275" s="4" t="n"/>
+      <c r="S275" s="4" t="n"/>
+      <c r="T275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="n"/>
@@ -5104,6 +8150,15 @@
       <c r="I276" s="4" t="n"/>
       <c r="J276" s="4" t="n"/>
       <c r="K276" s="4" t="n"/>
+      <c r="L276" s="4" t="n"/>
+      <c r="M276" s="4" t="n"/>
+      <c r="N276" s="4" t="n"/>
+      <c r="O276" s="4" t="n"/>
+      <c r="P276" s="4" t="n"/>
+      <c r="Q276" s="4" t="n"/>
+      <c r="R276" s="4" t="n"/>
+      <c r="S276" s="4" t="n"/>
+      <c r="T276" s="4" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n"/>
@@ -5117,6 +8172,15 @@
       <c r="I277" s="4" t="n"/>
       <c r="J277" s="4" t="n"/>
       <c r="K277" s="4" t="n"/>
+      <c r="L277" s="4" t="n"/>
+      <c r="M277" s="4" t="n"/>
+      <c r="N277" s="4" t="n"/>
+      <c r="O277" s="4" t="n"/>
+      <c r="P277" s="4" t="n"/>
+      <c r="Q277" s="4" t="n"/>
+      <c r="R277" s="4" t="n"/>
+      <c r="S277" s="4" t="n"/>
+      <c r="T277" s="4" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="n"/>
@@ -5130,6 +8194,15 @@
       <c r="I278" s="4" t="n"/>
       <c r="J278" s="4" t="n"/>
       <c r="K278" s="4" t="n"/>
+      <c r="L278" s="4" t="n"/>
+      <c r="M278" s="4" t="n"/>
+      <c r="N278" s="4" t="n"/>
+      <c r="O278" s="4" t="n"/>
+      <c r="P278" s="4" t="n"/>
+      <c r="Q278" s="4" t="n"/>
+      <c r="R278" s="4" t="n"/>
+      <c r="S278" s="4" t="n"/>
+      <c r="T278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n"/>
@@ -5143,6 +8216,15 @@
       <c r="I279" s="4" t="n"/>
       <c r="J279" s="4" t="n"/>
       <c r="K279" s="4" t="n"/>
+      <c r="L279" s="4" t="n"/>
+      <c r="M279" s="4" t="n"/>
+      <c r="N279" s="4" t="n"/>
+      <c r="O279" s="4" t="n"/>
+      <c r="P279" s="4" t="n"/>
+      <c r="Q279" s="4" t="n"/>
+      <c r="R279" s="4" t="n"/>
+      <c r="S279" s="4" t="n"/>
+      <c r="T279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="n"/>
@@ -5156,6 +8238,15 @@
       <c r="I280" s="4" t="n"/>
       <c r="J280" s="4" t="n"/>
       <c r="K280" s="4" t="n"/>
+      <c r="L280" s="4" t="n"/>
+      <c r="M280" s="4" t="n"/>
+      <c r="N280" s="4" t="n"/>
+      <c r="O280" s="4" t="n"/>
+      <c r="P280" s="4" t="n"/>
+      <c r="Q280" s="4" t="n"/>
+      <c r="R280" s="4" t="n"/>
+      <c r="S280" s="4" t="n"/>
+      <c r="T280" s="4" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n"/>
@@ -5169,6 +8260,15 @@
       <c r="I281" s="4" t="n"/>
       <c r="J281" s="4" t="n"/>
       <c r="K281" s="4" t="n"/>
+      <c r="L281" s="4" t="n"/>
+      <c r="M281" s="4" t="n"/>
+      <c r="N281" s="4" t="n"/>
+      <c r="O281" s="4" t="n"/>
+      <c r="P281" s="4" t="n"/>
+      <c r="Q281" s="4" t="n"/>
+      <c r="R281" s="4" t="n"/>
+      <c r="S281" s="4" t="n"/>
+      <c r="T281" s="4" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="4" t="n"/>
@@ -5182,6 +8282,15 @@
       <c r="I282" s="4" t="n"/>
       <c r="J282" s="4" t="n"/>
       <c r="K282" s="4" t="n"/>
+      <c r="L282" s="4" t="n"/>
+      <c r="M282" s="4" t="n"/>
+      <c r="N282" s="4" t="n"/>
+      <c r="O282" s="4" t="n"/>
+      <c r="P282" s="4" t="n"/>
+      <c r="Q282" s="4" t="n"/>
+      <c r="R282" s="4" t="n"/>
+      <c r="S282" s="4" t="n"/>
+      <c r="T282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n"/>
@@ -5195,6 +8304,15 @@
       <c r="I283" s="4" t="n"/>
       <c r="J283" s="4" t="n"/>
       <c r="K283" s="4" t="n"/>
+      <c r="L283" s="4" t="n"/>
+      <c r="M283" s="4" t="n"/>
+      <c r="N283" s="4" t="n"/>
+      <c r="O283" s="4" t="n"/>
+      <c r="P283" s="4" t="n"/>
+      <c r="Q283" s="4" t="n"/>
+      <c r="R283" s="4" t="n"/>
+      <c r="S283" s="4" t="n"/>
+      <c r="T283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="4" t="n"/>
@@ -5208,6 +8326,15 @@
       <c r="I284" s="4" t="n"/>
       <c r="J284" s="4" t="n"/>
       <c r="K284" s="4" t="n"/>
+      <c r="L284" s="4" t="n"/>
+      <c r="M284" s="4" t="n"/>
+      <c r="N284" s="4" t="n"/>
+      <c r="O284" s="4" t="n"/>
+      <c r="P284" s="4" t="n"/>
+      <c r="Q284" s="4" t="n"/>
+      <c r="R284" s="4" t="n"/>
+      <c r="S284" s="4" t="n"/>
+      <c r="T284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n"/>
@@ -5221,6 +8348,15 @@
       <c r="I285" s="4" t="n"/>
       <c r="J285" s="4" t="n"/>
       <c r="K285" s="4" t="n"/>
+      <c r="L285" s="4" t="n"/>
+      <c r="M285" s="4" t="n"/>
+      <c r="N285" s="4" t="n"/>
+      <c r="O285" s="4" t="n"/>
+      <c r="P285" s="4" t="n"/>
+      <c r="Q285" s="4" t="n"/>
+      <c r="R285" s="4" t="n"/>
+      <c r="S285" s="4" t="n"/>
+      <c r="T285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="4" t="n"/>
@@ -5234,6 +8370,15 @@
       <c r="I286" s="4" t="n"/>
       <c r="J286" s="4" t="n"/>
       <c r="K286" s="4" t="n"/>
+      <c r="L286" s="4" t="n"/>
+      <c r="M286" s="4" t="n"/>
+      <c r="N286" s="4" t="n"/>
+      <c r="O286" s="4" t="n"/>
+      <c r="P286" s="4" t="n"/>
+      <c r="Q286" s="4" t="n"/>
+      <c r="R286" s="4" t="n"/>
+      <c r="S286" s="4" t="n"/>
+      <c r="T286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n"/>
@@ -5247,6 +8392,15 @@
       <c r="I287" s="4" t="n"/>
       <c r="J287" s="4" t="n"/>
       <c r="K287" s="4" t="n"/>
+      <c r="L287" s="4" t="n"/>
+      <c r="M287" s="4" t="n"/>
+      <c r="N287" s="4" t="n"/>
+      <c r="O287" s="4" t="n"/>
+      <c r="P287" s="4" t="n"/>
+      <c r="Q287" s="4" t="n"/>
+      <c r="R287" s="4" t="n"/>
+      <c r="S287" s="4" t="n"/>
+      <c r="T287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n"/>
@@ -5260,6 +8414,15 @@
       <c r="I288" s="4" t="n"/>
       <c r="J288" s="4" t="n"/>
       <c r="K288" s="4" t="n"/>
+      <c r="L288" s="4" t="n"/>
+      <c r="M288" s="4" t="n"/>
+      <c r="N288" s="4" t="n"/>
+      <c r="O288" s="4" t="n"/>
+      <c r="P288" s="4" t="n"/>
+      <c r="Q288" s="4" t="n"/>
+      <c r="R288" s="4" t="n"/>
+      <c r="S288" s="4" t="n"/>
+      <c r="T288" s="4" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n"/>
@@ -5273,6 +8436,15 @@
       <c r="I289" s="4" t="n"/>
       <c r="J289" s="4" t="n"/>
       <c r="K289" s="4" t="n"/>
+      <c r="L289" s="4" t="n"/>
+      <c r="M289" s="4" t="n"/>
+      <c r="N289" s="4" t="n"/>
+      <c r="O289" s="4" t="n"/>
+      <c r="P289" s="4" t="n"/>
+      <c r="Q289" s="4" t="n"/>
+      <c r="R289" s="4" t="n"/>
+      <c r="S289" s="4" t="n"/>
+      <c r="T289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="4" t="n"/>
@@ -5286,6 +8458,15 @@
       <c r="I290" s="4" t="n"/>
       <c r="J290" s="4" t="n"/>
       <c r="K290" s="4" t="n"/>
+      <c r="L290" s="4" t="n"/>
+      <c r="M290" s="4" t="n"/>
+      <c r="N290" s="4" t="n"/>
+      <c r="O290" s="4" t="n"/>
+      <c r="P290" s="4" t="n"/>
+      <c r="Q290" s="4" t="n"/>
+      <c r="R290" s="4" t="n"/>
+      <c r="S290" s="4" t="n"/>
+      <c r="T290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n"/>
@@ -5299,6 +8480,15 @@
       <c r="I291" s="4" t="n"/>
       <c r="J291" s="4" t="n"/>
       <c r="K291" s="4" t="n"/>
+      <c r="L291" s="4" t="n"/>
+      <c r="M291" s="4" t="n"/>
+      <c r="N291" s="4" t="n"/>
+      <c r="O291" s="4" t="n"/>
+      <c r="P291" s="4" t="n"/>
+      <c r="Q291" s="4" t="n"/>
+      <c r="R291" s="4" t="n"/>
+      <c r="S291" s="4" t="n"/>
+      <c r="T291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="4" t="n"/>
@@ -5312,6 +8502,15 @@
       <c r="I292" s="4" t="n"/>
       <c r="J292" s="4" t="n"/>
       <c r="K292" s="4" t="n"/>
+      <c r="L292" s="4" t="n"/>
+      <c r="M292" s="4" t="n"/>
+      <c r="N292" s="4" t="n"/>
+      <c r="O292" s="4" t="n"/>
+      <c r="P292" s="4" t="n"/>
+      <c r="Q292" s="4" t="n"/>
+      <c r="R292" s="4" t="n"/>
+      <c r="S292" s="4" t="n"/>
+      <c r="T292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="4" t="n"/>
@@ -5325,6 +8524,15 @@
       <c r="I293" s="4" t="n"/>
       <c r="J293" s="4" t="n"/>
       <c r="K293" s="4" t="n"/>
+      <c r="L293" s="4" t="n"/>
+      <c r="M293" s="4" t="n"/>
+      <c r="N293" s="4" t="n"/>
+      <c r="O293" s="4" t="n"/>
+      <c r="P293" s="4" t="n"/>
+      <c r="Q293" s="4" t="n"/>
+      <c r="R293" s="4" t="n"/>
+      <c r="S293" s="4" t="n"/>
+      <c r="T293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="4" t="n"/>
@@ -5338,6 +8546,15 @@
       <c r="I294" s="4" t="n"/>
       <c r="J294" s="4" t="n"/>
       <c r="K294" s="4" t="n"/>
+      <c r="L294" s="4" t="n"/>
+      <c r="M294" s="4" t="n"/>
+      <c r="N294" s="4" t="n"/>
+      <c r="O294" s="4" t="n"/>
+      <c r="P294" s="4" t="n"/>
+      <c r="Q294" s="4" t="n"/>
+      <c r="R294" s="4" t="n"/>
+      <c r="S294" s="4" t="n"/>
+      <c r="T294" s="4" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="4" t="n"/>
@@ -5351,6 +8568,15 @@
       <c r="I295" s="4" t="n"/>
       <c r="J295" s="4" t="n"/>
       <c r="K295" s="4" t="n"/>
+      <c r="L295" s="4" t="n"/>
+      <c r="M295" s="4" t="n"/>
+      <c r="N295" s="4" t="n"/>
+      <c r="O295" s="4" t="n"/>
+      <c r="P295" s="4" t="n"/>
+      <c r="Q295" s="4" t="n"/>
+      <c r="R295" s="4" t="n"/>
+      <c r="S295" s="4" t="n"/>
+      <c r="T295" s="4" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="4" t="n"/>
@@ -5364,6 +8590,15 @@
       <c r="I296" s="4" t="n"/>
       <c r="J296" s="4" t="n"/>
       <c r="K296" s="4" t="n"/>
+      <c r="L296" s="4" t="n"/>
+      <c r="M296" s="4" t="n"/>
+      <c r="N296" s="4" t="n"/>
+      <c r="O296" s="4" t="n"/>
+      <c r="P296" s="4" t="n"/>
+      <c r="Q296" s="4" t="n"/>
+      <c r="R296" s="4" t="n"/>
+      <c r="S296" s="4" t="n"/>
+      <c r="T296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n"/>
@@ -5377,6 +8612,15 @@
       <c r="I297" s="4" t="n"/>
       <c r="J297" s="4" t="n"/>
       <c r="K297" s="4" t="n"/>
+      <c r="L297" s="4" t="n"/>
+      <c r="M297" s="4" t="n"/>
+      <c r="N297" s="4" t="n"/>
+      <c r="O297" s="4" t="n"/>
+      <c r="P297" s="4" t="n"/>
+      <c r="Q297" s="4" t="n"/>
+      <c r="R297" s="4" t="n"/>
+      <c r="S297" s="4" t="n"/>
+      <c r="T297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="4" t="n"/>
@@ -5390,6 +8634,15 @@
       <c r="I298" s="4" t="n"/>
       <c r="J298" s="4" t="n"/>
       <c r="K298" s="4" t="n"/>
+      <c r="L298" s="4" t="n"/>
+      <c r="M298" s="4" t="n"/>
+      <c r="N298" s="4" t="n"/>
+      <c r="O298" s="4" t="n"/>
+      <c r="P298" s="4" t="n"/>
+      <c r="Q298" s="4" t="n"/>
+      <c r="R298" s="4" t="n"/>
+      <c r="S298" s="4" t="n"/>
+      <c r="T298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n"/>
@@ -5403,6 +8656,15 @@
       <c r="I299" s="4" t="n"/>
       <c r="J299" s="4" t="n"/>
       <c r="K299" s="4" t="n"/>
+      <c r="L299" s="4" t="n"/>
+      <c r="M299" s="4" t="n"/>
+      <c r="N299" s="4" t="n"/>
+      <c r="O299" s="4" t="n"/>
+      <c r="P299" s="4" t="n"/>
+      <c r="Q299" s="4" t="n"/>
+      <c r="R299" s="4" t="n"/>
+      <c r="S299" s="4" t="n"/>
+      <c r="T299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="4" t="n"/>
@@ -5416,6 +8678,15 @@
       <c r="I300" s="4" t="n"/>
       <c r="J300" s="4" t="n"/>
       <c r="K300" s="4" t="n"/>
+      <c r="L300" s="4" t="n"/>
+      <c r="M300" s="4" t="n"/>
+      <c r="N300" s="4" t="n"/>
+      <c r="O300" s="4" t="n"/>
+      <c r="P300" s="4" t="n"/>
+      <c r="Q300" s="4" t="n"/>
+      <c r="R300" s="4" t="n"/>
+      <c r="S300" s="4" t="n"/>
+      <c r="T300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n"/>
@@ -5429,6 +8700,15 @@
       <c r="I301" s="4" t="n"/>
       <c r="J301" s="4" t="n"/>
       <c r="K301" s="4" t="n"/>
+      <c r="L301" s="4" t="n"/>
+      <c r="M301" s="4" t="n"/>
+      <c r="N301" s="4" t="n"/>
+      <c r="O301" s="4" t="n"/>
+      <c r="P301" s="4" t="n"/>
+      <c r="Q301" s="4" t="n"/>
+      <c r="R301" s="4" t="n"/>
+      <c r="S301" s="4" t="n"/>
+      <c r="T301" s="4" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="4" t="n"/>
@@ -5442,6 +8722,15 @@
       <c r="I302" s="4" t="n"/>
       <c r="J302" s="4" t="n"/>
       <c r="K302" s="4" t="n"/>
+      <c r="L302" s="4" t="n"/>
+      <c r="M302" s="4" t="n"/>
+      <c r="N302" s="4" t="n"/>
+      <c r="O302" s="4" t="n"/>
+      <c r="P302" s="4" t="n"/>
+      <c r="Q302" s="4" t="n"/>
+      <c r="R302" s="4" t="n"/>
+      <c r="S302" s="4" t="n"/>
+      <c r="T302" s="4" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n"/>
@@ -5455,6 +8744,15 @@
       <c r="I303" s="4" t="n"/>
       <c r="J303" s="4" t="n"/>
       <c r="K303" s="4" t="n"/>
+      <c r="L303" s="4" t="n"/>
+      <c r="M303" s="4" t="n"/>
+      <c r="N303" s="4" t="n"/>
+      <c r="O303" s="4" t="n"/>
+      <c r="P303" s="4" t="n"/>
+      <c r="Q303" s="4" t="n"/>
+      <c r="R303" s="4" t="n"/>
+      <c r="S303" s="4" t="n"/>
+      <c r="T303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="4" t="n"/>
@@ -5468,6 +8766,15 @@
       <c r="I304" s="4" t="n"/>
       <c r="J304" s="4" t="n"/>
       <c r="K304" s="4" t="n"/>
+      <c r="L304" s="4" t="n"/>
+      <c r="M304" s="4" t="n"/>
+      <c r="N304" s="4" t="n"/>
+      <c r="O304" s="4" t="n"/>
+      <c r="P304" s="4" t="n"/>
+      <c r="Q304" s="4" t="n"/>
+      <c r="R304" s="4" t="n"/>
+      <c r="S304" s="4" t="n"/>
+      <c r="T304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n"/>
@@ -5481,6 +8788,15 @@
       <c r="I305" s="4" t="n"/>
       <c r="J305" s="4" t="n"/>
       <c r="K305" s="4" t="n"/>
+      <c r="L305" s="4" t="n"/>
+      <c r="M305" s="4" t="n"/>
+      <c r="N305" s="4" t="n"/>
+      <c r="O305" s="4" t="n"/>
+      <c r="P305" s="4" t="n"/>
+      <c r="Q305" s="4" t="n"/>
+      <c r="R305" s="4" t="n"/>
+      <c r="S305" s="4" t="n"/>
+      <c r="T305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="4" t="n"/>
@@ -5494,6 +8810,15 @@
       <c r="I306" s="4" t="n"/>
       <c r="J306" s="4" t="n"/>
       <c r="K306" s="4" t="n"/>
+      <c r="L306" s="4" t="n"/>
+      <c r="M306" s="4" t="n"/>
+      <c r="N306" s="4" t="n"/>
+      <c r="O306" s="4" t="n"/>
+      <c r="P306" s="4" t="n"/>
+      <c r="Q306" s="4" t="n"/>
+      <c r="R306" s="4" t="n"/>
+      <c r="S306" s="4" t="n"/>
+      <c r="T306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="4" t="n"/>
@@ -5507,6 +8832,15 @@
       <c r="I307" s="4" t="n"/>
       <c r="J307" s="4" t="n"/>
       <c r="K307" s="4" t="n"/>
+      <c r="L307" s="4" t="n"/>
+      <c r="M307" s="4" t="n"/>
+      <c r="N307" s="4" t="n"/>
+      <c r="O307" s="4" t="n"/>
+      <c r="P307" s="4" t="n"/>
+      <c r="Q307" s="4" t="n"/>
+      <c r="R307" s="4" t="n"/>
+      <c r="S307" s="4" t="n"/>
+      <c r="T307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="4" t="n"/>
@@ -5520,6 +8854,15 @@
       <c r="I308" s="4" t="n"/>
       <c r="J308" s="4" t="n"/>
       <c r="K308" s="4" t="n"/>
+      <c r="L308" s="4" t="n"/>
+      <c r="M308" s="4" t="n"/>
+      <c r="N308" s="4" t="n"/>
+      <c r="O308" s="4" t="n"/>
+      <c r="P308" s="4" t="n"/>
+      <c r="Q308" s="4" t="n"/>
+      <c r="R308" s="4" t="n"/>
+      <c r="S308" s="4" t="n"/>
+      <c r="T308" s="4" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="4" t="n"/>
@@ -5533,6 +8876,15 @@
       <c r="I309" s="4" t="n"/>
       <c r="J309" s="4" t="n"/>
       <c r="K309" s="4" t="n"/>
+      <c r="L309" s="4" t="n"/>
+      <c r="M309" s="4" t="n"/>
+      <c r="N309" s="4" t="n"/>
+      <c r="O309" s="4" t="n"/>
+      <c r="P309" s="4" t="n"/>
+      <c r="Q309" s="4" t="n"/>
+      <c r="R309" s="4" t="n"/>
+      <c r="S309" s="4" t="n"/>
+      <c r="T309" s="4" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="4" t="n"/>
@@ -5546,6 +8898,15 @@
       <c r="I310" s="4" t="n"/>
       <c r="J310" s="4" t="n"/>
       <c r="K310" s="4" t="n"/>
+      <c r="L310" s="4" t="n"/>
+      <c r="M310" s="4" t="n"/>
+      <c r="N310" s="4" t="n"/>
+      <c r="O310" s="4" t="n"/>
+      <c r="P310" s="4" t="n"/>
+      <c r="Q310" s="4" t="n"/>
+      <c r="R310" s="4" t="n"/>
+      <c r="S310" s="4" t="n"/>
+      <c r="T310" s="4" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="4" t="n"/>
@@ -5559,6 +8920,15 @@
       <c r="I311" s="4" t="n"/>
       <c r="J311" s="4" t="n"/>
       <c r="K311" s="4" t="n"/>
+      <c r="L311" s="4" t="n"/>
+      <c r="M311" s="4" t="n"/>
+      <c r="N311" s="4" t="n"/>
+      <c r="O311" s="4" t="n"/>
+      <c r="P311" s="4" t="n"/>
+      <c r="Q311" s="4" t="n"/>
+      <c r="R311" s="4" t="n"/>
+      <c r="S311" s="4" t="n"/>
+      <c r="T311" s="4" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="4" t="n"/>
@@ -5572,6 +8942,15 @@
       <c r="I312" s="4" t="n"/>
       <c r="J312" s="4" t="n"/>
       <c r="K312" s="4" t="n"/>
+      <c r="L312" s="4" t="n"/>
+      <c r="M312" s="4" t="n"/>
+      <c r="N312" s="4" t="n"/>
+      <c r="O312" s="4" t="n"/>
+      <c r="P312" s="4" t="n"/>
+      <c r="Q312" s="4" t="n"/>
+      <c r="R312" s="4" t="n"/>
+      <c r="S312" s="4" t="n"/>
+      <c r="T312" s="4" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="4" t="n"/>
@@ -5585,6 +8964,15 @@
       <c r="I313" s="4" t="n"/>
       <c r="J313" s="4" t="n"/>
       <c r="K313" s="4" t="n"/>
+      <c r="L313" s="4" t="n"/>
+      <c r="M313" s="4" t="n"/>
+      <c r="N313" s="4" t="n"/>
+      <c r="O313" s="4" t="n"/>
+      <c r="P313" s="4" t="n"/>
+      <c r="Q313" s="4" t="n"/>
+      <c r="R313" s="4" t="n"/>
+      <c r="S313" s="4" t="n"/>
+      <c r="T313" s="4" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="4" t="n"/>
@@ -5598,6 +8986,15 @@
       <c r="I314" s="4" t="n"/>
       <c r="J314" s="4" t="n"/>
       <c r="K314" s="4" t="n"/>
+      <c r="L314" s="4" t="n"/>
+      <c r="M314" s="4" t="n"/>
+      <c r="N314" s="4" t="n"/>
+      <c r="O314" s="4" t="n"/>
+      <c r="P314" s="4" t="n"/>
+      <c r="Q314" s="4" t="n"/>
+      <c r="R314" s="4" t="n"/>
+      <c r="S314" s="4" t="n"/>
+      <c r="T314" s="4" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="4" t="n"/>
@@ -5611,6 +9008,15 @@
       <c r="I315" s="4" t="n"/>
       <c r="J315" s="4" t="n"/>
       <c r="K315" s="4" t="n"/>
+      <c r="L315" s="4" t="n"/>
+      <c r="M315" s="4" t="n"/>
+      <c r="N315" s="4" t="n"/>
+      <c r="O315" s="4" t="n"/>
+      <c r="P315" s="4" t="n"/>
+      <c r="Q315" s="4" t="n"/>
+      <c r="R315" s="4" t="n"/>
+      <c r="S315" s="4" t="n"/>
+      <c r="T315" s="4" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="4" t="n"/>
@@ -5624,6 +9030,15 @@
       <c r="I316" s="4" t="n"/>
       <c r="J316" s="4" t="n"/>
       <c r="K316" s="4" t="n"/>
+      <c r="L316" s="4" t="n"/>
+      <c r="M316" s="4" t="n"/>
+      <c r="N316" s="4" t="n"/>
+      <c r="O316" s="4" t="n"/>
+      <c r="P316" s="4" t="n"/>
+      <c r="Q316" s="4" t="n"/>
+      <c r="R316" s="4" t="n"/>
+      <c r="S316" s="4" t="n"/>
+      <c r="T316" s="4" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="4" t="n"/>
@@ -5637,6 +9052,15 @@
       <c r="I317" s="4" t="n"/>
       <c r="J317" s="4" t="n"/>
       <c r="K317" s="4" t="n"/>
+      <c r="L317" s="4" t="n"/>
+      <c r="M317" s="4" t="n"/>
+      <c r="N317" s="4" t="n"/>
+      <c r="O317" s="4" t="n"/>
+      <c r="P317" s="4" t="n"/>
+      <c r="Q317" s="4" t="n"/>
+      <c r="R317" s="4" t="n"/>
+      <c r="S317" s="4" t="n"/>
+      <c r="T317" s="4" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="4" t="n"/>
@@ -5650,6 +9074,15 @@
       <c r="I318" s="4" t="n"/>
       <c r="J318" s="4" t="n"/>
       <c r="K318" s="4" t="n"/>
+      <c r="L318" s="4" t="n"/>
+      <c r="M318" s="4" t="n"/>
+      <c r="N318" s="4" t="n"/>
+      <c r="O318" s="4" t="n"/>
+      <c r="P318" s="4" t="n"/>
+      <c r="Q318" s="4" t="n"/>
+      <c r="R318" s="4" t="n"/>
+      <c r="S318" s="4" t="n"/>
+      <c r="T318" s="4" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="4" t="n"/>
@@ -5663,6 +9096,15 @@
       <c r="I319" s="4" t="n"/>
       <c r="J319" s="4" t="n"/>
       <c r="K319" s="4" t="n"/>
+      <c r="L319" s="4" t="n"/>
+      <c r="M319" s="4" t="n"/>
+      <c r="N319" s="4" t="n"/>
+      <c r="O319" s="4" t="n"/>
+      <c r="P319" s="4" t="n"/>
+      <c r="Q319" s="4" t="n"/>
+      <c r="R319" s="4" t="n"/>
+      <c r="S319" s="4" t="n"/>
+      <c r="T319" s="4" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="4" t="n"/>
@@ -5676,6 +9118,15 @@
       <c r="I320" s="4" t="n"/>
       <c r="J320" s="4" t="n"/>
       <c r="K320" s="4" t="n"/>
+      <c r="L320" s="4" t="n"/>
+      <c r="M320" s="4" t="n"/>
+      <c r="N320" s="4" t="n"/>
+      <c r="O320" s="4" t="n"/>
+      <c r="P320" s="4" t="n"/>
+      <c r="Q320" s="4" t="n"/>
+      <c r="R320" s="4" t="n"/>
+      <c r="S320" s="4" t="n"/>
+      <c r="T320" s="4" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n"/>
@@ -5689,6 +9140,15 @@
       <c r="I321" s="4" t="n"/>
       <c r="J321" s="4" t="n"/>
       <c r="K321" s="4" t="n"/>
+      <c r="L321" s="4" t="n"/>
+      <c r="M321" s="4" t="n"/>
+      <c r="N321" s="4" t="n"/>
+      <c r="O321" s="4" t="n"/>
+      <c r="P321" s="4" t="n"/>
+      <c r="Q321" s="4" t="n"/>
+      <c r="R321" s="4" t="n"/>
+      <c r="S321" s="4" t="n"/>
+      <c r="T321" s="4" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="4" t="n"/>
@@ -5702,6 +9162,15 @@
       <c r="I322" s="4" t="n"/>
       <c r="J322" s="4" t="n"/>
       <c r="K322" s="4" t="n"/>
+      <c r="L322" s="4" t="n"/>
+      <c r="M322" s="4" t="n"/>
+      <c r="N322" s="4" t="n"/>
+      <c r="O322" s="4" t="n"/>
+      <c r="P322" s="4" t="n"/>
+      <c r="Q322" s="4" t="n"/>
+      <c r="R322" s="4" t="n"/>
+      <c r="S322" s="4" t="n"/>
+      <c r="T322" s="4" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n"/>
@@ -5715,6 +9184,15 @@
       <c r="I323" s="4" t="n"/>
       <c r="J323" s="4" t="n"/>
       <c r="K323" s="4" t="n"/>
+      <c r="L323" s="4" t="n"/>
+      <c r="M323" s="4" t="n"/>
+      <c r="N323" s="4" t="n"/>
+      <c r="O323" s="4" t="n"/>
+      <c r="P323" s="4" t="n"/>
+      <c r="Q323" s="4" t="n"/>
+      <c r="R323" s="4" t="n"/>
+      <c r="S323" s="4" t="n"/>
+      <c r="T323" s="4" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="4" t="n"/>
@@ -5728,6 +9206,15 @@
       <c r="I324" s="4" t="n"/>
       <c r="J324" s="4" t="n"/>
       <c r="K324" s="4" t="n"/>
+      <c r="L324" s="4" t="n"/>
+      <c r="M324" s="4" t="n"/>
+      <c r="N324" s="4" t="n"/>
+      <c r="O324" s="4" t="n"/>
+      <c r="P324" s="4" t="n"/>
+      <c r="Q324" s="4" t="n"/>
+      <c r="R324" s="4" t="n"/>
+      <c r="S324" s="4" t="n"/>
+      <c r="T324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n"/>
@@ -5741,6 +9228,15 @@
       <c r="I325" s="4" t="n"/>
       <c r="J325" s="4" t="n"/>
       <c r="K325" s="4" t="n"/>
+      <c r="L325" s="4" t="n"/>
+      <c r="M325" s="4" t="n"/>
+      <c r="N325" s="4" t="n"/>
+      <c r="O325" s="4" t="n"/>
+      <c r="P325" s="4" t="n"/>
+      <c r="Q325" s="4" t="n"/>
+      <c r="R325" s="4" t="n"/>
+      <c r="S325" s="4" t="n"/>
+      <c r="T325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="4" t="n"/>
@@ -5754,6 +9250,15 @@
       <c r="I326" s="4" t="n"/>
       <c r="J326" s="4" t="n"/>
       <c r="K326" s="4" t="n"/>
+      <c r="L326" s="4" t="n"/>
+      <c r="M326" s="4" t="n"/>
+      <c r="N326" s="4" t="n"/>
+      <c r="O326" s="4" t="n"/>
+      <c r="P326" s="4" t="n"/>
+      <c r="Q326" s="4" t="n"/>
+      <c r="R326" s="4" t="n"/>
+      <c r="S326" s="4" t="n"/>
+      <c r="T326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="4" t="n"/>
@@ -5767,6 +9272,15 @@
       <c r="I327" s="4" t="n"/>
       <c r="J327" s="4" t="n"/>
       <c r="K327" s="4" t="n"/>
+      <c r="L327" s="4" t="n"/>
+      <c r="M327" s="4" t="n"/>
+      <c r="N327" s="4" t="n"/>
+      <c r="O327" s="4" t="n"/>
+      <c r="P327" s="4" t="n"/>
+      <c r="Q327" s="4" t="n"/>
+      <c r="R327" s="4" t="n"/>
+      <c r="S327" s="4" t="n"/>
+      <c r="T327" s="4" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="4" t="n"/>
@@ -5780,6 +9294,15 @@
       <c r="I328" s="4" t="n"/>
       <c r="J328" s="4" t="n"/>
       <c r="K328" s="4" t="n"/>
+      <c r="L328" s="4" t="n"/>
+      <c r="M328" s="4" t="n"/>
+      <c r="N328" s="4" t="n"/>
+      <c r="O328" s="4" t="n"/>
+      <c r="P328" s="4" t="n"/>
+      <c r="Q328" s="4" t="n"/>
+      <c r="R328" s="4" t="n"/>
+      <c r="S328" s="4" t="n"/>
+      <c r="T328" s="4" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="4" t="n"/>
@@ -5793,6 +9316,15 @@
       <c r="I329" s="4" t="n"/>
       <c r="J329" s="4" t="n"/>
       <c r="K329" s="4" t="n"/>
+      <c r="L329" s="4" t="n"/>
+      <c r="M329" s="4" t="n"/>
+      <c r="N329" s="4" t="n"/>
+      <c r="O329" s="4" t="n"/>
+      <c r="P329" s="4" t="n"/>
+      <c r="Q329" s="4" t="n"/>
+      <c r="R329" s="4" t="n"/>
+      <c r="S329" s="4" t="n"/>
+      <c r="T329" s="4" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="4" t="n"/>
@@ -5806,6 +9338,15 @@
       <c r="I330" s="4" t="n"/>
       <c r="J330" s="4" t="n"/>
       <c r="K330" s="4" t="n"/>
+      <c r="L330" s="4" t="n"/>
+      <c r="M330" s="4" t="n"/>
+      <c r="N330" s="4" t="n"/>
+      <c r="O330" s="4" t="n"/>
+      <c r="P330" s="4" t="n"/>
+      <c r="Q330" s="4" t="n"/>
+      <c r="R330" s="4" t="n"/>
+      <c r="S330" s="4" t="n"/>
+      <c r="T330" s="4" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="4" t="n"/>
@@ -5819,6 +9360,15 @@
       <c r="I331" s="4" t="n"/>
       <c r="J331" s="4" t="n"/>
       <c r="K331" s="4" t="n"/>
+      <c r="L331" s="4" t="n"/>
+      <c r="M331" s="4" t="n"/>
+      <c r="N331" s="4" t="n"/>
+      <c r="O331" s="4" t="n"/>
+      <c r="P331" s="4" t="n"/>
+      <c r="Q331" s="4" t="n"/>
+      <c r="R331" s="4" t="n"/>
+      <c r="S331" s="4" t="n"/>
+      <c r="T331" s="4" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="4" t="n"/>
@@ -5832,6 +9382,15 @@
       <c r="I332" s="4" t="n"/>
       <c r="J332" s="4" t="n"/>
       <c r="K332" s="4" t="n"/>
+      <c r="L332" s="4" t="n"/>
+      <c r="M332" s="4" t="n"/>
+      <c r="N332" s="4" t="n"/>
+      <c r="O332" s="4" t="n"/>
+      <c r="P332" s="4" t="n"/>
+      <c r="Q332" s="4" t="n"/>
+      <c r="R332" s="4" t="n"/>
+      <c r="S332" s="4" t="n"/>
+      <c r="T332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="4" t="n"/>
@@ -5845,6 +9404,15 @@
       <c r="I333" s="4" t="n"/>
       <c r="J333" s="4" t="n"/>
       <c r="K333" s="4" t="n"/>
+      <c r="L333" s="4" t="n"/>
+      <c r="M333" s="4" t="n"/>
+      <c r="N333" s="4" t="n"/>
+      <c r="O333" s="4" t="n"/>
+      <c r="P333" s="4" t="n"/>
+      <c r="Q333" s="4" t="n"/>
+      <c r="R333" s="4" t="n"/>
+      <c r="S333" s="4" t="n"/>
+      <c r="T333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="4" t="n"/>
@@ -5858,6 +9426,15 @@
       <c r="I334" s="4" t="n"/>
       <c r="J334" s="4" t="n"/>
       <c r="K334" s="4" t="n"/>
+      <c r="L334" s="4" t="n"/>
+      <c r="M334" s="4" t="n"/>
+      <c r="N334" s="4" t="n"/>
+      <c r="O334" s="4" t="n"/>
+      <c r="P334" s="4" t="n"/>
+      <c r="Q334" s="4" t="n"/>
+      <c r="R334" s="4" t="n"/>
+      <c r="S334" s="4" t="n"/>
+      <c r="T334" s="4" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="4" t="n"/>
@@ -5871,6 +9448,15 @@
       <c r="I335" s="4" t="n"/>
       <c r="J335" s="4" t="n"/>
       <c r="K335" s="4" t="n"/>
+      <c r="L335" s="4" t="n"/>
+      <c r="M335" s="4" t="n"/>
+      <c r="N335" s="4" t="n"/>
+      <c r="O335" s="4" t="n"/>
+      <c r="P335" s="4" t="n"/>
+      <c r="Q335" s="4" t="n"/>
+      <c r="R335" s="4" t="n"/>
+      <c r="S335" s="4" t="n"/>
+      <c r="T335" s="4" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="4" t="n"/>
@@ -5884,6 +9470,15 @@
       <c r="I336" s="4" t="n"/>
       <c r="J336" s="4" t="n"/>
       <c r="K336" s="4" t="n"/>
+      <c r="L336" s="4" t="n"/>
+      <c r="M336" s="4" t="n"/>
+      <c r="N336" s="4" t="n"/>
+      <c r="O336" s="4" t="n"/>
+      <c r="P336" s="4" t="n"/>
+      <c r="Q336" s="4" t="n"/>
+      <c r="R336" s="4" t="n"/>
+      <c r="S336" s="4" t="n"/>
+      <c r="T336" s="4" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="4" t="n"/>
@@ -5897,6 +9492,15 @@
       <c r="I337" s="4" t="n"/>
       <c r="J337" s="4" t="n"/>
       <c r="K337" s="4" t="n"/>
+      <c r="L337" s="4" t="n"/>
+      <c r="M337" s="4" t="n"/>
+      <c r="N337" s="4" t="n"/>
+      <c r="O337" s="4" t="n"/>
+      <c r="P337" s="4" t="n"/>
+      <c r="Q337" s="4" t="n"/>
+      <c r="R337" s="4" t="n"/>
+      <c r="S337" s="4" t="n"/>
+      <c r="T337" s="4" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="4" t="n"/>
@@ -5910,6 +9514,15 @@
       <c r="I338" s="4" t="n"/>
       <c r="J338" s="4" t="n"/>
       <c r="K338" s="4" t="n"/>
+      <c r="L338" s="4" t="n"/>
+      <c r="M338" s="4" t="n"/>
+      <c r="N338" s="4" t="n"/>
+      <c r="O338" s="4" t="n"/>
+      <c r="P338" s="4" t="n"/>
+      <c r="Q338" s="4" t="n"/>
+      <c r="R338" s="4" t="n"/>
+      <c r="S338" s="4" t="n"/>
+      <c r="T338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="4" t="n"/>
@@ -5923,6 +9536,15 @@
       <c r="I339" s="4" t="n"/>
       <c r="J339" s="4" t="n"/>
       <c r="K339" s="4" t="n"/>
+      <c r="L339" s="4" t="n"/>
+      <c r="M339" s="4" t="n"/>
+      <c r="N339" s="4" t="n"/>
+      <c r="O339" s="4" t="n"/>
+      <c r="P339" s="4" t="n"/>
+      <c r="Q339" s="4" t="n"/>
+      <c r="R339" s="4" t="n"/>
+      <c r="S339" s="4" t="n"/>
+      <c r="T339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="4" t="n"/>
@@ -5936,6 +9558,15 @@
       <c r="I340" s="4" t="n"/>
       <c r="J340" s="4" t="n"/>
       <c r="K340" s="4" t="n"/>
+      <c r="L340" s="4" t="n"/>
+      <c r="M340" s="4" t="n"/>
+      <c r="N340" s="4" t="n"/>
+      <c r="O340" s="4" t="n"/>
+      <c r="P340" s="4" t="n"/>
+      <c r="Q340" s="4" t="n"/>
+      <c r="R340" s="4" t="n"/>
+      <c r="S340" s="4" t="n"/>
+      <c r="T340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="4" t="n"/>
@@ -5949,6 +9580,15 @@
       <c r="I341" s="4" t="n"/>
       <c r="J341" s="4" t="n"/>
       <c r="K341" s="4" t="n"/>
+      <c r="L341" s="4" t="n"/>
+      <c r="M341" s="4" t="n"/>
+      <c r="N341" s="4" t="n"/>
+      <c r="O341" s="4" t="n"/>
+      <c r="P341" s="4" t="n"/>
+      <c r="Q341" s="4" t="n"/>
+      <c r="R341" s="4" t="n"/>
+      <c r="S341" s="4" t="n"/>
+      <c r="T341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="4" t="n"/>
@@ -5962,6 +9602,15 @@
       <c r="I342" s="4" t="n"/>
       <c r="J342" s="4" t="n"/>
       <c r="K342" s="4" t="n"/>
+      <c r="L342" s="4" t="n"/>
+      <c r="M342" s="4" t="n"/>
+      <c r="N342" s="4" t="n"/>
+      <c r="O342" s="4" t="n"/>
+      <c r="P342" s="4" t="n"/>
+      <c r="Q342" s="4" t="n"/>
+      <c r="R342" s="4" t="n"/>
+      <c r="S342" s="4" t="n"/>
+      <c r="T342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="4" t="n"/>
@@ -5975,6 +9624,15 @@
       <c r="I343" s="4" t="n"/>
       <c r="J343" s="4" t="n"/>
       <c r="K343" s="4" t="n"/>
+      <c r="L343" s="4" t="n"/>
+      <c r="M343" s="4" t="n"/>
+      <c r="N343" s="4" t="n"/>
+      <c r="O343" s="4" t="n"/>
+      <c r="P343" s="4" t="n"/>
+      <c r="Q343" s="4" t="n"/>
+      <c r="R343" s="4" t="n"/>
+      <c r="S343" s="4" t="n"/>
+      <c r="T343" s="4" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="4" t="n"/>
@@ -5988,6 +9646,15 @@
       <c r="I344" s="4" t="n"/>
       <c r="J344" s="4" t="n"/>
       <c r="K344" s="4" t="n"/>
+      <c r="L344" s="4" t="n"/>
+      <c r="M344" s="4" t="n"/>
+      <c r="N344" s="4" t="n"/>
+      <c r="O344" s="4" t="n"/>
+      <c r="P344" s="4" t="n"/>
+      <c r="Q344" s="4" t="n"/>
+      <c r="R344" s="4" t="n"/>
+      <c r="S344" s="4" t="n"/>
+      <c r="T344" s="4" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n"/>
@@ -6001,6 +9668,15 @@
       <c r="I345" s="4" t="n"/>
       <c r="J345" s="4" t="n"/>
       <c r="K345" s="4" t="n"/>
+      <c r="L345" s="4" t="n"/>
+      <c r="M345" s="4" t="n"/>
+      <c r="N345" s="4" t="n"/>
+      <c r="O345" s="4" t="n"/>
+      <c r="P345" s="4" t="n"/>
+      <c r="Q345" s="4" t="n"/>
+      <c r="R345" s="4" t="n"/>
+      <c r="S345" s="4" t="n"/>
+      <c r="T345" s="4" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="4" t="n"/>
@@ -6014,6 +9690,15 @@
       <c r="I346" s="4" t="n"/>
       <c r="J346" s="4" t="n"/>
       <c r="K346" s="4" t="n"/>
+      <c r="L346" s="4" t="n"/>
+      <c r="M346" s="4" t="n"/>
+      <c r="N346" s="4" t="n"/>
+      <c r="O346" s="4" t="n"/>
+      <c r="P346" s="4" t="n"/>
+      <c r="Q346" s="4" t="n"/>
+      <c r="R346" s="4" t="n"/>
+      <c r="S346" s="4" t="n"/>
+      <c r="T346" s="4" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n"/>
@@ -6027,6 +9712,15 @@
       <c r="I347" s="4" t="n"/>
       <c r="J347" s="4" t="n"/>
       <c r="K347" s="4" t="n"/>
+      <c r="L347" s="4" t="n"/>
+      <c r="M347" s="4" t="n"/>
+      <c r="N347" s="4" t="n"/>
+      <c r="O347" s="4" t="n"/>
+      <c r="P347" s="4" t="n"/>
+      <c r="Q347" s="4" t="n"/>
+      <c r="R347" s="4" t="n"/>
+      <c r="S347" s="4" t="n"/>
+      <c r="T347" s="4" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="4" t="n"/>
@@ -6040,6 +9734,15 @@
       <c r="I348" s="4" t="n"/>
       <c r="J348" s="4" t="n"/>
       <c r="K348" s="4" t="n"/>
+      <c r="L348" s="4" t="n"/>
+      <c r="M348" s="4" t="n"/>
+      <c r="N348" s="4" t="n"/>
+      <c r="O348" s="4" t="n"/>
+      <c r="P348" s="4" t="n"/>
+      <c r="Q348" s="4" t="n"/>
+      <c r="R348" s="4" t="n"/>
+      <c r="S348" s="4" t="n"/>
+      <c r="T348" s="4" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="4" t="n"/>
@@ -6053,6 +9756,15 @@
       <c r="I349" s="4" t="n"/>
       <c r="J349" s="4" t="n"/>
       <c r="K349" s="4" t="n"/>
+      <c r="L349" s="4" t="n"/>
+      <c r="M349" s="4" t="n"/>
+      <c r="N349" s="4" t="n"/>
+      <c r="O349" s="4" t="n"/>
+      <c r="P349" s="4" t="n"/>
+      <c r="Q349" s="4" t="n"/>
+      <c r="R349" s="4" t="n"/>
+      <c r="S349" s="4" t="n"/>
+      <c r="T349" s="4" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="4" t="n"/>
@@ -6066,6 +9778,15 @@
       <c r="I350" s="4" t="n"/>
       <c r="J350" s="4" t="n"/>
       <c r="K350" s="4" t="n"/>
+      <c r="L350" s="4" t="n"/>
+      <c r="M350" s="4" t="n"/>
+      <c r="N350" s="4" t="n"/>
+      <c r="O350" s="4" t="n"/>
+      <c r="P350" s="4" t="n"/>
+      <c r="Q350" s="4" t="n"/>
+      <c r="R350" s="4" t="n"/>
+      <c r="S350" s="4" t="n"/>
+      <c r="T350" s="4" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="4" t="n"/>
@@ -6079,6 +9800,15 @@
       <c r="I351" s="4" t="n"/>
       <c r="J351" s="4" t="n"/>
       <c r="K351" s="4" t="n"/>
+      <c r="L351" s="4" t="n"/>
+      <c r="M351" s="4" t="n"/>
+      <c r="N351" s="4" t="n"/>
+      <c r="O351" s="4" t="n"/>
+      <c r="P351" s="4" t="n"/>
+      <c r="Q351" s="4" t="n"/>
+      <c r="R351" s="4" t="n"/>
+      <c r="S351" s="4" t="n"/>
+      <c r="T351" s="4" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="4" t="n"/>
@@ -6092,6 +9822,15 @@
       <c r="I352" s="4" t="n"/>
       <c r="J352" s="4" t="n"/>
       <c r="K352" s="4" t="n"/>
+      <c r="L352" s="4" t="n"/>
+      <c r="M352" s="4" t="n"/>
+      <c r="N352" s="4" t="n"/>
+      <c r="O352" s="4" t="n"/>
+      <c r="P352" s="4" t="n"/>
+      <c r="Q352" s="4" t="n"/>
+      <c r="R352" s="4" t="n"/>
+      <c r="S352" s="4" t="n"/>
+      <c r="T352" s="4" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="4" t="n"/>
@@ -6105,6 +9844,15 @@
       <c r="I353" s="4" t="n"/>
       <c r="J353" s="4" t="n"/>
       <c r="K353" s="4" t="n"/>
+      <c r="L353" s="4" t="n"/>
+      <c r="M353" s="4" t="n"/>
+      <c r="N353" s="4" t="n"/>
+      <c r="O353" s="4" t="n"/>
+      <c r="P353" s="4" t="n"/>
+      <c r="Q353" s="4" t="n"/>
+      <c r="R353" s="4" t="n"/>
+      <c r="S353" s="4" t="n"/>
+      <c r="T353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="4" t="n"/>
@@ -6118,6 +9866,15 @@
       <c r="I354" s="4" t="n"/>
       <c r="J354" s="4" t="n"/>
       <c r="K354" s="4" t="n"/>
+      <c r="L354" s="4" t="n"/>
+      <c r="M354" s="4" t="n"/>
+      <c r="N354" s="4" t="n"/>
+      <c r="O354" s="4" t="n"/>
+      <c r="P354" s="4" t="n"/>
+      <c r="Q354" s="4" t="n"/>
+      <c r="R354" s="4" t="n"/>
+      <c r="S354" s="4" t="n"/>
+      <c r="T354" s="4" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="4" t="n"/>
@@ -6131,6 +9888,15 @@
       <c r="I355" s="4" t="n"/>
       <c r="J355" s="4" t="n"/>
       <c r="K355" s="4" t="n"/>
+      <c r="L355" s="4" t="n"/>
+      <c r="M355" s="4" t="n"/>
+      <c r="N355" s="4" t="n"/>
+      <c r="O355" s="4" t="n"/>
+      <c r="P355" s="4" t="n"/>
+      <c r="Q355" s="4" t="n"/>
+      <c r="R355" s="4" t="n"/>
+      <c r="S355" s="4" t="n"/>
+      <c r="T355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="4" t="n"/>
@@ -6144,6 +9910,15 @@
       <c r="I356" s="4" t="n"/>
       <c r="J356" s="4" t="n"/>
       <c r="K356" s="4" t="n"/>
+      <c r="L356" s="4" t="n"/>
+      <c r="M356" s="4" t="n"/>
+      <c r="N356" s="4" t="n"/>
+      <c r="O356" s="4" t="n"/>
+      <c r="P356" s="4" t="n"/>
+      <c r="Q356" s="4" t="n"/>
+      <c r="R356" s="4" t="n"/>
+      <c r="S356" s="4" t="n"/>
+      <c r="T356" s="4" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="4" t="n"/>
@@ -6157,6 +9932,15 @@
       <c r="I357" s="4" t="n"/>
       <c r="J357" s="4" t="n"/>
       <c r="K357" s="4" t="n"/>
+      <c r="L357" s="4" t="n"/>
+      <c r="M357" s="4" t="n"/>
+      <c r="N357" s="4" t="n"/>
+      <c r="O357" s="4" t="n"/>
+      <c r="P357" s="4" t="n"/>
+      <c r="Q357" s="4" t="n"/>
+      <c r="R357" s="4" t="n"/>
+      <c r="S357" s="4" t="n"/>
+      <c r="T357" s="4" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="4" t="n"/>
@@ -6170,6 +9954,15 @@
       <c r="I358" s="4" t="n"/>
       <c r="J358" s="4" t="n"/>
       <c r="K358" s="4" t="n"/>
+      <c r="L358" s="4" t="n"/>
+      <c r="M358" s="4" t="n"/>
+      <c r="N358" s="4" t="n"/>
+      <c r="O358" s="4" t="n"/>
+      <c r="P358" s="4" t="n"/>
+      <c r="Q358" s="4" t="n"/>
+      <c r="R358" s="4" t="n"/>
+      <c r="S358" s="4" t="n"/>
+      <c r="T358" s="4" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n"/>
@@ -6183,6 +9976,15 @@
       <c r="I359" s="4" t="n"/>
       <c r="J359" s="4" t="n"/>
       <c r="K359" s="4" t="n"/>
+      <c r="L359" s="4" t="n"/>
+      <c r="M359" s="4" t="n"/>
+      <c r="N359" s="4" t="n"/>
+      <c r="O359" s="4" t="n"/>
+      <c r="P359" s="4" t="n"/>
+      <c r="Q359" s="4" t="n"/>
+      <c r="R359" s="4" t="n"/>
+      <c r="S359" s="4" t="n"/>
+      <c r="T359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="4" t="n"/>
@@ -6196,6 +9998,15 @@
       <c r="I360" s="4" t="n"/>
       <c r="J360" s="4" t="n"/>
       <c r="K360" s="4" t="n"/>
+      <c r="L360" s="4" t="n"/>
+      <c r="M360" s="4" t="n"/>
+      <c r="N360" s="4" t="n"/>
+      <c r="O360" s="4" t="n"/>
+      <c r="P360" s="4" t="n"/>
+      <c r="Q360" s="4" t="n"/>
+      <c r="R360" s="4" t="n"/>
+      <c r="S360" s="4" t="n"/>
+      <c r="T360" s="4" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="4" t="n"/>
@@ -6209,6 +10020,15 @@
       <c r="I361" s="4" t="n"/>
       <c r="J361" s="4" t="n"/>
       <c r="K361" s="4" t="n"/>
+      <c r="L361" s="4" t="n"/>
+      <c r="M361" s="4" t="n"/>
+      <c r="N361" s="4" t="n"/>
+      <c r="O361" s="4" t="n"/>
+      <c r="P361" s="4" t="n"/>
+      <c r="Q361" s="4" t="n"/>
+      <c r="R361" s="4" t="n"/>
+      <c r="S361" s="4" t="n"/>
+      <c r="T361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="4" t="n"/>
@@ -6222,6 +10042,15 @@
       <c r="I362" s="4" t="n"/>
       <c r="J362" s="4" t="n"/>
       <c r="K362" s="4" t="n"/>
+      <c r="L362" s="4" t="n"/>
+      <c r="M362" s="4" t="n"/>
+      <c r="N362" s="4" t="n"/>
+      <c r="O362" s="4" t="n"/>
+      <c r="P362" s="4" t="n"/>
+      <c r="Q362" s="4" t="n"/>
+      <c r="R362" s="4" t="n"/>
+      <c r="S362" s="4" t="n"/>
+      <c r="T362" s="4" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="4" t="n"/>
@@ -6235,6 +10064,15 @@
       <c r="I363" s="4" t="n"/>
       <c r="J363" s="4" t="n"/>
       <c r="K363" s="4" t="n"/>
+      <c r="L363" s="4" t="n"/>
+      <c r="M363" s="4" t="n"/>
+      <c r="N363" s="4" t="n"/>
+      <c r="O363" s="4" t="n"/>
+      <c r="P363" s="4" t="n"/>
+      <c r="Q363" s="4" t="n"/>
+      <c r="R363" s="4" t="n"/>
+      <c r="S363" s="4" t="n"/>
+      <c r="T363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="4" t="n"/>
@@ -6248,6 +10086,15 @@
       <c r="I364" s="4" t="n"/>
       <c r="J364" s="4" t="n"/>
       <c r="K364" s="4" t="n"/>
+      <c r="L364" s="4" t="n"/>
+      <c r="M364" s="4" t="n"/>
+      <c r="N364" s="4" t="n"/>
+      <c r="O364" s="4" t="n"/>
+      <c r="P364" s="4" t="n"/>
+      <c r="Q364" s="4" t="n"/>
+      <c r="R364" s="4" t="n"/>
+      <c r="S364" s="4" t="n"/>
+      <c r="T364" s="4" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="4" t="n"/>
@@ -6261,6 +10108,15 @@
       <c r="I365" s="4" t="n"/>
       <c r="J365" s="4" t="n"/>
       <c r="K365" s="4" t="n"/>
+      <c r="L365" s="4" t="n"/>
+      <c r="M365" s="4" t="n"/>
+      <c r="N365" s="4" t="n"/>
+      <c r="O365" s="4" t="n"/>
+      <c r="P365" s="4" t="n"/>
+      <c r="Q365" s="4" t="n"/>
+      <c r="R365" s="4" t="n"/>
+      <c r="S365" s="4" t="n"/>
+      <c r="T365" s="4" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="4" t="n"/>
@@ -6274,6 +10130,15 @@
       <c r="I366" s="4" t="n"/>
       <c r="J366" s="4" t="n"/>
       <c r="K366" s="4" t="n"/>
+      <c r="L366" s="4" t="n"/>
+      <c r="M366" s="4" t="n"/>
+      <c r="N366" s="4" t="n"/>
+      <c r="O366" s="4" t="n"/>
+      <c r="P366" s="4" t="n"/>
+      <c r="Q366" s="4" t="n"/>
+      <c r="R366" s="4" t="n"/>
+      <c r="S366" s="4" t="n"/>
+      <c r="T366" s="4" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="4" t="n"/>
@@ -6287,6 +10152,15 @@
       <c r="I367" s="4" t="n"/>
       <c r="J367" s="4" t="n"/>
       <c r="K367" s="4" t="n"/>
+      <c r="L367" s="4" t="n"/>
+      <c r="M367" s="4" t="n"/>
+      <c r="N367" s="4" t="n"/>
+      <c r="O367" s="4" t="n"/>
+      <c r="P367" s="4" t="n"/>
+      <c r="Q367" s="4" t="n"/>
+      <c r="R367" s="4" t="n"/>
+      <c r="S367" s="4" t="n"/>
+      <c r="T367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="4" t="n"/>
@@ -6300,6 +10174,15 @@
       <c r="I368" s="4" t="n"/>
       <c r="J368" s="4" t="n"/>
       <c r="K368" s="4" t="n"/>
+      <c r="L368" s="4" t="n"/>
+      <c r="M368" s="4" t="n"/>
+      <c r="N368" s="4" t="n"/>
+      <c r="O368" s="4" t="n"/>
+      <c r="P368" s="4" t="n"/>
+      <c r="Q368" s="4" t="n"/>
+      <c r="R368" s="4" t="n"/>
+      <c r="S368" s="4" t="n"/>
+      <c r="T368" s="4" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="4" t="n"/>
@@ -6313,6 +10196,15 @@
       <c r="I369" s="4" t="n"/>
       <c r="J369" s="4" t="n"/>
       <c r="K369" s="4" t="n"/>
+      <c r="L369" s="4" t="n"/>
+      <c r="M369" s="4" t="n"/>
+      <c r="N369" s="4" t="n"/>
+      <c r="O369" s="4" t="n"/>
+      <c r="P369" s="4" t="n"/>
+      <c r="Q369" s="4" t="n"/>
+      <c r="R369" s="4" t="n"/>
+      <c r="S369" s="4" t="n"/>
+      <c r="T369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="4" t="n"/>
@@ -6326,6 +10218,15 @@
       <c r="I370" s="4" t="n"/>
       <c r="J370" s="4" t="n"/>
       <c r="K370" s="4" t="n"/>
+      <c r="L370" s="4" t="n"/>
+      <c r="M370" s="4" t="n"/>
+      <c r="N370" s="4" t="n"/>
+      <c r="O370" s="4" t="n"/>
+      <c r="P370" s="4" t="n"/>
+      <c r="Q370" s="4" t="n"/>
+      <c r="R370" s="4" t="n"/>
+      <c r="S370" s="4" t="n"/>
+      <c r="T370" s="4" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="4" t="n"/>
@@ -6339,6 +10240,15 @@
       <c r="I371" s="4" t="n"/>
       <c r="J371" s="4" t="n"/>
       <c r="K371" s="4" t="n"/>
+      <c r="L371" s="4" t="n"/>
+      <c r="M371" s="4" t="n"/>
+      <c r="N371" s="4" t="n"/>
+      <c r="O371" s="4" t="n"/>
+      <c r="P371" s="4" t="n"/>
+      <c r="Q371" s="4" t="n"/>
+      <c r="R371" s="4" t="n"/>
+      <c r="S371" s="4" t="n"/>
+      <c r="T371" s="4" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="4" t="n"/>
@@ -6352,6 +10262,15 @@
       <c r="I372" s="4" t="n"/>
       <c r="J372" s="4" t="n"/>
       <c r="K372" s="4" t="n"/>
+      <c r="L372" s="4" t="n"/>
+      <c r="M372" s="4" t="n"/>
+      <c r="N372" s="4" t="n"/>
+      <c r="O372" s="4" t="n"/>
+      <c r="P372" s="4" t="n"/>
+      <c r="Q372" s="4" t="n"/>
+      <c r="R372" s="4" t="n"/>
+      <c r="S372" s="4" t="n"/>
+      <c r="T372" s="4" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="4" t="n"/>
@@ -6365,6 +10284,15 @@
       <c r="I373" s="4" t="n"/>
       <c r="J373" s="4" t="n"/>
       <c r="K373" s="4" t="n"/>
+      <c r="L373" s="4" t="n"/>
+      <c r="M373" s="4" t="n"/>
+      <c r="N373" s="4" t="n"/>
+      <c r="O373" s="4" t="n"/>
+      <c r="P373" s="4" t="n"/>
+      <c r="Q373" s="4" t="n"/>
+      <c r="R373" s="4" t="n"/>
+      <c r="S373" s="4" t="n"/>
+      <c r="T373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="4" t="n"/>
@@ -6378,6 +10306,15 @@
       <c r="I374" s="4" t="n"/>
       <c r="J374" s="4" t="n"/>
       <c r="K374" s="4" t="n"/>
+      <c r="L374" s="4" t="n"/>
+      <c r="M374" s="4" t="n"/>
+      <c r="N374" s="4" t="n"/>
+      <c r="O374" s="4" t="n"/>
+      <c r="P374" s="4" t="n"/>
+      <c r="Q374" s="4" t="n"/>
+      <c r="R374" s="4" t="n"/>
+      <c r="S374" s="4" t="n"/>
+      <c r="T374" s="4" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="4" t="n"/>
@@ -6391,6 +10328,15 @@
       <c r="I375" s="4" t="n"/>
       <c r="J375" s="4" t="n"/>
       <c r="K375" s="4" t="n"/>
+      <c r="L375" s="4" t="n"/>
+      <c r="M375" s="4" t="n"/>
+      <c r="N375" s="4" t="n"/>
+      <c r="O375" s="4" t="n"/>
+      <c r="P375" s="4" t="n"/>
+      <c r="Q375" s="4" t="n"/>
+      <c r="R375" s="4" t="n"/>
+      <c r="S375" s="4" t="n"/>
+      <c r="T375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="4" t="n"/>
@@ -6404,6 +10350,15 @@
       <c r="I376" s="4" t="n"/>
       <c r="J376" s="4" t="n"/>
       <c r="K376" s="4" t="n"/>
+      <c r="L376" s="4" t="n"/>
+      <c r="M376" s="4" t="n"/>
+      <c r="N376" s="4" t="n"/>
+      <c r="O376" s="4" t="n"/>
+      <c r="P376" s="4" t="n"/>
+      <c r="Q376" s="4" t="n"/>
+      <c r="R376" s="4" t="n"/>
+      <c r="S376" s="4" t="n"/>
+      <c r="T376" s="4" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="4" t="n"/>
@@ -6417,6 +10372,15 @@
       <c r="I377" s="4" t="n"/>
       <c r="J377" s="4" t="n"/>
       <c r="K377" s="4" t="n"/>
+      <c r="L377" s="4" t="n"/>
+      <c r="M377" s="4" t="n"/>
+      <c r="N377" s="4" t="n"/>
+      <c r="O377" s="4" t="n"/>
+      <c r="P377" s="4" t="n"/>
+      <c r="Q377" s="4" t="n"/>
+      <c r="R377" s="4" t="n"/>
+      <c r="S377" s="4" t="n"/>
+      <c r="T377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="4" t="n"/>
@@ -6430,6 +10394,15 @@
       <c r="I378" s="4" t="n"/>
       <c r="J378" s="4" t="n"/>
       <c r="K378" s="4" t="n"/>
+      <c r="L378" s="4" t="n"/>
+      <c r="M378" s="4" t="n"/>
+      <c r="N378" s="4" t="n"/>
+      <c r="O378" s="4" t="n"/>
+      <c r="P378" s="4" t="n"/>
+      <c r="Q378" s="4" t="n"/>
+      <c r="R378" s="4" t="n"/>
+      <c r="S378" s="4" t="n"/>
+      <c r="T378" s="4" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="4" t="n"/>
@@ -6443,6 +10416,15 @@
       <c r="I379" s="4" t="n"/>
       <c r="J379" s="4" t="n"/>
       <c r="K379" s="4" t="n"/>
+      <c r="L379" s="4" t="n"/>
+      <c r="M379" s="4" t="n"/>
+      <c r="N379" s="4" t="n"/>
+      <c r="O379" s="4" t="n"/>
+      <c r="P379" s="4" t="n"/>
+      <c r="Q379" s="4" t="n"/>
+      <c r="R379" s="4" t="n"/>
+      <c r="S379" s="4" t="n"/>
+      <c r="T379" s="4" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="4" t="n"/>
@@ -6456,6 +10438,15 @@
       <c r="I380" s="4" t="n"/>
       <c r="J380" s="4" t="n"/>
       <c r="K380" s="4" t="n"/>
+      <c r="L380" s="4" t="n"/>
+      <c r="M380" s="4" t="n"/>
+      <c r="N380" s="4" t="n"/>
+      <c r="O380" s="4" t="n"/>
+      <c r="P380" s="4" t="n"/>
+      <c r="Q380" s="4" t="n"/>
+      <c r="R380" s="4" t="n"/>
+      <c r="S380" s="4" t="n"/>
+      <c r="T380" s="4" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="4" t="n"/>
@@ -6469,6 +10460,15 @@
       <c r="I381" s="4" t="n"/>
       <c r="J381" s="4" t="n"/>
       <c r="K381" s="4" t="n"/>
+      <c r="L381" s="4" t="n"/>
+      <c r="M381" s="4" t="n"/>
+      <c r="N381" s="4" t="n"/>
+      <c r="O381" s="4" t="n"/>
+      <c r="P381" s="4" t="n"/>
+      <c r="Q381" s="4" t="n"/>
+      <c r="R381" s="4" t="n"/>
+      <c r="S381" s="4" t="n"/>
+      <c r="T381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="4" t="n"/>
@@ -6482,6 +10482,15 @@
       <c r="I382" s="4" t="n"/>
       <c r="J382" s="4" t="n"/>
       <c r="K382" s="4" t="n"/>
+      <c r="L382" s="4" t="n"/>
+      <c r="M382" s="4" t="n"/>
+      <c r="N382" s="4" t="n"/>
+      <c r="O382" s="4" t="n"/>
+      <c r="P382" s="4" t="n"/>
+      <c r="Q382" s="4" t="n"/>
+      <c r="R382" s="4" t="n"/>
+      <c r="S382" s="4" t="n"/>
+      <c r="T382" s="4" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="4" t="n"/>
@@ -6495,6 +10504,15 @@
       <c r="I383" s="4" t="n"/>
       <c r="J383" s="4" t="n"/>
       <c r="K383" s="4" t="n"/>
+      <c r="L383" s="4" t="n"/>
+      <c r="M383" s="4" t="n"/>
+      <c r="N383" s="4" t="n"/>
+      <c r="O383" s="4" t="n"/>
+      <c r="P383" s="4" t="n"/>
+      <c r="Q383" s="4" t="n"/>
+      <c r="R383" s="4" t="n"/>
+      <c r="S383" s="4" t="n"/>
+      <c r="T383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="4" t="n"/>
@@ -6508,6 +10526,15 @@
       <c r="I384" s="4" t="n"/>
       <c r="J384" s="4" t="n"/>
       <c r="K384" s="4" t="n"/>
+      <c r="L384" s="4" t="n"/>
+      <c r="M384" s="4" t="n"/>
+      <c r="N384" s="4" t="n"/>
+      <c r="O384" s="4" t="n"/>
+      <c r="P384" s="4" t="n"/>
+      <c r="Q384" s="4" t="n"/>
+      <c r="R384" s="4" t="n"/>
+      <c r="S384" s="4" t="n"/>
+      <c r="T384" s="4" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="4" t="n"/>
@@ -6521,6 +10548,15 @@
       <c r="I385" s="4" t="n"/>
       <c r="J385" s="4" t="n"/>
       <c r="K385" s="4" t="n"/>
+      <c r="L385" s="4" t="n"/>
+      <c r="M385" s="4" t="n"/>
+      <c r="N385" s="4" t="n"/>
+      <c r="O385" s="4" t="n"/>
+      <c r="P385" s="4" t="n"/>
+      <c r="Q385" s="4" t="n"/>
+      <c r="R385" s="4" t="n"/>
+      <c r="S385" s="4" t="n"/>
+      <c r="T385" s="4" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="4" t="n"/>
@@ -6534,6 +10570,15 @@
       <c r="I386" s="4" t="n"/>
       <c r="J386" s="4" t="n"/>
       <c r="K386" s="4" t="n"/>
+      <c r="L386" s="4" t="n"/>
+      <c r="M386" s="4" t="n"/>
+      <c r="N386" s="4" t="n"/>
+      <c r="O386" s="4" t="n"/>
+      <c r="P386" s="4" t="n"/>
+      <c r="Q386" s="4" t="n"/>
+      <c r="R386" s="4" t="n"/>
+      <c r="S386" s="4" t="n"/>
+      <c r="T386" s="4" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="4" t="n"/>
@@ -6547,6 +10592,15 @@
       <c r="I387" s="4" t="n"/>
       <c r="J387" s="4" t="n"/>
       <c r="K387" s="4" t="n"/>
+      <c r="L387" s="4" t="n"/>
+      <c r="M387" s="4" t="n"/>
+      <c r="N387" s="4" t="n"/>
+      <c r="O387" s="4" t="n"/>
+      <c r="P387" s="4" t="n"/>
+      <c r="Q387" s="4" t="n"/>
+      <c r="R387" s="4" t="n"/>
+      <c r="S387" s="4" t="n"/>
+      <c r="T387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="4" t="n"/>
@@ -6560,6 +10614,15 @@
       <c r="I388" s="4" t="n"/>
       <c r="J388" s="4" t="n"/>
       <c r="K388" s="4" t="n"/>
+      <c r="L388" s="4" t="n"/>
+      <c r="M388" s="4" t="n"/>
+      <c r="N388" s="4" t="n"/>
+      <c r="O388" s="4" t="n"/>
+      <c r="P388" s="4" t="n"/>
+      <c r="Q388" s="4" t="n"/>
+      <c r="R388" s="4" t="n"/>
+      <c r="S388" s="4" t="n"/>
+      <c r="T388" s="4" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="4" t="n"/>
@@ -6573,6 +10636,15 @@
       <c r="I389" s="4" t="n"/>
       <c r="J389" s="4" t="n"/>
       <c r="K389" s="4" t="n"/>
+      <c r="L389" s="4" t="n"/>
+      <c r="M389" s="4" t="n"/>
+      <c r="N389" s="4" t="n"/>
+      <c r="O389" s="4" t="n"/>
+      <c r="P389" s="4" t="n"/>
+      <c r="Q389" s="4" t="n"/>
+      <c r="R389" s="4" t="n"/>
+      <c r="S389" s="4" t="n"/>
+      <c r="T389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="4" t="n"/>
@@ -6586,6 +10658,15 @@
       <c r="I390" s="4" t="n"/>
       <c r="J390" s="4" t="n"/>
       <c r="K390" s="4" t="n"/>
+      <c r="L390" s="4" t="n"/>
+      <c r="M390" s="4" t="n"/>
+      <c r="N390" s="4" t="n"/>
+      <c r="O390" s="4" t="n"/>
+      <c r="P390" s="4" t="n"/>
+      <c r="Q390" s="4" t="n"/>
+      <c r="R390" s="4" t="n"/>
+      <c r="S390" s="4" t="n"/>
+      <c r="T390" s="4" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="4" t="n"/>
@@ -6599,6 +10680,15 @@
       <c r="I391" s="4" t="n"/>
       <c r="J391" s="4" t="n"/>
       <c r="K391" s="4" t="n"/>
+      <c r="L391" s="4" t="n"/>
+      <c r="M391" s="4" t="n"/>
+      <c r="N391" s="4" t="n"/>
+      <c r="O391" s="4" t="n"/>
+      <c r="P391" s="4" t="n"/>
+      <c r="Q391" s="4" t="n"/>
+      <c r="R391" s="4" t="n"/>
+      <c r="S391" s="4" t="n"/>
+      <c r="T391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="4" t="n"/>
@@ -6612,6 +10702,15 @@
       <c r="I392" s="4" t="n"/>
       <c r="J392" s="4" t="n"/>
       <c r="K392" s="4" t="n"/>
+      <c r="L392" s="4" t="n"/>
+      <c r="M392" s="4" t="n"/>
+      <c r="N392" s="4" t="n"/>
+      <c r="O392" s="4" t="n"/>
+      <c r="P392" s="4" t="n"/>
+      <c r="Q392" s="4" t="n"/>
+      <c r="R392" s="4" t="n"/>
+      <c r="S392" s="4" t="n"/>
+      <c r="T392" s="4" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="4" t="n"/>
@@ -6625,6 +10724,15 @@
       <c r="I393" s="4" t="n"/>
       <c r="J393" s="4" t="n"/>
       <c r="K393" s="4" t="n"/>
+      <c r="L393" s="4" t="n"/>
+      <c r="M393" s="4" t="n"/>
+      <c r="N393" s="4" t="n"/>
+      <c r="O393" s="4" t="n"/>
+      <c r="P393" s="4" t="n"/>
+      <c r="Q393" s="4" t="n"/>
+      <c r="R393" s="4" t="n"/>
+      <c r="S393" s="4" t="n"/>
+      <c r="T393" s="4" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="4" t="n"/>
@@ -6638,6 +10746,15 @@
       <c r="I394" s="4" t="n"/>
       <c r="J394" s="4" t="n"/>
       <c r="K394" s="4" t="n"/>
+      <c r="L394" s="4" t="n"/>
+      <c r="M394" s="4" t="n"/>
+      <c r="N394" s="4" t="n"/>
+      <c r="O394" s="4" t="n"/>
+      <c r="P394" s="4" t="n"/>
+      <c r="Q394" s="4" t="n"/>
+      <c r="R394" s="4" t="n"/>
+      <c r="S394" s="4" t="n"/>
+      <c r="T394" s="4" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="4" t="n"/>
@@ -6651,6 +10768,15 @@
       <c r="I395" s="4" t="n"/>
       <c r="J395" s="4" t="n"/>
       <c r="K395" s="4" t="n"/>
+      <c r="L395" s="4" t="n"/>
+      <c r="M395" s="4" t="n"/>
+      <c r="N395" s="4" t="n"/>
+      <c r="O395" s="4" t="n"/>
+      <c r="P395" s="4" t="n"/>
+      <c r="Q395" s="4" t="n"/>
+      <c r="R395" s="4" t="n"/>
+      <c r="S395" s="4" t="n"/>
+      <c r="T395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="4" t="n"/>
@@ -6664,6 +10790,15 @@
       <c r="I396" s="4" t="n"/>
       <c r="J396" s="4" t="n"/>
       <c r="K396" s="4" t="n"/>
+      <c r="L396" s="4" t="n"/>
+      <c r="M396" s="4" t="n"/>
+      <c r="N396" s="4" t="n"/>
+      <c r="O396" s="4" t="n"/>
+      <c r="P396" s="4" t="n"/>
+      <c r="Q396" s="4" t="n"/>
+      <c r="R396" s="4" t="n"/>
+      <c r="S396" s="4" t="n"/>
+      <c r="T396" s="4" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="4" t="n"/>
@@ -6677,6 +10812,15 @@
       <c r="I397" s="4" t="n"/>
       <c r="J397" s="4" t="n"/>
       <c r="K397" s="4" t="n"/>
+      <c r="L397" s="4" t="n"/>
+      <c r="M397" s="4" t="n"/>
+      <c r="N397" s="4" t="n"/>
+      <c r="O397" s="4" t="n"/>
+      <c r="P397" s="4" t="n"/>
+      <c r="Q397" s="4" t="n"/>
+      <c r="R397" s="4" t="n"/>
+      <c r="S397" s="4" t="n"/>
+      <c r="T397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="4" t="n"/>
@@ -6690,6 +10834,15 @@
       <c r="I398" s="4" t="n"/>
       <c r="J398" s="4" t="n"/>
       <c r="K398" s="4" t="n"/>
+      <c r="L398" s="4" t="n"/>
+      <c r="M398" s="4" t="n"/>
+      <c r="N398" s="4" t="n"/>
+      <c r="O398" s="4" t="n"/>
+      <c r="P398" s="4" t="n"/>
+      <c r="Q398" s="4" t="n"/>
+      <c r="R398" s="4" t="n"/>
+      <c r="S398" s="4" t="n"/>
+      <c r="T398" s="4" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="4" t="n"/>
@@ -6703,6 +10856,15 @@
       <c r="I399" s="4" t="n"/>
       <c r="J399" s="4" t="n"/>
       <c r="K399" s="4" t="n"/>
+      <c r="L399" s="4" t="n"/>
+      <c r="M399" s="4" t="n"/>
+      <c r="N399" s="4" t="n"/>
+      <c r="O399" s="4" t="n"/>
+      <c r="P399" s="4" t="n"/>
+      <c r="Q399" s="4" t="n"/>
+      <c r="R399" s="4" t="n"/>
+      <c r="S399" s="4" t="n"/>
+      <c r="T399" s="4" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="4" t="n"/>
@@ -6716,6 +10878,15 @@
       <c r="I400" s="4" t="n"/>
       <c r="J400" s="4" t="n"/>
       <c r="K400" s="4" t="n"/>
+      <c r="L400" s="4" t="n"/>
+      <c r="M400" s="4" t="n"/>
+      <c r="N400" s="4" t="n"/>
+      <c r="O400" s="4" t="n"/>
+      <c r="P400" s="4" t="n"/>
+      <c r="Q400" s="4" t="n"/>
+      <c r="R400" s="4" t="n"/>
+      <c r="S400" s="4" t="n"/>
+      <c r="T400" s="4" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n"/>
@@ -6729,6 +10900,15 @@
       <c r="I401" s="4" t="n"/>
       <c r="J401" s="4" t="n"/>
       <c r="K401" s="4" t="n"/>
+      <c r="L401" s="4" t="n"/>
+      <c r="M401" s="4" t="n"/>
+      <c r="N401" s="4" t="n"/>
+      <c r="O401" s="4" t="n"/>
+      <c r="P401" s="4" t="n"/>
+      <c r="Q401" s="4" t="n"/>
+      <c r="R401" s="4" t="n"/>
+      <c r="S401" s="4" t="n"/>
+      <c r="T401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="4" t="n"/>
@@ -6742,6 +10922,15 @@
       <c r="I402" s="4" t="n"/>
       <c r="J402" s="4" t="n"/>
       <c r="K402" s="4" t="n"/>
+      <c r="L402" s="4" t="n"/>
+      <c r="M402" s="4" t="n"/>
+      <c r="N402" s="4" t="n"/>
+      <c r="O402" s="4" t="n"/>
+      <c r="P402" s="4" t="n"/>
+      <c r="Q402" s="4" t="n"/>
+      <c r="R402" s="4" t="n"/>
+      <c r="S402" s="4" t="n"/>
+      <c r="T402" s="4" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="4" t="n"/>
@@ -6755,6 +10944,15 @@
       <c r="I403" s="4" t="n"/>
       <c r="J403" s="4" t="n"/>
       <c r="K403" s="4" t="n"/>
+      <c r="L403" s="4" t="n"/>
+      <c r="M403" s="4" t="n"/>
+      <c r="N403" s="4" t="n"/>
+      <c r="O403" s="4" t="n"/>
+      <c r="P403" s="4" t="n"/>
+      <c r="Q403" s="4" t="n"/>
+      <c r="R403" s="4" t="n"/>
+      <c r="S403" s="4" t="n"/>
+      <c r="T403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="4" t="n"/>
@@ -6768,6 +10966,15 @@
       <c r="I404" s="4" t="n"/>
       <c r="J404" s="4" t="n"/>
       <c r="K404" s="4" t="n"/>
+      <c r="L404" s="4" t="n"/>
+      <c r="M404" s="4" t="n"/>
+      <c r="N404" s="4" t="n"/>
+      <c r="O404" s="4" t="n"/>
+      <c r="P404" s="4" t="n"/>
+      <c r="Q404" s="4" t="n"/>
+      <c r="R404" s="4" t="n"/>
+      <c r="S404" s="4" t="n"/>
+      <c r="T404" s="4" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="4" t="n"/>
@@ -6781,6 +10988,15 @@
       <c r="I405" s="4" t="n"/>
       <c r="J405" s="4" t="n"/>
       <c r="K405" s="4" t="n"/>
+      <c r="L405" s="4" t="n"/>
+      <c r="M405" s="4" t="n"/>
+      <c r="N405" s="4" t="n"/>
+      <c r="O405" s="4" t="n"/>
+      <c r="P405" s="4" t="n"/>
+      <c r="Q405" s="4" t="n"/>
+      <c r="R405" s="4" t="n"/>
+      <c r="S405" s="4" t="n"/>
+      <c r="T405" s="4" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="4" t="n"/>
@@ -6794,6 +11010,15 @@
       <c r="I406" s="4" t="n"/>
       <c r="J406" s="4" t="n"/>
       <c r="K406" s="4" t="n"/>
+      <c r="L406" s="4" t="n"/>
+      <c r="M406" s="4" t="n"/>
+      <c r="N406" s="4" t="n"/>
+      <c r="O406" s="4" t="n"/>
+      <c r="P406" s="4" t="n"/>
+      <c r="Q406" s="4" t="n"/>
+      <c r="R406" s="4" t="n"/>
+      <c r="S406" s="4" t="n"/>
+      <c r="T406" s="4" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="4" t="n"/>
@@ -6807,6 +11032,15 @@
       <c r="I407" s="4" t="n"/>
       <c r="J407" s="4" t="n"/>
       <c r="K407" s="4" t="n"/>
+      <c r="L407" s="4" t="n"/>
+      <c r="M407" s="4" t="n"/>
+      <c r="N407" s="4" t="n"/>
+      <c r="O407" s="4" t="n"/>
+      <c r="P407" s="4" t="n"/>
+      <c r="Q407" s="4" t="n"/>
+      <c r="R407" s="4" t="n"/>
+      <c r="S407" s="4" t="n"/>
+      <c r="T407" s="4" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="4" t="n"/>
@@ -6820,6 +11054,15 @@
       <c r="I408" s="4" t="n"/>
       <c r="J408" s="4" t="n"/>
       <c r="K408" s="4" t="n"/>
+      <c r="L408" s="4" t="n"/>
+      <c r="M408" s="4" t="n"/>
+      <c r="N408" s="4" t="n"/>
+      <c r="O408" s="4" t="n"/>
+      <c r="P408" s="4" t="n"/>
+      <c r="Q408" s="4" t="n"/>
+      <c r="R408" s="4" t="n"/>
+      <c r="S408" s="4" t="n"/>
+      <c r="T408" s="4" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="4" t="n"/>
@@ -6833,6 +11076,15 @@
       <c r="I409" s="4" t="n"/>
       <c r="J409" s="4" t="n"/>
       <c r="K409" s="4" t="n"/>
+      <c r="L409" s="4" t="n"/>
+      <c r="M409" s="4" t="n"/>
+      <c r="N409" s="4" t="n"/>
+      <c r="O409" s="4" t="n"/>
+      <c r="P409" s="4" t="n"/>
+      <c r="Q409" s="4" t="n"/>
+      <c r="R409" s="4" t="n"/>
+      <c r="S409" s="4" t="n"/>
+      <c r="T409" s="4" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="4" t="n"/>
@@ -6846,6 +11098,15 @@
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="4" t="n"/>
       <c r="K410" s="4" t="n"/>
+      <c r="L410" s="4" t="n"/>
+      <c r="M410" s="4" t="n"/>
+      <c r="N410" s="4" t="n"/>
+      <c r="O410" s="4" t="n"/>
+      <c r="P410" s="4" t="n"/>
+      <c r="Q410" s="4" t="n"/>
+      <c r="R410" s="4" t="n"/>
+      <c r="S410" s="4" t="n"/>
+      <c r="T410" s="4" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="4" t="n"/>
@@ -6859,6 +11120,15 @@
       <c r="I411" s="4" t="n"/>
       <c r="J411" s="4" t="n"/>
       <c r="K411" s="4" t="n"/>
+      <c r="L411" s="4" t="n"/>
+      <c r="M411" s="4" t="n"/>
+      <c r="N411" s="4" t="n"/>
+      <c r="O411" s="4" t="n"/>
+      <c r="P411" s="4" t="n"/>
+      <c r="Q411" s="4" t="n"/>
+      <c r="R411" s="4" t="n"/>
+      <c r="S411" s="4" t="n"/>
+      <c r="T411" s="4" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="4" t="n"/>
@@ -6872,6 +11142,15 @@
       <c r="I412" s="4" t="n"/>
       <c r="J412" s="4" t="n"/>
       <c r="K412" s="4" t="n"/>
+      <c r="L412" s="4" t="n"/>
+      <c r="M412" s="4" t="n"/>
+      <c r="N412" s="4" t="n"/>
+      <c r="O412" s="4" t="n"/>
+      <c r="P412" s="4" t="n"/>
+      <c r="Q412" s="4" t="n"/>
+      <c r="R412" s="4" t="n"/>
+      <c r="S412" s="4" t="n"/>
+      <c r="T412" s="4" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="4" t="n"/>
@@ -6885,6 +11164,15 @@
       <c r="I413" s="4" t="n"/>
       <c r="J413" s="4" t="n"/>
       <c r="K413" s="4" t="n"/>
+      <c r="L413" s="4" t="n"/>
+      <c r="M413" s="4" t="n"/>
+      <c r="N413" s="4" t="n"/>
+      <c r="O413" s="4" t="n"/>
+      <c r="P413" s="4" t="n"/>
+      <c r="Q413" s="4" t="n"/>
+      <c r="R413" s="4" t="n"/>
+      <c r="S413" s="4" t="n"/>
+      <c r="T413" s="4" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="4" t="n"/>
@@ -6898,6 +11186,15 @@
       <c r="I414" s="4" t="n"/>
       <c r="J414" s="4" t="n"/>
       <c r="K414" s="4" t="n"/>
+      <c r="L414" s="4" t="n"/>
+      <c r="M414" s="4" t="n"/>
+      <c r="N414" s="4" t="n"/>
+      <c r="O414" s="4" t="n"/>
+      <c r="P414" s="4" t="n"/>
+      <c r="Q414" s="4" t="n"/>
+      <c r="R414" s="4" t="n"/>
+      <c r="S414" s="4" t="n"/>
+      <c r="T414" s="4" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="4" t="n"/>
@@ -6911,6 +11208,15 @@
       <c r="I415" s="4" t="n"/>
       <c r="J415" s="4" t="n"/>
       <c r="K415" s="4" t="n"/>
+      <c r="L415" s="4" t="n"/>
+      <c r="M415" s="4" t="n"/>
+      <c r="N415" s="4" t="n"/>
+      <c r="O415" s="4" t="n"/>
+      <c r="P415" s="4" t="n"/>
+      <c r="Q415" s="4" t="n"/>
+      <c r="R415" s="4" t="n"/>
+      <c r="S415" s="4" t="n"/>
+      <c r="T415" s="4" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="4" t="n"/>
@@ -6924,6 +11230,15 @@
       <c r="I416" s="4" t="n"/>
       <c r="J416" s="4" t="n"/>
       <c r="K416" s="4" t="n"/>
+      <c r="L416" s="4" t="n"/>
+      <c r="M416" s="4" t="n"/>
+      <c r="N416" s="4" t="n"/>
+      <c r="O416" s="4" t="n"/>
+      <c r="P416" s="4" t="n"/>
+      <c r="Q416" s="4" t="n"/>
+      <c r="R416" s="4" t="n"/>
+      <c r="S416" s="4" t="n"/>
+      <c r="T416" s="4" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="4" t="n"/>
@@ -6937,6 +11252,15 @@
       <c r="I417" s="4" t="n"/>
       <c r="J417" s="4" t="n"/>
       <c r="K417" s="4" t="n"/>
+      <c r="L417" s="4" t="n"/>
+      <c r="M417" s="4" t="n"/>
+      <c r="N417" s="4" t="n"/>
+      <c r="O417" s="4" t="n"/>
+      <c r="P417" s="4" t="n"/>
+      <c r="Q417" s="4" t="n"/>
+      <c r="R417" s="4" t="n"/>
+      <c r="S417" s="4" t="n"/>
+      <c r="T417" s="4" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="4" t="n"/>
@@ -6950,6 +11274,15 @@
       <c r="I418" s="4" t="n"/>
       <c r="J418" s="4" t="n"/>
       <c r="K418" s="4" t="n"/>
+      <c r="L418" s="4" t="n"/>
+      <c r="M418" s="4" t="n"/>
+      <c r="N418" s="4" t="n"/>
+      <c r="O418" s="4" t="n"/>
+      <c r="P418" s="4" t="n"/>
+      <c r="Q418" s="4" t="n"/>
+      <c r="R418" s="4" t="n"/>
+      <c r="S418" s="4" t="n"/>
+      <c r="T418" s="4" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="4" t="n"/>
@@ -6963,6 +11296,15 @@
       <c r="I419" s="4" t="n"/>
       <c r="J419" s="4" t="n"/>
       <c r="K419" s="4" t="n"/>
+      <c r="L419" s="4" t="n"/>
+      <c r="M419" s="4" t="n"/>
+      <c r="N419" s="4" t="n"/>
+      <c r="O419" s="4" t="n"/>
+      <c r="P419" s="4" t="n"/>
+      <c r="Q419" s="4" t="n"/>
+      <c r="R419" s="4" t="n"/>
+      <c r="S419" s="4" t="n"/>
+      <c r="T419" s="4" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="4" t="n"/>
@@ -6976,6 +11318,15 @@
       <c r="I420" s="4" t="n"/>
       <c r="J420" s="4" t="n"/>
       <c r="K420" s="4" t="n"/>
+      <c r="L420" s="4" t="n"/>
+      <c r="M420" s="4" t="n"/>
+      <c r="N420" s="4" t="n"/>
+      <c r="O420" s="4" t="n"/>
+      <c r="P420" s="4" t="n"/>
+      <c r="Q420" s="4" t="n"/>
+      <c r="R420" s="4" t="n"/>
+      <c r="S420" s="4" t="n"/>
+      <c r="T420" s="4" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="4" t="n"/>
@@ -6989,6 +11340,15 @@
       <c r="I421" s="4" t="n"/>
       <c r="J421" s="4" t="n"/>
       <c r="K421" s="4" t="n"/>
+      <c r="L421" s="4" t="n"/>
+      <c r="M421" s="4" t="n"/>
+      <c r="N421" s="4" t="n"/>
+      <c r="O421" s="4" t="n"/>
+      <c r="P421" s="4" t="n"/>
+      <c r="Q421" s="4" t="n"/>
+      <c r="R421" s="4" t="n"/>
+      <c r="S421" s="4" t="n"/>
+      <c r="T421" s="4" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="4" t="n"/>
@@ -7002,6 +11362,15 @@
       <c r="I422" s="4" t="n"/>
       <c r="J422" s="4" t="n"/>
       <c r="K422" s="4" t="n"/>
+      <c r="L422" s="4" t="n"/>
+      <c r="M422" s="4" t="n"/>
+      <c r="N422" s="4" t="n"/>
+      <c r="O422" s="4" t="n"/>
+      <c r="P422" s="4" t="n"/>
+      <c r="Q422" s="4" t="n"/>
+      <c r="R422" s="4" t="n"/>
+      <c r="S422" s="4" t="n"/>
+      <c r="T422" s="4" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="4" t="n"/>
@@ -7015,6 +11384,15 @@
       <c r="I423" s="4" t="n"/>
       <c r="J423" s="4" t="n"/>
       <c r="K423" s="4" t="n"/>
+      <c r="L423" s="4" t="n"/>
+      <c r="M423" s="4" t="n"/>
+      <c r="N423" s="4" t="n"/>
+      <c r="O423" s="4" t="n"/>
+      <c r="P423" s="4" t="n"/>
+      <c r="Q423" s="4" t="n"/>
+      <c r="R423" s="4" t="n"/>
+      <c r="S423" s="4" t="n"/>
+      <c r="T423" s="4" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="4" t="n"/>
@@ -7028,6 +11406,15 @@
       <c r="I424" s="4" t="n"/>
       <c r="J424" s="4" t="n"/>
       <c r="K424" s="4" t="n"/>
+      <c r="L424" s="4" t="n"/>
+      <c r="M424" s="4" t="n"/>
+      <c r="N424" s="4" t="n"/>
+      <c r="O424" s="4" t="n"/>
+      <c r="P424" s="4" t="n"/>
+      <c r="Q424" s="4" t="n"/>
+      <c r="R424" s="4" t="n"/>
+      <c r="S424" s="4" t="n"/>
+      <c r="T424" s="4" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="4" t="n"/>
@@ -7041,6 +11428,15 @@
       <c r="I425" s="4" t="n"/>
       <c r="J425" s="4" t="n"/>
       <c r="K425" s="4" t="n"/>
+      <c r="L425" s="4" t="n"/>
+      <c r="M425" s="4" t="n"/>
+      <c r="N425" s="4" t="n"/>
+      <c r="O425" s="4" t="n"/>
+      <c r="P425" s="4" t="n"/>
+      <c r="Q425" s="4" t="n"/>
+      <c r="R425" s="4" t="n"/>
+      <c r="S425" s="4" t="n"/>
+      <c r="T425" s="4" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="4" t="n"/>
@@ -7054,6 +11450,15 @@
       <c r="I426" s="4" t="n"/>
       <c r="J426" s="4" t="n"/>
       <c r="K426" s="4" t="n"/>
+      <c r="L426" s="4" t="n"/>
+      <c r="M426" s="4" t="n"/>
+      <c r="N426" s="4" t="n"/>
+      <c r="O426" s="4" t="n"/>
+      <c r="P426" s="4" t="n"/>
+      <c r="Q426" s="4" t="n"/>
+      <c r="R426" s="4" t="n"/>
+      <c r="S426" s="4" t="n"/>
+      <c r="T426" s="4" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="4" t="n"/>
@@ -7067,6 +11472,15 @@
       <c r="I427" s="4" t="n"/>
       <c r="J427" s="4" t="n"/>
       <c r="K427" s="4" t="n"/>
+      <c r="L427" s="4" t="n"/>
+      <c r="M427" s="4" t="n"/>
+      <c r="N427" s="4" t="n"/>
+      <c r="O427" s="4" t="n"/>
+      <c r="P427" s="4" t="n"/>
+      <c r="Q427" s="4" t="n"/>
+      <c r="R427" s="4" t="n"/>
+      <c r="S427" s="4" t="n"/>
+      <c r="T427" s="4" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="4" t="n"/>
@@ -7080,6 +11494,15 @@
       <c r="I428" s="4" t="n"/>
       <c r="J428" s="4" t="n"/>
       <c r="K428" s="4" t="n"/>
+      <c r="L428" s="4" t="n"/>
+      <c r="M428" s="4" t="n"/>
+      <c r="N428" s="4" t="n"/>
+      <c r="O428" s="4" t="n"/>
+      <c r="P428" s="4" t="n"/>
+      <c r="Q428" s="4" t="n"/>
+      <c r="R428" s="4" t="n"/>
+      <c r="S428" s="4" t="n"/>
+      <c r="T428" s="4" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="4" t="n"/>
@@ -7093,6 +11516,15 @@
       <c r="I429" s="4" t="n"/>
       <c r="J429" s="4" t="n"/>
       <c r="K429" s="4" t="n"/>
+      <c r="L429" s="4" t="n"/>
+      <c r="M429" s="4" t="n"/>
+      <c r="N429" s="4" t="n"/>
+      <c r="O429" s="4" t="n"/>
+      <c r="P429" s="4" t="n"/>
+      <c r="Q429" s="4" t="n"/>
+      <c r="R429" s="4" t="n"/>
+      <c r="S429" s="4" t="n"/>
+      <c r="T429" s="4" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="4" t="n"/>
@@ -7106,6 +11538,15 @@
       <c r="I430" s="4" t="n"/>
       <c r="J430" s="4" t="n"/>
       <c r="K430" s="4" t="n"/>
+      <c r="L430" s="4" t="n"/>
+      <c r="M430" s="4" t="n"/>
+      <c r="N430" s="4" t="n"/>
+      <c r="O430" s="4" t="n"/>
+      <c r="P430" s="4" t="n"/>
+      <c r="Q430" s="4" t="n"/>
+      <c r="R430" s="4" t="n"/>
+      <c r="S430" s="4" t="n"/>
+      <c r="T430" s="4" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="4" t="n"/>
@@ -7119,6 +11560,15 @@
       <c r="I431" s="4" t="n"/>
       <c r="J431" s="4" t="n"/>
       <c r="K431" s="4" t="n"/>
+      <c r="L431" s="4" t="n"/>
+      <c r="M431" s="4" t="n"/>
+      <c r="N431" s="4" t="n"/>
+      <c r="O431" s="4" t="n"/>
+      <c r="P431" s="4" t="n"/>
+      <c r="Q431" s="4" t="n"/>
+      <c r="R431" s="4" t="n"/>
+      <c r="S431" s="4" t="n"/>
+      <c r="T431" s="4" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="4" t="n"/>
@@ -7132,6 +11582,15 @@
       <c r="I432" s="4" t="n"/>
       <c r="J432" s="4" t="n"/>
       <c r="K432" s="4" t="n"/>
+      <c r="L432" s="4" t="n"/>
+      <c r="M432" s="4" t="n"/>
+      <c r="N432" s="4" t="n"/>
+      <c r="O432" s="4" t="n"/>
+      <c r="P432" s="4" t="n"/>
+      <c r="Q432" s="4" t="n"/>
+      <c r="R432" s="4" t="n"/>
+      <c r="S432" s="4" t="n"/>
+      <c r="T432" s="4" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="4" t="n"/>
@@ -7145,6 +11604,15 @@
       <c r="I433" s="4" t="n"/>
       <c r="J433" s="4" t="n"/>
       <c r="K433" s="4" t="n"/>
+      <c r="L433" s="4" t="n"/>
+      <c r="M433" s="4" t="n"/>
+      <c r="N433" s="4" t="n"/>
+      <c r="O433" s="4" t="n"/>
+      <c r="P433" s="4" t="n"/>
+      <c r="Q433" s="4" t="n"/>
+      <c r="R433" s="4" t="n"/>
+      <c r="S433" s="4" t="n"/>
+      <c r="T433" s="4" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="4" t="n"/>
@@ -7158,6 +11626,15 @@
       <c r="I434" s="4" t="n"/>
       <c r="J434" s="4" t="n"/>
       <c r="K434" s="4" t="n"/>
+      <c r="L434" s="4" t="n"/>
+      <c r="M434" s="4" t="n"/>
+      <c r="N434" s="4" t="n"/>
+      <c r="O434" s="4" t="n"/>
+      <c r="P434" s="4" t="n"/>
+      <c r="Q434" s="4" t="n"/>
+      <c r="R434" s="4" t="n"/>
+      <c r="S434" s="4" t="n"/>
+      <c r="T434" s="4" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="4" t="n"/>
@@ -7171,6 +11648,15 @@
       <c r="I435" s="4" t="n"/>
       <c r="J435" s="4" t="n"/>
       <c r="K435" s="4" t="n"/>
+      <c r="L435" s="4" t="n"/>
+      <c r="M435" s="4" t="n"/>
+      <c r="N435" s="4" t="n"/>
+      <c r="O435" s="4" t="n"/>
+      <c r="P435" s="4" t="n"/>
+      <c r="Q435" s="4" t="n"/>
+      <c r="R435" s="4" t="n"/>
+      <c r="S435" s="4" t="n"/>
+      <c r="T435" s="4" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="4" t="n"/>
@@ -7184,6 +11670,15 @@
       <c r="I436" s="4" t="n"/>
       <c r="J436" s="4" t="n"/>
       <c r="K436" s="4" t="n"/>
+      <c r="L436" s="4" t="n"/>
+      <c r="M436" s="4" t="n"/>
+      <c r="N436" s="4" t="n"/>
+      <c r="O436" s="4" t="n"/>
+      <c r="P436" s="4" t="n"/>
+      <c r="Q436" s="4" t="n"/>
+      <c r="R436" s="4" t="n"/>
+      <c r="S436" s="4" t="n"/>
+      <c r="T436" s="4" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="4" t="n"/>
@@ -7197,6 +11692,15 @@
       <c r="I437" s="4" t="n"/>
       <c r="J437" s="4" t="n"/>
       <c r="K437" s="4" t="n"/>
+      <c r="L437" s="4" t="n"/>
+      <c r="M437" s="4" t="n"/>
+      <c r="N437" s="4" t="n"/>
+      <c r="O437" s="4" t="n"/>
+      <c r="P437" s="4" t="n"/>
+      <c r="Q437" s="4" t="n"/>
+      <c r="R437" s="4" t="n"/>
+      <c r="S437" s="4" t="n"/>
+      <c r="T437" s="4" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="4" t="n"/>
@@ -7210,6 +11714,15 @@
       <c r="I438" s="4" t="n"/>
       <c r="J438" s="4" t="n"/>
       <c r="K438" s="4" t="n"/>
+      <c r="L438" s="4" t="n"/>
+      <c r="M438" s="4" t="n"/>
+      <c r="N438" s="4" t="n"/>
+      <c r="O438" s="4" t="n"/>
+      <c r="P438" s="4" t="n"/>
+      <c r="Q438" s="4" t="n"/>
+      <c r="R438" s="4" t="n"/>
+      <c r="S438" s="4" t="n"/>
+      <c r="T438" s="4" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="4" t="n"/>
@@ -7223,6 +11736,15 @@
       <c r="I439" s="4" t="n"/>
       <c r="J439" s="4" t="n"/>
       <c r="K439" s="4" t="n"/>
+      <c r="L439" s="4" t="n"/>
+      <c r="M439" s="4" t="n"/>
+      <c r="N439" s="4" t="n"/>
+      <c r="O439" s="4" t="n"/>
+      <c r="P439" s="4" t="n"/>
+      <c r="Q439" s="4" t="n"/>
+      <c r="R439" s="4" t="n"/>
+      <c r="S439" s="4" t="n"/>
+      <c r="T439" s="4" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="4" t="n"/>
@@ -7236,6 +11758,15 @@
       <c r="I440" s="4" t="n"/>
       <c r="J440" s="4" t="n"/>
       <c r="K440" s="4" t="n"/>
+      <c r="L440" s="4" t="n"/>
+      <c r="M440" s="4" t="n"/>
+      <c r="N440" s="4" t="n"/>
+      <c r="O440" s="4" t="n"/>
+      <c r="P440" s="4" t="n"/>
+      <c r="Q440" s="4" t="n"/>
+      <c r="R440" s="4" t="n"/>
+      <c r="S440" s="4" t="n"/>
+      <c r="T440" s="4" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="4" t="n"/>
@@ -7249,6 +11780,15 @@
       <c r="I441" s="4" t="n"/>
       <c r="J441" s="4" t="n"/>
       <c r="K441" s="4" t="n"/>
+      <c r="L441" s="4" t="n"/>
+      <c r="M441" s="4" t="n"/>
+      <c r="N441" s="4" t="n"/>
+      <c r="O441" s="4" t="n"/>
+      <c r="P441" s="4" t="n"/>
+      <c r="Q441" s="4" t="n"/>
+      <c r="R441" s="4" t="n"/>
+      <c r="S441" s="4" t="n"/>
+      <c r="T441" s="4" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="4" t="n"/>
@@ -7262,6 +11802,15 @@
       <c r="I442" s="4" t="n"/>
       <c r="J442" s="4" t="n"/>
       <c r="K442" s="4" t="n"/>
+      <c r="L442" s="4" t="n"/>
+      <c r="M442" s="4" t="n"/>
+      <c r="N442" s="4" t="n"/>
+      <c r="O442" s="4" t="n"/>
+      <c r="P442" s="4" t="n"/>
+      <c r="Q442" s="4" t="n"/>
+      <c r="R442" s="4" t="n"/>
+      <c r="S442" s="4" t="n"/>
+      <c r="T442" s="4" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="4" t="n"/>
@@ -7275,6 +11824,15 @@
       <c r="I443" s="4" t="n"/>
       <c r="J443" s="4" t="n"/>
       <c r="K443" s="4" t="n"/>
+      <c r="L443" s="4" t="n"/>
+      <c r="M443" s="4" t="n"/>
+      <c r="N443" s="4" t="n"/>
+      <c r="O443" s="4" t="n"/>
+      <c r="P443" s="4" t="n"/>
+      <c r="Q443" s="4" t="n"/>
+      <c r="R443" s="4" t="n"/>
+      <c r="S443" s="4" t="n"/>
+      <c r="T443" s="4" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="4" t="n"/>
@@ -7288,6 +11846,15 @@
       <c r="I444" s="4" t="n"/>
       <c r="J444" s="4" t="n"/>
       <c r="K444" s="4" t="n"/>
+      <c r="L444" s="4" t="n"/>
+      <c r="M444" s="4" t="n"/>
+      <c r="N444" s="4" t="n"/>
+      <c r="O444" s="4" t="n"/>
+      <c r="P444" s="4" t="n"/>
+      <c r="Q444" s="4" t="n"/>
+      <c r="R444" s="4" t="n"/>
+      <c r="S444" s="4" t="n"/>
+      <c r="T444" s="4" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="4" t="n"/>
@@ -7301,6 +11868,15 @@
       <c r="I445" s="4" t="n"/>
       <c r="J445" s="4" t="n"/>
       <c r="K445" s="4" t="n"/>
+      <c r="L445" s="4" t="n"/>
+      <c r="M445" s="4" t="n"/>
+      <c r="N445" s="4" t="n"/>
+      <c r="O445" s="4" t="n"/>
+      <c r="P445" s="4" t="n"/>
+      <c r="Q445" s="4" t="n"/>
+      <c r="R445" s="4" t="n"/>
+      <c r="S445" s="4" t="n"/>
+      <c r="T445" s="4" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="4" t="n"/>
@@ -7314,6 +11890,15 @@
       <c r="I446" s="4" t="n"/>
       <c r="J446" s="4" t="n"/>
       <c r="K446" s="4" t="n"/>
+      <c r="L446" s="4" t="n"/>
+      <c r="M446" s="4" t="n"/>
+      <c r="N446" s="4" t="n"/>
+      <c r="O446" s="4" t="n"/>
+      <c r="P446" s="4" t="n"/>
+      <c r="Q446" s="4" t="n"/>
+      <c r="R446" s="4" t="n"/>
+      <c r="S446" s="4" t="n"/>
+      <c r="T446" s="4" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="4" t="n"/>
@@ -7327,6 +11912,15 @@
       <c r="I447" s="4" t="n"/>
       <c r="J447" s="4" t="n"/>
       <c r="K447" s="4" t="n"/>
+      <c r="L447" s="4" t="n"/>
+      <c r="M447" s="4" t="n"/>
+      <c r="N447" s="4" t="n"/>
+      <c r="O447" s="4" t="n"/>
+      <c r="P447" s="4" t="n"/>
+      <c r="Q447" s="4" t="n"/>
+      <c r="R447" s="4" t="n"/>
+      <c r="S447" s="4" t="n"/>
+      <c r="T447" s="4" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="4" t="n"/>
@@ -7340,6 +11934,15 @@
       <c r="I448" s="4" t="n"/>
       <c r="J448" s="4" t="n"/>
       <c r="K448" s="4" t="n"/>
+      <c r="L448" s="4" t="n"/>
+      <c r="M448" s="4" t="n"/>
+      <c r="N448" s="4" t="n"/>
+      <c r="O448" s="4" t="n"/>
+      <c r="P448" s="4" t="n"/>
+      <c r="Q448" s="4" t="n"/>
+      <c r="R448" s="4" t="n"/>
+      <c r="S448" s="4" t="n"/>
+      <c r="T448" s="4" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="4" t="n"/>
@@ -7353,6 +11956,15 @@
       <c r="I449" s="4" t="n"/>
       <c r="J449" s="4" t="n"/>
       <c r="K449" s="4" t="n"/>
+      <c r="L449" s="4" t="n"/>
+      <c r="M449" s="4" t="n"/>
+      <c r="N449" s="4" t="n"/>
+      <c r="O449" s="4" t="n"/>
+      <c r="P449" s="4" t="n"/>
+      <c r="Q449" s="4" t="n"/>
+      <c r="R449" s="4" t="n"/>
+      <c r="S449" s="4" t="n"/>
+      <c r="T449" s="4" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="4" t="n"/>
@@ -7366,6 +11978,15 @@
       <c r="I450" s="4" t="n"/>
       <c r="J450" s="4" t="n"/>
       <c r="K450" s="4" t="n"/>
+      <c r="L450" s="4" t="n"/>
+      <c r="M450" s="4" t="n"/>
+      <c r="N450" s="4" t="n"/>
+      <c r="O450" s="4" t="n"/>
+      <c r="P450" s="4" t="n"/>
+      <c r="Q450" s="4" t="n"/>
+      <c r="R450" s="4" t="n"/>
+      <c r="S450" s="4" t="n"/>
+      <c r="T450" s="4" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="4" t="n"/>
@@ -7379,6 +12000,15 @@
       <c r="I451" s="4" t="n"/>
       <c r="J451" s="4" t="n"/>
       <c r="K451" s="4" t="n"/>
+      <c r="L451" s="4" t="n"/>
+      <c r="M451" s="4" t="n"/>
+      <c r="N451" s="4" t="n"/>
+      <c r="O451" s="4" t="n"/>
+      <c r="P451" s="4" t="n"/>
+      <c r="Q451" s="4" t="n"/>
+      <c r="R451" s="4" t="n"/>
+      <c r="S451" s="4" t="n"/>
+      <c r="T451" s="4" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="4" t="n"/>
@@ -7392,6 +12022,15 @@
       <c r="I452" s="4" t="n"/>
       <c r="J452" s="4" t="n"/>
       <c r="K452" s="4" t="n"/>
+      <c r="L452" s="4" t="n"/>
+      <c r="M452" s="4" t="n"/>
+      <c r="N452" s="4" t="n"/>
+      <c r="O452" s="4" t="n"/>
+      <c r="P452" s="4" t="n"/>
+      <c r="Q452" s="4" t="n"/>
+      <c r="R452" s="4" t="n"/>
+      <c r="S452" s="4" t="n"/>
+      <c r="T452" s="4" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="4" t="n"/>
@@ -7405,6 +12044,15 @@
       <c r="I453" s="4" t="n"/>
       <c r="J453" s="4" t="n"/>
       <c r="K453" s="4" t="n"/>
+      <c r="L453" s="4" t="n"/>
+      <c r="M453" s="4" t="n"/>
+      <c r="N453" s="4" t="n"/>
+      <c r="O453" s="4" t="n"/>
+      <c r="P453" s="4" t="n"/>
+      <c r="Q453" s="4" t="n"/>
+      <c r="R453" s="4" t="n"/>
+      <c r="S453" s="4" t="n"/>
+      <c r="T453" s="4" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="4" t="n"/>
@@ -7418,6 +12066,15 @@
       <c r="I454" s="4" t="n"/>
       <c r="J454" s="4" t="n"/>
       <c r="K454" s="4" t="n"/>
+      <c r="L454" s="4" t="n"/>
+      <c r="M454" s="4" t="n"/>
+      <c r="N454" s="4" t="n"/>
+      <c r="O454" s="4" t="n"/>
+      <c r="P454" s="4" t="n"/>
+      <c r="Q454" s="4" t="n"/>
+      <c r="R454" s="4" t="n"/>
+      <c r="S454" s="4" t="n"/>
+      <c r="T454" s="4" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="4" t="n"/>
@@ -7431,6 +12088,15 @@
       <c r="I455" s="4" t="n"/>
       <c r="J455" s="4" t="n"/>
       <c r="K455" s="4" t="n"/>
+      <c r="L455" s="4" t="n"/>
+      <c r="M455" s="4" t="n"/>
+      <c r="N455" s="4" t="n"/>
+      <c r="O455" s="4" t="n"/>
+      <c r="P455" s="4" t="n"/>
+      <c r="Q455" s="4" t="n"/>
+      <c r="R455" s="4" t="n"/>
+      <c r="S455" s="4" t="n"/>
+      <c r="T455" s="4" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="4" t="n"/>
@@ -7444,6 +12110,15 @@
       <c r="I456" s="4" t="n"/>
       <c r="J456" s="4" t="n"/>
       <c r="K456" s="4" t="n"/>
+      <c r="L456" s="4" t="n"/>
+      <c r="M456" s="4" t="n"/>
+      <c r="N456" s="4" t="n"/>
+      <c r="O456" s="4" t="n"/>
+      <c r="P456" s="4" t="n"/>
+      <c r="Q456" s="4" t="n"/>
+      <c r="R456" s="4" t="n"/>
+      <c r="S456" s="4" t="n"/>
+      <c r="T456" s="4" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="4" t="n"/>
@@ -7457,6 +12132,15 @@
       <c r="I457" s="4" t="n"/>
       <c r="J457" s="4" t="n"/>
       <c r="K457" s="4" t="n"/>
+      <c r="L457" s="4" t="n"/>
+      <c r="M457" s="4" t="n"/>
+      <c r="N457" s="4" t="n"/>
+      <c r="O457" s="4" t="n"/>
+      <c r="P457" s="4" t="n"/>
+      <c r="Q457" s="4" t="n"/>
+      <c r="R457" s="4" t="n"/>
+      <c r="S457" s="4" t="n"/>
+      <c r="T457" s="4" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="4" t="n"/>
@@ -7470,6 +12154,15 @@
       <c r="I458" s="4" t="n"/>
       <c r="J458" s="4" t="n"/>
       <c r="K458" s="4" t="n"/>
+      <c r="L458" s="4" t="n"/>
+      <c r="M458" s="4" t="n"/>
+      <c r="N458" s="4" t="n"/>
+      <c r="O458" s="4" t="n"/>
+      <c r="P458" s="4" t="n"/>
+      <c r="Q458" s="4" t="n"/>
+      <c r="R458" s="4" t="n"/>
+      <c r="S458" s="4" t="n"/>
+      <c r="T458" s="4" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="4" t="n"/>
@@ -7483,6 +12176,15 @@
       <c r="I459" s="4" t="n"/>
       <c r="J459" s="4" t="n"/>
       <c r="K459" s="4" t="n"/>
+      <c r="L459" s="4" t="n"/>
+      <c r="M459" s="4" t="n"/>
+      <c r="N459" s="4" t="n"/>
+      <c r="O459" s="4" t="n"/>
+      <c r="P459" s="4" t="n"/>
+      <c r="Q459" s="4" t="n"/>
+      <c r="R459" s="4" t="n"/>
+      <c r="S459" s="4" t="n"/>
+      <c r="T459" s="4" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="4" t="n"/>
@@ -7496,6 +12198,15 @@
       <c r="I460" s="4" t="n"/>
       <c r="J460" s="4" t="n"/>
       <c r="K460" s="4" t="n"/>
+      <c r="L460" s="4" t="n"/>
+      <c r="M460" s="4" t="n"/>
+      <c r="N460" s="4" t="n"/>
+      <c r="O460" s="4" t="n"/>
+      <c r="P460" s="4" t="n"/>
+      <c r="Q460" s="4" t="n"/>
+      <c r="R460" s="4" t="n"/>
+      <c r="S460" s="4" t="n"/>
+      <c r="T460" s="4" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="4" t="n"/>
@@ -7509,6 +12220,15 @@
       <c r="I461" s="4" t="n"/>
       <c r="J461" s="4" t="n"/>
       <c r="K461" s="4" t="n"/>
+      <c r="L461" s="4" t="n"/>
+      <c r="M461" s="4" t="n"/>
+      <c r="N461" s="4" t="n"/>
+      <c r="O461" s="4" t="n"/>
+      <c r="P461" s="4" t="n"/>
+      <c r="Q461" s="4" t="n"/>
+      <c r="R461" s="4" t="n"/>
+      <c r="S461" s="4" t="n"/>
+      <c r="T461" s="4" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="4" t="n"/>
@@ -7522,6 +12242,15 @@
       <c r="I462" s="4" t="n"/>
       <c r="J462" s="4" t="n"/>
       <c r="K462" s="4" t="n"/>
+      <c r="L462" s="4" t="n"/>
+      <c r="M462" s="4" t="n"/>
+      <c r="N462" s="4" t="n"/>
+      <c r="O462" s="4" t="n"/>
+      <c r="P462" s="4" t="n"/>
+      <c r="Q462" s="4" t="n"/>
+      <c r="R462" s="4" t="n"/>
+      <c r="S462" s="4" t="n"/>
+      <c r="T462" s="4" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="4" t="n"/>
@@ -7535,6 +12264,15 @@
       <c r="I463" s="4" t="n"/>
       <c r="J463" s="4" t="n"/>
       <c r="K463" s="4" t="n"/>
+      <c r="L463" s="4" t="n"/>
+      <c r="M463" s="4" t="n"/>
+      <c r="N463" s="4" t="n"/>
+      <c r="O463" s="4" t="n"/>
+      <c r="P463" s="4" t="n"/>
+      <c r="Q463" s="4" t="n"/>
+      <c r="R463" s="4" t="n"/>
+      <c r="S463" s="4" t="n"/>
+      <c r="T463" s="4" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="4" t="n"/>
@@ -7548,6 +12286,15 @@
       <c r="I464" s="4" t="n"/>
       <c r="J464" s="4" t="n"/>
       <c r="K464" s="4" t="n"/>
+      <c r="L464" s="4" t="n"/>
+      <c r="M464" s="4" t="n"/>
+      <c r="N464" s="4" t="n"/>
+      <c r="O464" s="4" t="n"/>
+      <c r="P464" s="4" t="n"/>
+      <c r="Q464" s="4" t="n"/>
+      <c r="R464" s="4" t="n"/>
+      <c r="S464" s="4" t="n"/>
+      <c r="T464" s="4" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="4" t="n"/>
@@ -7561,6 +12308,15 @@
       <c r="I465" s="4" t="n"/>
       <c r="J465" s="4" t="n"/>
       <c r="K465" s="4" t="n"/>
+      <c r="L465" s="4" t="n"/>
+      <c r="M465" s="4" t="n"/>
+      <c r="N465" s="4" t="n"/>
+      <c r="O465" s="4" t="n"/>
+      <c r="P465" s="4" t="n"/>
+      <c r="Q465" s="4" t="n"/>
+      <c r="R465" s="4" t="n"/>
+      <c r="S465" s="4" t="n"/>
+      <c r="T465" s="4" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="4" t="n"/>
@@ -7574,6 +12330,15 @@
       <c r="I466" s="4" t="n"/>
       <c r="J466" s="4" t="n"/>
       <c r="K466" s="4" t="n"/>
+      <c r="L466" s="4" t="n"/>
+      <c r="M466" s="4" t="n"/>
+      <c r="N466" s="4" t="n"/>
+      <c r="O466" s="4" t="n"/>
+      <c r="P466" s="4" t="n"/>
+      <c r="Q466" s="4" t="n"/>
+      <c r="R466" s="4" t="n"/>
+      <c r="S466" s="4" t="n"/>
+      <c r="T466" s="4" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="4" t="n"/>
@@ -7587,6 +12352,15 @@
       <c r="I467" s="4" t="n"/>
       <c r="J467" s="4" t="n"/>
       <c r="K467" s="4" t="n"/>
+      <c r="L467" s="4" t="n"/>
+      <c r="M467" s="4" t="n"/>
+      <c r="N467" s="4" t="n"/>
+      <c r="O467" s="4" t="n"/>
+      <c r="P467" s="4" t="n"/>
+      <c r="Q467" s="4" t="n"/>
+      <c r="R467" s="4" t="n"/>
+      <c r="S467" s="4" t="n"/>
+      <c r="T467" s="4" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="4" t="n"/>
@@ -7600,6 +12374,15 @@
       <c r="I468" s="4" t="n"/>
       <c r="J468" s="4" t="n"/>
       <c r="K468" s="4" t="n"/>
+      <c r="L468" s="4" t="n"/>
+      <c r="M468" s="4" t="n"/>
+      <c r="N468" s="4" t="n"/>
+      <c r="O468" s="4" t="n"/>
+      <c r="P468" s="4" t="n"/>
+      <c r="Q468" s="4" t="n"/>
+      <c r="R468" s="4" t="n"/>
+      <c r="S468" s="4" t="n"/>
+      <c r="T468" s="4" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="4" t="n"/>
@@ -7613,6 +12396,15 @@
       <c r="I469" s="4" t="n"/>
       <c r="J469" s="4" t="n"/>
       <c r="K469" s="4" t="n"/>
+      <c r="L469" s="4" t="n"/>
+      <c r="M469" s="4" t="n"/>
+      <c r="N469" s="4" t="n"/>
+      <c r="O469" s="4" t="n"/>
+      <c r="P469" s="4" t="n"/>
+      <c r="Q469" s="4" t="n"/>
+      <c r="R469" s="4" t="n"/>
+      <c r="S469" s="4" t="n"/>
+      <c r="T469" s="4" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="4" t="n"/>
@@ -7626,6 +12418,15 @@
       <c r="I470" s="4" t="n"/>
       <c r="J470" s="4" t="n"/>
       <c r="K470" s="4" t="n"/>
+      <c r="L470" s="4" t="n"/>
+      <c r="M470" s="4" t="n"/>
+      <c r="N470" s="4" t="n"/>
+      <c r="O470" s="4" t="n"/>
+      <c r="P470" s="4" t="n"/>
+      <c r="Q470" s="4" t="n"/>
+      <c r="R470" s="4" t="n"/>
+      <c r="S470" s="4" t="n"/>
+      <c r="T470" s="4" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="4" t="n"/>
@@ -7639,6 +12440,15 @@
       <c r="I471" s="4" t="n"/>
       <c r="J471" s="4" t="n"/>
       <c r="K471" s="4" t="n"/>
+      <c r="L471" s="4" t="n"/>
+      <c r="M471" s="4" t="n"/>
+      <c r="N471" s="4" t="n"/>
+      <c r="O471" s="4" t="n"/>
+      <c r="P471" s="4" t="n"/>
+      <c r="Q471" s="4" t="n"/>
+      <c r="R471" s="4" t="n"/>
+      <c r="S471" s="4" t="n"/>
+      <c r="T471" s="4" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="4" t="n"/>
@@ -7652,6 +12462,15 @@
       <c r="I472" s="4" t="n"/>
       <c r="J472" s="4" t="n"/>
       <c r="K472" s="4" t="n"/>
+      <c r="L472" s="4" t="n"/>
+      <c r="M472" s="4" t="n"/>
+      <c r="N472" s="4" t="n"/>
+      <c r="O472" s="4" t="n"/>
+      <c r="P472" s="4" t="n"/>
+      <c r="Q472" s="4" t="n"/>
+      <c r="R472" s="4" t="n"/>
+      <c r="S472" s="4" t="n"/>
+      <c r="T472" s="4" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="4" t="n"/>
@@ -7665,6 +12484,15 @@
       <c r="I473" s="4" t="n"/>
       <c r="J473" s="4" t="n"/>
       <c r="K473" s="4" t="n"/>
+      <c r="L473" s="4" t="n"/>
+      <c r="M473" s="4" t="n"/>
+      <c r="N473" s="4" t="n"/>
+      <c r="O473" s="4" t="n"/>
+      <c r="P473" s="4" t="n"/>
+      <c r="Q473" s="4" t="n"/>
+      <c r="R473" s="4" t="n"/>
+      <c r="S473" s="4" t="n"/>
+      <c r="T473" s="4" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="4" t="n"/>
@@ -7678,6 +12506,15 @@
       <c r="I474" s="4" t="n"/>
       <c r="J474" s="4" t="n"/>
       <c r="K474" s="4" t="n"/>
+      <c r="L474" s="4" t="n"/>
+      <c r="M474" s="4" t="n"/>
+      <c r="N474" s="4" t="n"/>
+      <c r="O474" s="4" t="n"/>
+      <c r="P474" s="4" t="n"/>
+      <c r="Q474" s="4" t="n"/>
+      <c r="R474" s="4" t="n"/>
+      <c r="S474" s="4" t="n"/>
+      <c r="T474" s="4" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="4" t="n"/>
@@ -7691,6 +12528,15 @@
       <c r="I475" s="4" t="n"/>
       <c r="J475" s="4" t="n"/>
       <c r="K475" s="4" t="n"/>
+      <c r="L475" s="4" t="n"/>
+      <c r="M475" s="4" t="n"/>
+      <c r="N475" s="4" t="n"/>
+      <c r="O475" s="4" t="n"/>
+      <c r="P475" s="4" t="n"/>
+      <c r="Q475" s="4" t="n"/>
+      <c r="R475" s="4" t="n"/>
+      <c r="S475" s="4" t="n"/>
+      <c r="T475" s="4" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="4" t="n"/>
@@ -7704,6 +12550,15 @@
       <c r="I476" s="4" t="n"/>
       <c r="J476" s="4" t="n"/>
       <c r="K476" s="4" t="n"/>
+      <c r="L476" s="4" t="n"/>
+      <c r="M476" s="4" t="n"/>
+      <c r="N476" s="4" t="n"/>
+      <c r="O476" s="4" t="n"/>
+      <c r="P476" s="4" t="n"/>
+      <c r="Q476" s="4" t="n"/>
+      <c r="R476" s="4" t="n"/>
+      <c r="S476" s="4" t="n"/>
+      <c r="T476" s="4" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="4" t="n"/>
@@ -7717,6 +12572,15 @@
       <c r="I477" s="4" t="n"/>
       <c r="J477" s="4" t="n"/>
       <c r="K477" s="4" t="n"/>
+      <c r="L477" s="4" t="n"/>
+      <c r="M477" s="4" t="n"/>
+      <c r="N477" s="4" t="n"/>
+      <c r="O477" s="4" t="n"/>
+      <c r="P477" s="4" t="n"/>
+      <c r="Q477" s="4" t="n"/>
+      <c r="R477" s="4" t="n"/>
+      <c r="S477" s="4" t="n"/>
+      <c r="T477" s="4" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="4" t="n"/>
@@ -7730,6 +12594,15 @@
       <c r="I478" s="4" t="n"/>
       <c r="J478" s="4" t="n"/>
       <c r="K478" s="4" t="n"/>
+      <c r="L478" s="4" t="n"/>
+      <c r="M478" s="4" t="n"/>
+      <c r="N478" s="4" t="n"/>
+      <c r="O478" s="4" t="n"/>
+      <c r="P478" s="4" t="n"/>
+      <c r="Q478" s="4" t="n"/>
+      <c r="R478" s="4" t="n"/>
+      <c r="S478" s="4" t="n"/>
+      <c r="T478" s="4" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="4" t="n"/>
@@ -7743,6 +12616,15 @@
       <c r="I479" s="4" t="n"/>
       <c r="J479" s="4" t="n"/>
       <c r="K479" s="4" t="n"/>
+      <c r="L479" s="4" t="n"/>
+      <c r="M479" s="4" t="n"/>
+      <c r="N479" s="4" t="n"/>
+      <c r="O479" s="4" t="n"/>
+      <c r="P479" s="4" t="n"/>
+      <c r="Q479" s="4" t="n"/>
+      <c r="R479" s="4" t="n"/>
+      <c r="S479" s="4" t="n"/>
+      <c r="T479" s="4" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="4" t="n"/>
@@ -7756,6 +12638,15 @@
       <c r="I480" s="4" t="n"/>
       <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
+      <c r="L480" s="4" t="n"/>
+      <c r="M480" s="4" t="n"/>
+      <c r="N480" s="4" t="n"/>
+      <c r="O480" s="4" t="n"/>
+      <c r="P480" s="4" t="n"/>
+      <c r="Q480" s="4" t="n"/>
+      <c r="R480" s="4" t="n"/>
+      <c r="S480" s="4" t="n"/>
+      <c r="T480" s="4" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="4" t="n"/>
@@ -7769,6 +12660,15 @@
       <c r="I481" s="4" t="n"/>
       <c r="J481" s="4" t="n"/>
       <c r="K481" s="4" t="n"/>
+      <c r="L481" s="4" t="n"/>
+      <c r="M481" s="4" t="n"/>
+      <c r="N481" s="4" t="n"/>
+      <c r="O481" s="4" t="n"/>
+      <c r="P481" s="4" t="n"/>
+      <c r="Q481" s="4" t="n"/>
+      <c r="R481" s="4" t="n"/>
+      <c r="S481" s="4" t="n"/>
+      <c r="T481" s="4" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="4" t="n"/>
@@ -7782,6 +12682,15 @@
       <c r="I482" s="4" t="n"/>
       <c r="J482" s="4" t="n"/>
       <c r="K482" s="4" t="n"/>
+      <c r="L482" s="4" t="n"/>
+      <c r="M482" s="4" t="n"/>
+      <c r="N482" s="4" t="n"/>
+      <c r="O482" s="4" t="n"/>
+      <c r="P482" s="4" t="n"/>
+      <c r="Q482" s="4" t="n"/>
+      <c r="R482" s="4" t="n"/>
+      <c r="S482" s="4" t="n"/>
+      <c r="T482" s="4" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="4" t="n"/>
@@ -7795,6 +12704,15 @@
       <c r="I483" s="4" t="n"/>
       <c r="J483" s="4" t="n"/>
       <c r="K483" s="4" t="n"/>
+      <c r="L483" s="4" t="n"/>
+      <c r="M483" s="4" t="n"/>
+      <c r="N483" s="4" t="n"/>
+      <c r="O483" s="4" t="n"/>
+      <c r="P483" s="4" t="n"/>
+      <c r="Q483" s="4" t="n"/>
+      <c r="R483" s="4" t="n"/>
+      <c r="S483" s="4" t="n"/>
+      <c r="T483" s="4" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="4" t="n"/>
@@ -7808,6 +12726,15 @@
       <c r="I484" s="4" t="n"/>
       <c r="J484" s="4" t="n"/>
       <c r="K484" s="4" t="n"/>
+      <c r="L484" s="4" t="n"/>
+      <c r="M484" s="4" t="n"/>
+      <c r="N484" s="4" t="n"/>
+      <c r="O484" s="4" t="n"/>
+      <c r="P484" s="4" t="n"/>
+      <c r="Q484" s="4" t="n"/>
+      <c r="R484" s="4" t="n"/>
+      <c r="S484" s="4" t="n"/>
+      <c r="T484" s="4" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="4" t="n"/>
@@ -7821,6 +12748,15 @@
       <c r="I485" s="4" t="n"/>
       <c r="J485" s="4" t="n"/>
       <c r="K485" s="4" t="n"/>
+      <c r="L485" s="4" t="n"/>
+      <c r="M485" s="4" t="n"/>
+      <c r="N485" s="4" t="n"/>
+      <c r="O485" s="4" t="n"/>
+      <c r="P485" s="4" t="n"/>
+      <c r="Q485" s="4" t="n"/>
+      <c r="R485" s="4" t="n"/>
+      <c r="S485" s="4" t="n"/>
+      <c r="T485" s="4" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="4" t="n"/>
@@ -7834,6 +12770,15 @@
       <c r="I486" s="4" t="n"/>
       <c r="J486" s="4" t="n"/>
       <c r="K486" s="4" t="n"/>
+      <c r="L486" s="4" t="n"/>
+      <c r="M486" s="4" t="n"/>
+      <c r="N486" s="4" t="n"/>
+      <c r="O486" s="4" t="n"/>
+      <c r="P486" s="4" t="n"/>
+      <c r="Q486" s="4" t="n"/>
+      <c r="R486" s="4" t="n"/>
+      <c r="S486" s="4" t="n"/>
+      <c r="T486" s="4" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="4" t="n"/>
@@ -7847,6 +12792,15 @@
       <c r="I487" s="4" t="n"/>
       <c r="J487" s="4" t="n"/>
       <c r="K487" s="4" t="n"/>
+      <c r="L487" s="4" t="n"/>
+      <c r="M487" s="4" t="n"/>
+      <c r="N487" s="4" t="n"/>
+      <c r="O487" s="4" t="n"/>
+      <c r="P487" s="4" t="n"/>
+      <c r="Q487" s="4" t="n"/>
+      <c r="R487" s="4" t="n"/>
+      <c r="S487" s="4" t="n"/>
+      <c r="T487" s="4" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="4" t="n"/>
@@ -7860,6 +12814,15 @@
       <c r="I488" s="4" t="n"/>
       <c r="J488" s="4" t="n"/>
       <c r="K488" s="4" t="n"/>
+      <c r="L488" s="4" t="n"/>
+      <c r="M488" s="4" t="n"/>
+      <c r="N488" s="4" t="n"/>
+      <c r="O488" s="4" t="n"/>
+      <c r="P488" s="4" t="n"/>
+      <c r="Q488" s="4" t="n"/>
+      <c r="R488" s="4" t="n"/>
+      <c r="S488" s="4" t="n"/>
+      <c r="T488" s="4" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="4" t="n"/>
@@ -7873,6 +12836,15 @@
       <c r="I489" s="4" t="n"/>
       <c r="J489" s="4" t="n"/>
       <c r="K489" s="4" t="n"/>
+      <c r="L489" s="4" t="n"/>
+      <c r="M489" s="4" t="n"/>
+      <c r="N489" s="4" t="n"/>
+      <c r="O489" s="4" t="n"/>
+      <c r="P489" s="4" t="n"/>
+      <c r="Q489" s="4" t="n"/>
+      <c r="R489" s="4" t="n"/>
+      <c r="S489" s="4" t="n"/>
+      <c r="T489" s="4" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="4" t="n"/>
@@ -7886,6 +12858,15 @@
       <c r="I490" s="4" t="n"/>
       <c r="J490" s="4" t="n"/>
       <c r="K490" s="4" t="n"/>
+      <c r="L490" s="4" t="n"/>
+      <c r="M490" s="4" t="n"/>
+      <c r="N490" s="4" t="n"/>
+      <c r="O490" s="4" t="n"/>
+      <c r="P490" s="4" t="n"/>
+      <c r="Q490" s="4" t="n"/>
+      <c r="R490" s="4" t="n"/>
+      <c r="S490" s="4" t="n"/>
+      <c r="T490" s="4" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="4" t="n"/>
@@ -7899,6 +12880,15 @@
       <c r="I491" s="4" t="n"/>
       <c r="J491" s="4" t="n"/>
       <c r="K491" s="4" t="n"/>
+      <c r="L491" s="4" t="n"/>
+      <c r="M491" s="4" t="n"/>
+      <c r="N491" s="4" t="n"/>
+      <c r="O491" s="4" t="n"/>
+      <c r="P491" s="4" t="n"/>
+      <c r="Q491" s="4" t="n"/>
+      <c r="R491" s="4" t="n"/>
+      <c r="S491" s="4" t="n"/>
+      <c r="T491" s="4" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="4" t="n"/>
@@ -7912,6 +12902,15 @@
       <c r="I492" s="4" t="n"/>
       <c r="J492" s="4" t="n"/>
       <c r="K492" s="4" t="n"/>
+      <c r="L492" s="4" t="n"/>
+      <c r="M492" s="4" t="n"/>
+      <c r="N492" s="4" t="n"/>
+      <c r="O492" s="4" t="n"/>
+      <c r="P492" s="4" t="n"/>
+      <c r="Q492" s="4" t="n"/>
+      <c r="R492" s="4" t="n"/>
+      <c r="S492" s="4" t="n"/>
+      <c r="T492" s="4" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="4" t="n"/>
@@ -7925,6 +12924,15 @@
       <c r="I493" s="4" t="n"/>
       <c r="J493" s="4" t="n"/>
       <c r="K493" s="4" t="n"/>
+      <c r="L493" s="4" t="n"/>
+      <c r="M493" s="4" t="n"/>
+      <c r="N493" s="4" t="n"/>
+      <c r="O493" s="4" t="n"/>
+      <c r="P493" s="4" t="n"/>
+      <c r="Q493" s="4" t="n"/>
+      <c r="R493" s="4" t="n"/>
+      <c r="S493" s="4" t="n"/>
+      <c r="T493" s="4" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="4" t="n"/>
@@ -7938,6 +12946,15 @@
       <c r="I494" s="4" t="n"/>
       <c r="J494" s="4" t="n"/>
       <c r="K494" s="4" t="n"/>
+      <c r="L494" s="4" t="n"/>
+      <c r="M494" s="4" t="n"/>
+      <c r="N494" s="4" t="n"/>
+      <c r="O494" s="4" t="n"/>
+      <c r="P494" s="4" t="n"/>
+      <c r="Q494" s="4" t="n"/>
+      <c r="R494" s="4" t="n"/>
+      <c r="S494" s="4" t="n"/>
+      <c r="T494" s="4" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="4" t="n"/>
@@ -7951,6 +12968,15 @@
       <c r="I495" s="4" t="n"/>
       <c r="J495" s="4" t="n"/>
       <c r="K495" s="4" t="n"/>
+      <c r="L495" s="4" t="n"/>
+      <c r="M495" s="4" t="n"/>
+      <c r="N495" s="4" t="n"/>
+      <c r="O495" s="4" t="n"/>
+      <c r="P495" s="4" t="n"/>
+      <c r="Q495" s="4" t="n"/>
+      <c r="R495" s="4" t="n"/>
+      <c r="S495" s="4" t="n"/>
+      <c r="T495" s="4" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="4" t="n"/>
@@ -7964,6 +12990,15 @@
       <c r="I496" s="4" t="n"/>
       <c r="J496" s="4" t="n"/>
       <c r="K496" s="4" t="n"/>
+      <c r="L496" s="4" t="n"/>
+      <c r="M496" s="4" t="n"/>
+      <c r="N496" s="4" t="n"/>
+      <c r="O496" s="4" t="n"/>
+      <c r="P496" s="4" t="n"/>
+      <c r="Q496" s="4" t="n"/>
+      <c r="R496" s="4" t="n"/>
+      <c r="S496" s="4" t="n"/>
+      <c r="T496" s="4" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="4" t="n"/>
@@ -7977,6 +13012,15 @@
       <c r="I497" s="4" t="n"/>
       <c r="J497" s="4" t="n"/>
       <c r="K497" s="4" t="n"/>
+      <c r="L497" s="4" t="n"/>
+      <c r="M497" s="4" t="n"/>
+      <c r="N497" s="4" t="n"/>
+      <c r="O497" s="4" t="n"/>
+      <c r="P497" s="4" t="n"/>
+      <c r="Q497" s="4" t="n"/>
+      <c r="R497" s="4" t="n"/>
+      <c r="S497" s="4" t="n"/>
+      <c r="T497" s="4" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="4" t="n"/>
@@ -7990,6 +13034,15 @@
       <c r="I498" s="4" t="n"/>
       <c r="J498" s="4" t="n"/>
       <c r="K498" s="4" t="n"/>
+      <c r="L498" s="4" t="n"/>
+      <c r="M498" s="4" t="n"/>
+      <c r="N498" s="4" t="n"/>
+      <c r="O498" s="4" t="n"/>
+      <c r="P498" s="4" t="n"/>
+      <c r="Q498" s="4" t="n"/>
+      <c r="R498" s="4" t="n"/>
+      <c r="S498" s="4" t="n"/>
+      <c r="T498" s="4" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="4" t="n"/>
@@ -8003,6 +13056,15 @@
       <c r="I499" s="4" t="n"/>
       <c r="J499" s="4" t="n"/>
       <c r="K499" s="4" t="n"/>
+      <c r="L499" s="4" t="n"/>
+      <c r="M499" s="4" t="n"/>
+      <c r="N499" s="4" t="n"/>
+      <c r="O499" s="4" t="n"/>
+      <c r="P499" s="4" t="n"/>
+      <c r="Q499" s="4" t="n"/>
+      <c r="R499" s="4" t="n"/>
+      <c r="S499" s="4" t="n"/>
+      <c r="T499" s="4" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="4" t="n"/>
@@ -8016,6 +13078,15 @@
       <c r="I500" s="4" t="n"/>
       <c r="J500" s="4" t="n"/>
       <c r="K500" s="4" t="n"/>
+      <c r="L500" s="4" t="n"/>
+      <c r="M500" s="4" t="n"/>
+      <c r="N500" s="4" t="n"/>
+      <c r="O500" s="4" t="n"/>
+      <c r="P500" s="4" t="n"/>
+      <c r="Q500" s="4" t="n"/>
+      <c r="R500" s="4" t="n"/>
+      <c r="S500" s="4" t="n"/>
+      <c r="T500" s="4" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="4" t="n"/>
@@ -8029,10 +13100,19 @@
       <c r="I501" s="4" t="n"/>
       <c r="J501" s="4" t="n"/>
       <c r="K501" s="4" t="n"/>
+      <c r="L501" s="4" t="n"/>
+      <c r="M501" s="4" t="n"/>
+      <c r="N501" s="4" t="n"/>
+      <c r="O501" s="4" t="n"/>
+      <c r="P501" s="4" t="n"/>
+      <c r="Q501" s="4" t="n"/>
+      <c r="R501" s="4" t="n"/>
+      <c r="S501" s="4" t="n"/>
+      <c r="T501" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K501"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:T501"/>
+  <dataValidations count="4">
     <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid materialization" error="Choose table, view, incremental or ephemeral." type="list">
       <formula1>=LISTS!$A$2:$A$5</formula1>
     </dataValidation>
@@ -8041,6 +13121,9 @@
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Custom datatype" error="Not in the suggested list - it will be used as typed. Click OK to keep it." type="list" errorStyle="information">
       <formula1>=LISTS!$C$2:$C$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Enter Y or N (or leave blank for the generator default)." type="list">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
